--- a/data/unlabel/unlabel_data.xlsx
+++ b/data/unlabel/unlabel_data.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C172"/>
+  <dimension ref="A1:C374"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,2224 +448,4850 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Let's video chat and text on imo! Get the free app https://imo.onelink.me/7QOl/ics</t>
+          <t>Let's chat on WhatsApp! It's a fast, simple, and secure app we can use to message and call each other for free. Get it at https://whatsapp.com/dl/</t>
         </is>
       </c>
       <c r="B2" t="n">
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>0.8563620339348258</v>
+        <v>0.7983353284853723</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Let's chat on WhatsApp! It's a fast, simple, and secure app we can use to message and call each other for free. Get it at https://whatsapp.com/dl/</t>
+          <t>Amoi sini company goldenbet99,apa kabar sudah bossku,lama dah tak try spin mari.jackpot,free game,Bonusgame menanti anda. Web ; goldenbet99 .com</t>
         </is>
       </c>
       <c r="B3" t="n">
         <v>1</v>
       </c>
       <c r="C3" t="n">
-        <v>0.8507161268238027</v>
+        <v>0.6317334321993615</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>You have a new MMS from 966506528932. You can pick up your MMS on https://mmsvd2.bics.com/mms. Your login name is 601133020565, your PIN is 083787.</t>
+          <t>Let's chat on WhatsApp! It's a fast, simple, and secure app we can use to message and call each other for free. Get it at https://whatsapp.com/dl/</t>
         </is>
       </c>
       <c r="B4" t="n">
         <v>1</v>
       </c>
       <c r="C4" t="n">
-        <v>0.9347915021394497</v>
+        <v>0.7983353284853723</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Alat dengar anda digunakan oleh kad SIM lain, kedudukan ialah: MCC:502; MNC:13; CELL:14281; LAC:23097</t>
+          <t>{Kasino-77} : Weekend Big W1n Package! Claim 1st Bns Slot 3O%</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C5" t="n">
-        <v>0.6813463462288205</v>
+        <v>0.7444172648447778</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Waalaikumsalam Sayangbie xperr sayangbie &lt;EMO&gt;&lt;EMO&gt;</t>
+          <t>နင်လိုမိန်းမငါ့နဲ့ပျက်ပီ</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>0</v>
       </c>
       <c r="C6" t="n">
-        <v>0.842526470573228</v>
+        <v>0.806330219123957</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Sayanggg plssss</t>
+          <t>没看到那性感叻</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>0</v>
       </c>
       <c r="C7" t="n">
-        <v>0.9371873614978325</v>
+        <v>0.6167427750569556</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>You have a new MMS from 966506528932. You can pick up your MMS on https://mmsvd2.bics.com/mms. Your login name is 601133020565, your PIN is 083787.</t>
+          <t>Air lbih</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C8" t="n">
-        <v>0.9347915021394497</v>
+        <v>0.848418340299723</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>FMCS SMS System Healthy</t>
+          <t>Sorry k mun akw minak btak bie mumeng</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C9" t="n">
-        <v>0.7875759089024956</v>
+        <v>0.728383794214132</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Call</t>
+          <t>89 dragon</t>
         </is>
       </c>
       <c r="B10" t="n">
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>0.9327214130597774</v>
+        <v>0.894444152925608</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>panjang citenye</t>
+          <t>Let's chat on WhatsApp! It's a fast, simple, and secure app we can use to message and call each other for free. Get it at https://whatsapp.com/dl/</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C11" t="n">
-        <v>0.8678373235784169</v>
+        <v>0.7983353284853723</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Amoi sini company goldenbet99,apa kabar sudah bossku,lama dah tak try spin mari.jackpot,free game,Bonusgame menanti anda. Web ; goldenbet99 .com</t>
+          <t>Pls bagi Mak fon kejap boleh....nanti Miss call...sy call balik..tq</t>
         </is>
       </c>
       <c r="B12" t="n">
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>0.592208612117288</v>
+        <v>0.8585644664508079</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Let's video chat and text on imo! Get the free app https://imo.onelink.me/7QOl/ics</t>
+          <t>Let's chat on WhatsApp! It's a fast, simple, and secure app we can use to message and call each other for free. Get it at https://whatsapp.com/dl/</t>
         </is>
       </c>
       <c r="B13" t="n">
         <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>0.8563618579730975</v>
+        <v>0.7983353284853723</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>I1M88: Web Done Upgrade! In/Out Lebih Mudah &amp; Cepat Jom Unlock Mystery Box Upto RM555 Lucky Gift RM35 - RM138 Google: I1M88 WS :+6016 -273 -1498</t>
+          <t>Empangan Batu - ID:WPKL1001RF 2025-06-16 00:00:53 RF Light Rain PassHour:1mm</t>
         </is>
       </c>
       <c r="B14" t="n">
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>0.8211705630055854</v>
+        <v>0.5338092593210961</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>H H G G 337 Call From Atlas N3w BOn0s Sl0T --Fr3xx Voucher-- note: C1imm Juni Wsp: 60_17_7078_902 Wsp: 60_17_7075_004</t>
+          <t>Ada kes oncall di green zone.pt nama nusaibah 6 tahun.laceration kt lower lip</t>
         </is>
       </c>
       <c r="B15" t="n">
         <v>1</v>
       </c>
       <c r="C15" t="n">
-        <v>0.7877251834588351</v>
+        <v>0.8739547876375939</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Ane nane iye sik angenen ndk yak inik pirem&lt;EMO&gt;</t>
+          <t>Let's chat on WhatsApp! It's a fast, simple, and secure app we can use to message and call each other for free. Get it at https://whatsapp.com/dl/</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C16" t="n">
-        <v>0.9275513056550474</v>
+        <v>0.7983353284853723</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Let's chat on WhatsApp! It's a fast, simple, and secure app we can use to message and call each other for free. Get it at https://whatsapp.com/dl/</t>
+          <t>742</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>0.8507161268238027</v>
+        <v>0.5735026451092933</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Your Credit Has Been Added By 0177173373. Total Added:RM 500. Your New Balance:RM545.1778</t>
+          <t>1763, Jalan Jambu 24 81400 Senai 柔佛州 马来西亚</t>
         </is>
       </c>
       <c r="B18" t="n">
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>0.907321978891685</v>
+        <v>0.7762748745936181</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>{Kasino-77} : Weekend Big W1n Package! Claim 1st Bns Slot 3O%</t>
+          <t>Mudah: I'm interested in your ad on Mudah Flat Pandan Mewah, please share more details with me.</t>
         </is>
       </c>
       <c r="B19" t="n">
         <v>1</v>
       </c>
       <c r="C19" t="n">
-        <v>0.6464981746552988</v>
+        <v>0.6532077936190392</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>klk nmpk nya sy bogel klk &lt;EMO&gt;</t>
+          <t>Ayo chat di WhatsApp, aplikasi yang cepat, sederhana, dan aman untuk berkirim pesan dan menelepon secara gratis. Dapatkan di https://whatsapp.com/dl/</t>
         </is>
       </c>
       <c r="B20" t="n">
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>0.9250328390110619</v>
+        <v>0.6300301404935096</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Sannah helwah fii umrik bie....semoga bie dmurahkan rezeki dpermudahkan urusan...aamin...guk2 lh alom umeng enh bahh.. ameng tuker jd umeng jak lah alom naran bie nah... Akw syg ekw samakk laka mula tbak kilak sapai engyak kenak kou x berubahh... Ipak akw k..sikit ms lel alom hel.kou settle...love u so much bie..</t>
+          <t>Ayo chat di WhatsApp, aplikasi yang cepat, sederhana, dan aman untuk berkirim pesan dan menelepon secara gratis. Dapatkan di https://whatsapp.com/dl/</t>
         </is>
       </c>
       <c r="B21" t="n">
         <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>0.9030740802477955</v>
+        <v>0.6300301404935096</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>MEGA GIVEAWAY TANPA DEPOSIT ! FREE KREDIT KHAS utk member terpilih sahaja. PM amoi kami Rebut skrg sebelum terlepas. Whatsapp : 45.77.242.198</t>
+          <t>Ayo chat di WhatsApp, aplikasi yang cepat, sederhana, dan aman untuk berkirim pesan dan menelepon secara gratis. Dapatkan di https://whatsapp.com/dl/</t>
         </is>
       </c>
       <c r="B22" t="n">
         <v>0</v>
       </c>
       <c r="C22" t="n">
-        <v>0.5820987600843022</v>
+        <v>0.6300301404935096</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Fr66 RM 50 dah masuk 1D! Kla1m Now!New Cus 80% C4sh2u 3v.ent Open! AFB x 0NEG0LD KLA1M: 016 - 367 6116 Want out? Reply STOP. 4bjkrvr;</t>
+          <t>sikmok2</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C23" t="n">
-        <v>0.929119428575364</v>
+        <v>0.7342517825108741</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>MEGA GIVEAWAY TANPA DEPOSIT ! FREE KREDIT KHAS utk member terpilih sahaja. PM amoi kami Rebut skrg sebelum terlepas. Whatsapp : 45.77.242.198</t>
+          <t>Let's chat on WhatsApp! It's a fast, simple, and secure app we can use to message and call each other for free. Get it at https://whatsapp.com/dl/</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C24" t="n">
-        <v>0.5820987600843022</v>
+        <v>0.7983353284853723</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>dkt kdai blok14,knp x bli mkn lg.ke nk tman,</t>
+          <t>Takpelah. Saya tau dah ada yg temankan awak sleepcall that's why taknak dgr suda suara perempuan yg gaya mcm sial babi ni. Takpelah, sorry ganggu awak dgn c dia. Okaylah, thanks sebab sudi dgrkan suara awak utk kali yg terakhir. Okaylah saya akan menjauh dan undur diri duluan</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C25" t="n">
-        <v>0.8539884389360826</v>
+        <v>0.5046023277300622</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Tp abg tetp sdh syg</t>
+          <t>E T: Wlcm u, MAX-M u=1441627946Q6 p=EEee7673 on:16/06 00:01:29</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C26" t="n">
-        <v>0.7507638021113402</v>
+        <v>0.7761575130480554</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Waalaikumsalam alhamdulillah masih waras lgi bang</t>
+          <t>Bendar mangkang keting mangkang butuh pukik dia.. Nya line ndai nemu clear</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C27" t="n">
-        <v>0.8921393357863397</v>
+        <v>0.7950637487429406</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>没看到那性感叻</t>
+          <t>tirak please me back ok</t>
         </is>
       </c>
       <c r="B28" t="n">
         <v>0</v>
       </c>
       <c r="C28" t="n">
-        <v>0.8243331622031034</v>
+        <v>0.7647222133618568</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>310419 is your Vyke verification code.</t>
+          <t>854461697560978</t>
         </is>
       </c>
       <c r="B29" t="n">
         <v>1</v>
       </c>
       <c r="C29" t="n">
-        <v>0.9012320521843674</v>
+        <v>0.8353436140078332</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>IMEI2 C542D0C7307BACE3197117713BF9F6B1349B6E8119B4DBE0E4EAD9E57A6B18ECB5BBA579F04801FA899F906345A4954DA185BA95E13E52AC742AE81586869FDA</t>
+          <t>晚安,亲爱的老婆&lt;EMO&gt;&lt;EMO&gt;&lt;EMO&gt;&lt;EMO&gt;</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C30" t="n">
-        <v>0.8517607621466237</v>
+        <v>0.5935865787524011</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>310419 is your Vyke verification code.</t>
+          <t>Safety and health is very important so when you reach home (Penang) please kindly let me know as well as kejashini akka Please be safe and safely reach home ,Thiveya ji Wherever you go please be safe and careful always, stay safe always,Thiveya ji As well as health please take care of your health,Thiveya thangapulla &lt;EMO&gt;</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C31" t="n">
-        <v>0.9012320521843674</v>
+        <v>0.5116615148526404</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Biesayang faham &lt;EMO&gt;&lt;EMO&gt;&lt;EMO&gt;</t>
+          <t>Amoi sini company goldenbet99,apa kabar sudah bossku,lama dah tak try spin mari.jackpot,free game,Bonusgame menanti anda. Web ; goldenbet99 .com</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C32" t="n">
-        <v>0.8305322928418944</v>
+        <v>0.6317334321993615</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Air lbih</t>
+          <t>Amoi sini company goldenbet99,apa kabar sudah bossku,lama dah tak try spin mari.jackpot,free game,Bonusgame menanti anda. Web ; goldenbet99 .com</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C33" t="n">
-        <v>0.863338996791864</v>
+        <v>0.6317334321993615</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>satu bar aje . jadinyaa takleh nk bkk wsp:)</t>
+          <t>Mudah: I'm interested in your ad on Mudah Pesona Villa Apartment Unit For Rent, please share more details with me.</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C34" t="n">
-        <v>0.8339259667555421</v>
+        <v>0.6832302955645349</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Sorry k mun akw minak btak bie mumeng</t>
+          <t>Amoi sini company goldenbet99,apa kabar sudah bossku,lama dah tak try spin mari.jackpot,free game,Bonusgame menanti anda. Web ; goldenbet99 .com</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C35" t="n">
-        <v>0.8341643618147712</v>
+        <v>0.5124115143220297</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>MEGA GIVEAWAY TANPA DEPOSIT ! FREE KREDIT KHAS utk member terpilih sahaja. PM amoi kami Rebut skrg sebelum terlepas. Whatsapp : 45.77.242.198</t>
+          <t>Takpelah. Saya tau dah ada yg temankan awak sleepcall that's why taknak dgr suda suara perempuan yg gaya mcm sial babi ni. Takpelah, sorry ganggu awak dgn c dia. Okaylah, thanks sebab sudi dgrkan suara awak utk kali yg terakhir. Okaylah saya akan menjauh dan undur diri duluan</t>
         </is>
       </c>
       <c r="B36" t="n">
         <v>0</v>
       </c>
       <c r="C36" t="n">
-        <v>0.5820987600843022</v>
+        <v>0.6064002718527445</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Aboi servis ranger. Tukar paip oil coler . Pak lang dan pon pasang i jem no 11. Udin setel bekho</t>
+          <t>(764090) okywpwzPoV</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C37" t="n">
-        <v>0.7671775751273691</v>
+        <v>0.7623781357209555</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Baka di ikaw yon aa iba number e dami mong number.! &lt;EMO&gt;</t>
+          <t>Name : Ajit Budget : as low as possible when move in : 1july How many ppl stay : 8 Nepal friend or family : workers Occupation : security Working company name/ school name : security company Local / Foreigner : Race : nepal Tenancy 1 or 2 years : 2</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C38" t="n">
-        <v>0.8761088723223743</v>
+        <v>0.5326576624314657</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>安记22包</t>
+          <t>BX99:您被选了(ong111)!恭喜您获得228次免费旋转。存RM50就解锁!bx99my{dot}com</t>
         </is>
       </c>
       <c r="B39" t="n">
         <v>0</v>
       </c>
       <c r="C39" t="n">
-        <v>0.8097287244109358</v>
+        <v>0.5293791498739847</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>FMCS SMS System Healthy</t>
+          <t>Oklah....goodluck kenal laki lain...aku doakan impian hang kawin dan jadi anjing pada azam tercapai. Azam lelaki terhebat kan</t>
         </is>
       </c>
       <c r="B40" t="n">
         <v>0</v>
       </c>
       <c r="C40" t="n">
-        <v>0.7875759089024956</v>
+        <v>0.8593468870718607</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>5986 yeDwmvzKna</t>
+          <t>Ayo chat di WhatsApp, aplikasi yang cepat, sederhana, dan aman untuk berkirim pesan dan menelepon secara gratis. Dapatkan di https://whatsapp.com/dl/</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C41" t="n">
-        <v>0.7567709673530102</v>
+        <v>0.7370392288763651</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>抱歉,现在不方便接电话。</t>
+          <t>BX99:您被选了(marioccc)!恭喜您获得228次免费旋转。存RM50就解锁!bx99my{dot}com</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C42" t="n">
-        <v>0.7751598911273817</v>
+        <v>0.722986975709664</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Your Credit Has Been Added By 0177173373. Total Added:RM 500. Your New Balance:RM545.1778</t>
+          <t>Let's use Meet to video chat: https://duo.app.goo.gl/2Dtc2LZ</t>
         </is>
       </c>
       <c r="B43" t="n">
         <v>1</v>
       </c>
       <c r="C43" t="n">
-        <v>0.907321978891685</v>
+        <v>0.8778616581361166</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>01c5f5b63a8635c7dog_</t>
+          <t>好消息!您的限时优惠从188次免费旋转增加至208次,仅需存款RM50!立即在12HUATmy{dot}com领取!</t>
         </is>
       </c>
       <c r="B44" t="n">
         <v>1</v>
       </c>
       <c r="C44" t="n">
-        <v>0.9407212710929678</v>
+        <v>0.778443256417977</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Aboi servis ranger. Tukar paip oil coler . Pak lang dan pon pasang i jem no 11. Udin setel bekho</t>
+          <t>Let's use Meet to video chat: https://duo.app.goo.gl/2Dtc2LZ</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C45" t="n">
-        <v>0.7671775751273691</v>
+        <v>0.8778616581361166</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>MEGA GIVEAWAY TANPA DEPOSIT ! FREE KREDIT KHAS utk member terpilih sahaja. PM amoi kami Rebut skrg sebelum terlepas. Whatsapp : 45.77.242.198</t>
+          <t>selamat ulang tahun kelahiran ya roma syg. moga kau panjang umur, murah rezeki dan diberikan kesihatan yg baik. dihari yg indah ak mau mntak maaf ya kt kau sbb slama 3tahun kita brkwan ak xprnah lakukan apa pn yg baik utk kau dan ak pn xtau nk explain apa lg sbb ak ckap ap pn mcm takda gunanya gara2 ak prnah tpu kau. maafkn ak yaa roma. ak harap kau bisa bhgia tnpa ak di samping kau dan ak brharap ada yg bisa bhgiakn kau hgga akhir hayat kau yaa. maafkn ak dan ak ikhlas maksudkn. terima kasih dh byk brkorban utk ak. ak sayangkn kau dr dlu ikhlas dan xprnah ada niat jahat. tu aja ak bisa ckap.</t>
         </is>
       </c>
       <c r="B46" t="n">
         <v>0</v>
       </c>
       <c r="C46" t="n">
-        <v>0.5820987600843022</v>
+        <v>0.8310553040106424</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Ko send gmbr tmpat c pian</t>
+          <t>Ok ...Jaga diri molek ..jgn susoh² Hati... ada masa Kita lepak skali</t>
         </is>
       </c>
       <c r="B47" t="n">
         <v>0</v>
       </c>
       <c r="C47" t="n">
-        <v>0.839503912189301</v>
+        <v>0.6720697488386759</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Tkpe ar tdo jela</t>
+          <t>Jom cuba aplikasi WhatsApp Business, saya menggunakannya untuk berhubung dengan pelanggan saya. Dapatkannya secara percuma di https://whatsapp.com/biz/</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C48" t="n">
-        <v>0.9126853370148479</v>
+        <v>0.7957651410500876</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>89 dragon</t>
+          <t>Jom cuba aplikasi WhatsApp Business, saya menggunakannya untuk berhubung dengan pelanggan saya. Dapatkannya secara percuma di https://whatsapp.com/biz/</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C49" t="n">
-        <v>0.9287843792766114</v>
+        <v>0.7957651410500876</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Aboi servis ranger. Tukar paip oil coler . Pak lang dan pon pasang i jem no 11. Udin setel bekho</t>
+          <t>Ok ...Jaga diri molek ..jgn susoh² Hati... ada masa Kita lepak skali</t>
         </is>
       </c>
       <c r="B50" t="n">
         <v>0</v>
       </c>
       <c r="C50" t="n">
-        <v>0.7671775751273691</v>
+        <v>0.6720697488386759</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>8725 RpewjrpbVY</t>
+          <t>HAHAHHAHA INI BUDAK SUKA TIDO PUKUL 4 PAGII NI</t>
         </is>
       </c>
       <c r="B51" t="n">
         <v>1</v>
       </c>
       <c r="C51" t="n">
-        <v>0.8936902518830975</v>
+        <v>0.5155193005006186</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>You Have 2 Missed Call(2) J..K8 Fr66 Rm.10 R3d pa0 j01n N0w!Dapatkan RM 10 j8k.jb5.mx To opt out, Reply STOP. f3blxu;</t>
+          <t>https://maps.apple.com/?ll=1.62042,103.72699&amp;q=Location</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C52" t="n">
-        <v>0.9454820712971133</v>
+        <v>0.5289406981070169</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Let's video chat and text on imo! Get the free app https://imo.onelink.me/7QOl/ics</t>
+          <t>https://maps.apple.com/?ll=1.62042,103.72699&amp;q=Location</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C53" t="n">
-        <v>0.8563618579730975</v>
+        <v>0.5289406981070169</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Salam</t>
+          <t>https://maps.apple.com/?ll=1.62042,103.72699&amp;q=Location</t>
         </is>
       </c>
       <c r="B54" t="n">
         <v>0</v>
       </c>
       <c r="C54" t="n">
-        <v>0.8786607621703429</v>
+        <v>0.5289406981070169</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Aboi servis ranger. Tukar paip oil coler . Pak lang dan pon pasang i jem no 11. Udin setel bekho</t>
+          <t>https://maps.apple.com/?ll=1.62042,103.72699&amp;q=Location</t>
         </is>
       </c>
       <c r="B55" t="n">
         <v>0</v>
       </c>
       <c r="C55" t="n">
-        <v>0.7671775751273691</v>
+        <v>0.5289410557348856</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>8af157507091948bdog_</t>
+          <t>7 thun bersabar, last2 sbb hal online..putus Tahniah.. Bye!</t>
         </is>
       </c>
       <c r="B56" t="n">
         <v>1</v>
       </c>
       <c r="C56" t="n">
-        <v>0.9080784619941495</v>
+        <v>0.5192491207520834</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Let's chat on WhatsApp! It's a fast, simple, and secure app we can use to message and call each other for free. Get it at https://whatsapp.com/dl/</t>
+          <t>E T: Wlcm u, MAX-M u=1441653931Q6 p=IIii2672 on:16/06 00:02:35</t>
         </is>
       </c>
       <c r="B57" t="n">
         <v>1</v>
       </c>
       <c r="C57" t="n">
-        <v>0.8507161268238027</v>
+        <v>0.6583528314034811</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Aboi servis ranger. Tukar paip oil coler . Pak lang dan pon pasang i jem no 11. Udin setel bekho</t>
+          <t>4那享受当小三虐妻的求主推到火海去那被后伤害我和婚姻求主不要放过他们以恶报善火&lt;EMO&gt;海去你看到恶计淫 pls come to those against the hurt our marriage opress spouse Abba Jesus saw, UArise!</t>
         </is>
       </c>
       <c r="B58" t="n">
         <v>0</v>
       </c>
       <c r="C58" t="n">
-        <v>0.7671775751273691</v>
+        <v>0.7681363429625162</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Tandas ada&lt;EMO&gt;</t>
+          <t>https://maps.apple.com/?ll=1.62042,103.72699&amp;q=Location</t>
         </is>
       </c>
       <c r="B59" t="n">
         <v>0</v>
       </c>
       <c r="C59" t="n">
-        <v>0.9450917088681222</v>
+        <v>0.5289406981070169</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Chat with me on WhatsApp! It lets us message privately and share photos, videos and more. https://whatsapp.com/dl/code=1GcQsMEWJJ?mode=c</t>
+          <t>Ok ...Jaga diri molek ..jgn susoh² Hati... ada masa Kita lepak skali</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C60" t="n">
-        <v>0.9373519923068176</v>
+        <v>0.6720697488386759</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>kurg jls</t>
+          <t>Amoi sini company goldenbet99,apa kabar sudah bossku,lama dah tak try spin mari.jackpot,free game,Bonusgame menanti anda. Web ; goldenbet99 .com</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C61" t="n">
-        <v>0.9388732834522266</v>
+        <v>0.5124115143220297</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>IMEI2 F98370B68A357EECAA0E5EDD3260FD6292738820258B5151A42CA7AF632F85421BD552939C1BF8668CC44FBB22104375342352351968185091C399F2EFC2D48D</t>
+          <t>Bos ni nmor Wasap saye 01116514506 ni saye budak Indonesia</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C62" t="n">
-        <v>0.8614595036442385</v>
+        <v>0.656510392228829</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Chat with me on WhatsApp! It lets us message privately and share photos, videos and more. https://whatsapp.com/dl/code=1GcQsMEWJJ?mode=c</t>
+          <t>Jom cuba aplikasi WhatsApp Business, saya menggunakannya untuk berhubung dengan pelanggan saya. Dapatkannya secara percuma di https://whatsapp.com/biz/</t>
         </is>
       </c>
       <c r="B63" t="n">
         <v>1</v>
       </c>
       <c r="C63" t="n">
-        <v>0.9373519923068176</v>
+        <v>0.7957651410500876</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Aboi servis ranger. Tukar paip oil coler . Pak lang dan pon pasang i jem no 11. Udin setel bekho</t>
+          <t>Amoi sini company goldenbet99,apa kabar sudah bossku,lama dah tak try spin mari.jackpot,free game,Bonusgame menanti anda. Web ; goldenbet99 .com</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C64" t="n">
-        <v>0.7671775751273691</v>
+        <v>0.5124115143220297</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Pls bagi Mak fon kejap boleh....nanti Miss call...sy call balik..tq</t>
+          <t>sy ta slh kan awk klau awk na benci sy . tak nak contact sy da lepas ni. da sy mintak maaf klau hadir sy dlm idup awk, buat idup awk beban. insAllah. sy ada rezeki lepas ni. sy ta janji , tpi sy cuba tolong bayar balik duit2 yg awk keluar utk sy dgn ank. spnjg awk dgn sy.</t>
         </is>
       </c>
       <c r="B65" t="n">
         <v>0</v>
       </c>
       <c r="C65" t="n">
-        <v>0.8617121571911119</v>
+        <v>0.5249406900007852</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>The answer selected is B xqjFJhk</t>
+          <t>Amoi sini company goldenbet99,apa kabar sudah bossku,lama dah tak try spin mari.jackpot,free game,Bonusgame menanti anda. Web ; goldenbet99 .com</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C66" t="n">
-        <v>0.8760880386605798</v>
+        <v>0.5561876463185136</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Let's chat on WhatsApp! It's a fast, simple, and secure app we can use to message and call each other for free. Get it at https://whatsapp.com/dl/</t>
+          <t>Ok ...Jaga diri molek ..jgn susoh² Hati... ada masa Kita lepak skali</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C67" t="n">
-        <v>0.8507161268238027</v>
+        <v>0.6249765289534743</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Your Credit Has Been Added By 0177173373. Total Added:RM 500. Your New Balance:RM545.1778</t>
+          <t>Ok ...Jaga diri molek ..jgn susoh² Hati... ada masa Kita lepak skali</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C68" t="n">
-        <v>0.907321978891685</v>
+        <v>0.6249760223139937</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Mari bersembang di WhatsApp! Ia cepat, mudah dan selamat untuk membuat panggilan dan menghantar mesej secara percuma. Dapatkannya di https://whatsapp.com/dl/code=gvyuXASOf9?mode=tac</t>
+          <t>https://youtube.com/shorts/fuqANpZirh8?si=iQQrb0BO1qZukNSX</t>
         </is>
       </c>
       <c r="B69" t="n">
         <v>1</v>
       </c>
       <c r="C69" t="n">
-        <v>0.8326817923217034</v>
+        <v>0.672743992734987</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>FMCS SMS System Healthy</t>
+          <t>HAPPY BIRTHDAY UNGKU SEMOGA PNJG UMUR SORRY AKU TK JOIN TADi</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C70" t="n">
-        <v>0.7875759089024956</v>
+        <v>0.7055777477513139</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>(BOLA) B16/06/99 00:00:58 401#22692 *BS4AAC 1*1 16/06 GE 4732 B5 9658 B5 7472 B5 2161 B5 box(9979) B5 T = 80 NT = 80 21,9642916 P456 Points:0086 6429 1648 7983 16/06 GD JP:H DRG JP 6+1D 16/06 5201611...5201613 NINE JP 6+1D 16/06 1358100 2039080 8902843 0205169 9622293 2434204 5741143 6430541</t>
+          <t>https://youtube.com/shorts/fuqANpZirh8?si=iQQrb0BO1qZukNSX</t>
         </is>
       </c>
       <c r="B71" t="n">
         <v>1</v>
       </c>
       <c r="C71" t="n">
-        <v>0.7849255225979862</v>
+        <v>0.672743992734987</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Empangan Batu - ID:WPKL1001RF 2025-06-16 00:00:53 RF Light Rain PassHour:1mm</t>
+          <t>https://youtube.com/shorts/fuqANpZirh8?si=iQQrb0BO1qZukNSX</t>
         </is>
       </c>
       <c r="B72" t="n">
         <v>1</v>
       </c>
       <c r="C72" t="n">
-        <v>0.7319263342656327</v>
+        <v>0.672743992734987</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Let's video chat and text on imo! Get the free app https://imo.onelink.me/7QOl/ics</t>
+          <t>Hampir 3 bln mas buat aku mcm ni</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C73" t="n">
-        <v>0.8563620339348258</v>
+        <v>0.8973616195429976</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Let's video chat and text on imo! Get the free app https://imo.onelink.me/7QOl/ics</t>
+          <t>https://youtube.com/shorts/fuqANpZirh8?si=iQQrb0BO1qZukNSX</t>
         </is>
       </c>
       <c r="B74" t="n">
         <v>1</v>
       </c>
       <c r="C74" t="n">
-        <v>0.8563618579730975</v>
+        <v>0.672743992734987</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Sedih sye bila tengok awak senang2 je dh syg org lain.. Sbb sye dh takde apa.. Awak lgsg tak pandang segala pengorbanan sye kat awak.. Hati nie jadi kecik tp apa kan daya.. Sye dh jatuh teruk.. Dh tak mampu jge awak dan anak2..</t>
+          <t>https://youtube.com/shorts/fuqANpZirh8?si=iQQrb0BO1qZukNSX</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C75" t="n">
-        <v>0.9176858023410275</v>
+        <v>0.672743992734987</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>WALTON 357715821933753 Olvio L30</t>
+          <t>https://youtube.com/shorts/fuqANpZirh8?si=iQQrb0BO1qZukNSX</t>
         </is>
       </c>
       <c r="B76" t="n">
         <v>1</v>
       </c>
       <c r="C76" t="n">
-        <v>0.8718340520671263</v>
+        <v>0.672743992734987</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>&lt;EMO&gt;</t>
+          <t>Salam sayang aku ni mcm mana c nana ada kurang sudah</t>
         </is>
       </c>
       <c r="B77" t="n">
         <v>0</v>
       </c>
       <c r="C77" t="n">
-        <v>0.949186252233548</v>
+        <v>0.6113076639880355</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>You Have 2 Missed Call(2) J..K8 Fr66 Rm.10 R3d pa0 j01n N0w!Dapatkan RM 10 j8k.jb5.mx To opt out, Reply STOP. rojgsywe;</t>
+          <t>Salam sayang aku ni mcm mana c nana ada kurang sudah</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C78" t="n">
-        <v>0.9464930535514431</v>
+        <v>0.6113076639880355</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Ada kes oncall di green zone.pt nama nusaibah 6 tahun.laceration kt lower lip</t>
+          <t>Jangan rosakkan diri . bukan tkdk jalan lain adaa . laniee kita perlukan masaa , syg sentiasa doaakan yg terbaik utk biy . syg maafkn segalaa salah silap biy . syg tkpenah pendam sikit pon . syg cumaa nk yg trbaik jaa utk biy</t>
         </is>
       </c>
       <c r="B79" t="n">
         <v>1</v>
       </c>
       <c r="C79" t="n">
-        <v>0.5510136045364379</v>
+        <v>0.7081667947064225</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Asalam ayah ayah tengah buat apa tu adik nak tido ni selamat malam ayah bai asalamualaikum ayah</t>
+          <t>Ok ...Jaga diri molek ..jgn susoh² Hati... ada masa Kita lepak skali</t>
         </is>
       </c>
       <c r="B80" t="n">
         <v>0</v>
       </c>
       <c r="C80" t="n">
-        <v>0.922130735457332</v>
+        <v>0.6249765289534743</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Let's chat on WhatsApp! It's a fast, simple, and secure app we can use to message and call each other for free. Get it at https://whatsapp.com/dl/</t>
+          <t>Bos ni nmor Wasap saye 01116514506 ni saye budak Indonesia</t>
         </is>
       </c>
       <c r="B81" t="n">
         <v>1</v>
       </c>
       <c r="C81" t="n">
-        <v>0.8507161268238027</v>
+        <v>0.6931705641041581</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Chat with me on WhatsApp! It lets us message privately and share photos, videos and more. https://whatsapp.com/dl/code=rdau1KsWBU?mode=c</t>
+          <t>Amoi sini company goldenbet99,apa kabar sudah bossku,lama dah tak try spin mari.jackpot,free game,Bonusgame menanti anda. Web ; goldenbet99 .com</t>
         </is>
       </c>
       <c r="B82" t="n">
         <v>1</v>
       </c>
       <c r="C82" t="n">
-        <v>0.9344380405789388</v>
+        <v>0.5561876463185136</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Let's video chat and text on imo! Get the free app https://imo.onelink.me/7QOl/ics</t>
+          <t>Bgsa ktrunan sawan gila bbi mmg mcm to lh prgai bbto hdop pun sial ape xde ape lgi duit ..hdop mnpu mcm to lh ..hdop pun x berkat mcm to lh</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C83" t="n">
-        <v>0.8563620339348258</v>
+        <v>0.6217015219439681</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>canver balls</t>
+          <t>上 WhatsApp 对话!使用此快速、简便且安全的应用免费发消息和进行通话。下载:https://whatsapp.com/dl/</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C84" t="n">
-        <v>0.9258582403658059</v>
+        <v>0.8773306774388139</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>742</t>
+          <t>KakaoTalk HgAAABIwALXuTmgAAAAAAjEABwAAADMzMTg4NQAA</t>
         </is>
       </c>
       <c r="B85" t="n">
         <v>0</v>
       </c>
       <c r="C85" t="n">
-        <v>0.7045107328060626</v>
+        <v>0.7582788301219161</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Biesayang baru balik nie&lt;EMO&gt;&lt;EMO&gt;</t>
+          <t>tirak please call me back ok</t>
         </is>
       </c>
       <c r="B86" t="n">
         <v>0</v>
       </c>
       <c r="C86" t="n">
-        <v>0.9455852431454016</v>
+        <v>0.7734016013850387</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Call Sy balik sekrang urgent .Kang lambat Sy keje dalam kedai ni lame dahm.sy nk g ATM jauh .Kang sekali jalan g keje Sy kuar n bank in rehat</t>
+          <t>1166 ABAwdEyBez</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C87" t="n">
-        <v>0.9352919804969141</v>
+        <v>0.6755719351063554</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Your Credit Has Been Added By 0177173373. Total Added:RM 500. Your New Balance:RM545.1778</t>
+          <t>Credit percuma tunggu anda mari claim, PM Jana skrg! WS: 01 137623420</t>
         </is>
       </c>
       <c r="B88" t="n">
         <v>1</v>
       </c>
       <c r="C88" t="n">
-        <v>0.907321978891685</v>
+        <v>0.5289785432110612</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>25O616 OOOO (1) kcc419 16/O6 *H 2O28=4B 5646=4B 2OO7=4B 5278=4B 59O7=4B O5O2=4B 53O7=4B *E 2O28=2B 5646=2B 2OO7=2B 5278=2B 59O7=2B O5O2=2B 53O7=2B GT=42 O19398798O DRG JP 6+1D 16Jun 4951613 4962279 16Jun JP:H Points:OO13 5113 5196 7O18 NINE 6+1D 16Jun 1566163 393485O</t>
+          <t>Ok ...Jaga diri molek ..jgn susoh² Hati... ada masa Kita lepak skali</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C89" t="n">
-        <v>0.8753200294913798</v>
+        <v>0.6249760223139937</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>AC/02b00ba873f610911fd8c8f6281b8418:684eec8ec921208e/8:This SMS is used to activate your Mi service</t>
+          <t>Ok ...Jaga diri molek ..jgn susoh² Hati... ada masa Kita lepak skali</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C90" t="n">
-        <v>0.848468598164379</v>
+        <v>0.6249760223139937</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Let's video chat and text on imo! Get the free app https://n7265.app.goo.gl/pGuk#-0-1</t>
+          <t>BX99:您被选了(ycchong)!恭喜您获得228次免费旋转。存RM50就解锁!bx99my{dot}com</t>
         </is>
       </c>
       <c r="B91" t="n">
         <v>1</v>
       </c>
       <c r="C91" t="n">
-        <v>0.9203522203735527</v>
+        <v>0.5127223896275346</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Let's video chat and text on imo! Get the free app https://n7265.app.goo.gl/pGuk#-0-1</t>
+          <t>Dear tenant, please fill up tenant background. I will check with owner and looking unit for you&lt;EMO&gt; Name : Ajit Budget : as low as possible when move in : 1july How many ppl stay : 8 Nepal friend or family : workers Occupation : security Working company name/ school name : security company Local / Foreigner : Race : nepal Tenancy 1 or 2 years : 2</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C92" t="n">
-        <v>0.9203522203735527</v>
+        <v>0.5273876023997481</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>အရမ်းချစ်တယ် မိန်းမရေ လွမ်းလှပီ အလုပ်က မနက်ဆင်းမလို့ အိပ်ပီ</t>
+          <t>Ok ...Jaga diri molek ..jgn susoh² Hati... ada masa Kita lepak skali</t>
         </is>
       </c>
       <c r="B93" t="n">
         <v>0</v>
       </c>
       <c r="C93" t="n">
-        <v>0.9207800994632201</v>
+        <v>0.6249765289534743</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>1763, Jalan Jambu 24 81400 Senai 柔佛州 马来西亚</t>
+          <t>https://images.app.goo.gl/tAviyQQ2vsZb75Qw8</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C94" t="n">
-        <v>0.7331899363709833</v>
+        <v>0.5719411206950362</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Mudah: I'm interested in your ad on Mudah Flat Pandan Mewah, please share more details with me.</t>
+          <t>https://maps.apple.com/?ll=1.32480,103.91279&amp;q=Location</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C95" t="n">
-        <v>0.5565510044379487</v>
+        <v>0.5955420302639787</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Ayo chat di WhatsApp, aplikasi yang cepat, sederhana, dan aman untuk berkirim pesan dan menelepon secara gratis. Dapatkan di https://whatsapp.com/dl/</t>
+          <t>Ok ...Jaga diri molek ..jgn susoh² Hati... ada masa Kita lepak skali</t>
         </is>
       </c>
       <c r="B96" t="n">
         <v>0</v>
       </c>
       <c r="C96" t="n">
-        <v>0.5027159973659833</v>
+        <v>0.6249765289534743</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Ayo chat di WhatsApp, aplikasi yang cepat, sederhana, dan aman untuk berkirim pesan dan menelepon secara gratis. Dapatkan di https://whatsapp.com/dl/</t>
+          <t>Ok ...Jaga diri molek ..jgn susoh² Hati... ada masa Kita lepak skali</t>
         </is>
       </c>
       <c r="B97" t="n">
         <v>0</v>
       </c>
       <c r="C97" t="n">
-        <v>0.5027159973659833</v>
+        <v>0.6249760223139937</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Ayo chat di WhatsApp, aplikasi yang cepat, sederhana, dan aman untuk berkirim pesan dan menelepon secara gratis. Dapatkan di https://whatsapp.com/dl/</t>
+          <t>inimuhammat01116384619muhammat semau orang mari tolong mari inidurga hari hari tujihbuli maruthai semau orang mari tolong mari tolong</t>
         </is>
       </c>
       <c r="B98" t="n">
         <v>0</v>
       </c>
       <c r="C98" t="n">
-        <v>0.5027159973659833</v>
+        <v>0.8997632373841769</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>sikmok2</t>
+          <t>Amoi sini company goldenbet99,apa kabar sudah bossku,lama dah tak try spin mari.jackpot,free game,Bonusgame menanti anda. Web ; goldenbet99 .com</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C99" t="n">
-        <v>0.7191816445905086</v>
+        <v>0.5945115427700514</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>JAZ9(1) 2025-06-16.00:01 18~21~22 P * 6932 S5.5 T(16.5)</t>
+          <t>(522003) LGzwYKxLMG</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C100" t="n">
-        <v>0.8879917960350249</v>
+        <v>0.6366351504596239</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Mari bersembang di WhatsApp! Ia cepat, mudah dan selamat untuk membuat panggilan dan menghantar mesej secara percuma. Dapatkannya di https://whatsapp.com/dl/code=gvyuXASOf9?mode=tac</t>
+          <t>Mamaa bsk tlng sa bgi rm54 sma jnt HAHA taadi sa kna bgi duit orngg. Bkn sa pnya. Nnti hri mnggu sa bgi mama tu duit, bsk mama byr ja</t>
         </is>
       </c>
       <c r="B101" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C101" t="n">
-        <v>0.8326817923217034</v>
+        <v>0.8670931269200808</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Temn bb tido</t>
+          <t>inimuhammat01116384619muhammat semau orang mari tolong mari inidurga hari hari tujihbuli maruthai semau orang mari tolong mari tolong</t>
         </is>
       </c>
       <c r="B102" t="n">
         <v>0</v>
       </c>
       <c r="C102" t="n">
-        <v>0.9155834346805032</v>
+        <v>0.8997632373841769</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Please unblock whatsapp ktk. Makan duit pake sms tok by</t>
+          <t>Ok ...Jaga diri molek ..jgn susoh² Hati... ada masa Kita lepak skali</t>
         </is>
       </c>
       <c r="B103" t="n">
         <v>0</v>
       </c>
       <c r="C103" t="n">
-        <v>0.8676687289949462</v>
+        <v>0.6237796206744677</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Temn bb tido</t>
+          <t>1367800000764</t>
         </is>
       </c>
       <c r="B104" t="n">
         <v>0</v>
       </c>
       <c r="C104" t="n">
-        <v>0.9155834346805032</v>
+        <v>0.690739359405852</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Your Credit Has Been Added By 0177173373. Total Added:RM 500. Your New Balance:RM545.1778</t>
+          <t>Mcm mna mo ubah blikk p imessge ni cinta</t>
         </is>
       </c>
       <c r="B105" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C105" t="n">
-        <v>0.907321978891685</v>
+        <v>0.8061758835586077</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Let's chat on WhatsApp! It's a fast, simple, and secure app we can use to message and call each other for free. Get it at https://whatsapp.com/dl/</t>
+          <t>BX99: (ID: ryan678) Congrats, you are one of todays lucky picks. Deposit RM50 to get 228 FREE Spins. Dont miss out! bx99my{dot}com</t>
         </is>
       </c>
       <c r="B106" t="n">
         <v>1</v>
       </c>
       <c r="C106" t="n">
-        <v>0.8507161268238027</v>
+        <v>0.8702712993351454</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>&lt;EMO&gt;&lt;EMO&gt;&lt;EMO&gt;</t>
+          <t>Amoi sini company goldenbet99,apa kabar sudah bossku,lama dah tak try spin mari.jackpot,free game,Bonusgame menanti anda. Web ; goldenbet99 .com</t>
         </is>
       </c>
       <c r="B107" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C107" t="n">
-        <v>0.8822370035393468</v>
+        <v>0.5945115427700514</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Salam din poksu ni fon su skrin pecah.ni pakai fon nek.su dokleh wsp mtk tlg epi din anto buleh su ada 25,cash.su kije dgn edemi anto budok sek skrg.tlg din</t>
+          <t>Bkt.Berlian Res R 24,0 20:26 unet 23.239.111.108 352134012067105 0508 0 1 3 12 62 17600 17600 0.00OK In1=1 In2=0 In3=0</t>
         </is>
       </c>
       <c r="B108" t="n">
         <v>0</v>
       </c>
       <c r="C108" t="n">
-        <v>0.911278071748534</v>
+        <v>0.628415550735808</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Takpelah. Saya tau dah ada yg temankan awak sleepcall that's why taknak dgr suda suara perempuan yg gaya mcm sial babi ni. Takpelah, sorry ganggu awak dgn c dia. Okaylah, thanks sebab sudi dgrkan suara awak utk kali yg terakhir. Okaylah saya akan menjauh dan undur diri duluan</t>
+          <t>Boleh dapatkan maklumat mengenaie diri anda terima kasih</t>
         </is>
       </c>
       <c r="B109" t="n">
         <v>0</v>
       </c>
       <c r="C109" t="n">
-        <v>0.7326597078785648</v>
+        <v>0.8164299984248644</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>HHGG ~ 07 Hi , Hari ini ada Rebate Untuk Try , Sila Wsp : 01 46 07 0145 G1030</t>
+          <t>KakaoTalk HgAAABIwAP7uTmgAAAAAAjEABwAAADcxOTE5MwAA</t>
         </is>
       </c>
       <c r="B110" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C110" t="n">
-        <v>0.9391256871237472</v>
+        <v>0.6223733384879595</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>SMS From LUCAS Agent H-H-G-G- 322 N3w BOn0s Sl0T --Giff Vocher-- Whatsapp = O 1 7 7 0 7 5 4 7 8</t>
+          <t>BX99:您被选了(jcvoon88)!恭喜您获得228次免费旋转。存RM50就解锁!bx99my{dot}com</t>
         </is>
       </c>
       <c r="B111" t="n">
         <v>1</v>
       </c>
       <c r="C111" t="n">
-        <v>0.939971528234109</v>
+        <v>0.7585540752140516</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Salam din poksu ni fon su skrin pecah.ni pakai fon nek.su dokleh wsp mtk tlg epi din anto buleh su ada 25,cash.su kije dgn edemi anto budok sek skrg.tlg din</t>
+          <t>KakaoTalk HgAAABIwAP7uTmgAAAAAAjEABwAAADcxOTE5MwAA</t>
         </is>
       </c>
       <c r="B112" t="n">
         <v>0</v>
       </c>
       <c r="C112" t="n">
-        <v>0.911278071748534</v>
+        <v>0.6223733384879595</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Please syg abg merayu please unblock abg</t>
+          <t>https://i.lf360.co/BatterySaver</t>
         </is>
       </c>
       <c r="B113" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C113" t="n">
-        <v>0.8226494971430671</v>
+        <v>0.5968180637089247</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Let's video chat and text on imo! Get the free app https://imo.onelink.me/7QOl/ics</t>
+          <t>https://i.lf360.co/BatterySaver</t>
         </is>
       </c>
       <c r="B114" t="n">
         <v>1</v>
       </c>
       <c r="C114" t="n">
-        <v>0.8563620339348258</v>
+        <v>0.5968180637089247</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>E T: Wlcm u, MAX-M u=1441627946Q6 p=EEee7673 on:16/06 00:01:29</t>
+          <t>https://i.lf360.co/BatterySaver</t>
         </is>
       </c>
       <c r="B115" t="n">
         <v>1</v>
       </c>
       <c r="C115" t="n">
-        <v>0.9048540762090302</v>
+        <v>0.5968180637089247</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>x buke block tpun x .abg bt nk main gile sngt .mg bt sloh aku plok mg mrh.</t>
+          <t>https://i.lf360.co/BatterySaver</t>
         </is>
       </c>
       <c r="B116" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C116" t="n">
-        <v>0.9411682579527126</v>
+        <v>0.5968180637089247</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Halo</t>
+          <t>Ok ...Jaga diri molek ..jgn susoh² Hati... ada masa Kita lepak skali</t>
         </is>
       </c>
       <c r="B117" t="n">
         <v>0</v>
       </c>
       <c r="C117" t="n">
-        <v>0.9389865275611721</v>
+        <v>0.6237796206744677</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Let's chat on WhatsApp! It's a fast, simple, and secure app we can use to message and call each other for free. Get it at https://whatsapp.com/dl/code=ky7rFmkYNP</t>
+          <t>Salam love. Mek dh blt ke bilit. Kmk dh cuci mka n kaki. Kepak gilak kmk. Esok pg jak kmk iron baju. Doakan kmk sentiasa dimudahkan class &amp; exam. Supaya kmk berlapang dada &amp; masik ilmu. Love u n miss u</t>
         </is>
       </c>
       <c r="B118" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C118" t="n">
-        <v>0.8938881555772697</v>
+        <v>0.5431432385715014</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>FMCS SMS System Healthy</t>
+          <t>Ok ...Jaga diri molek ..jgn susoh² Hati... ada masa Kita lepak skali</t>
         </is>
       </c>
       <c r="B119" t="n">
         <v>0</v>
       </c>
       <c r="C119" t="n">
-        <v>0.7875759089024956</v>
+        <v>0.6237796206744677</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Abg tetap ap abg</t>
+          <t>Credit percuma tunggu anda mari claim, PM Jana skrg! WS: 01 137623420</t>
         </is>
       </c>
       <c r="B120" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C120" t="n">
-        <v>0.9363091850823804</v>
+        <v>0.5652156810490125</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>92873087-Sungai Pertama: 2025-06-16 00:01:00 Gate 2 Fully Closed</t>
+          <t>Mai lah sni gilak</t>
         </is>
       </c>
       <c r="B121" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C121" t="n">
-        <v>0.8958870253151325</v>
+        <v>0.7512793798717028</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Selamat</t>
+          <t>https://i.lf360.co/BatterySaver</t>
         </is>
       </c>
       <c r="B122" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C122" t="n">
-        <v>0.8882998605060803</v>
+        <v>0.5968180637089247</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Dear Blood Donor, Greetings from BCCM Tuaran Parish . Please to inform you that our next blood donation campaign will be held on 22nd June 2025 (Sunday) at 1st Floor City Mall from 10am to 5pm. Your participation would be highly appreciated. Tq</t>
+          <t>https://maps.apple.com/?ll=1.32006,103.84447&amp;q=Location</t>
         </is>
       </c>
       <c r="B123" t="n">
         <v>1</v>
       </c>
       <c r="C123" t="n">
-        <v>0.8160476998315082</v>
+        <v>0.6185624341694349</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>IMEI2 49EECE0505EE2643FC28A1D9493824B3D8F83187F63B2F42286709974E791CC68F8CB7006AC11239F3F380A268D50B427AE7A7E463B97B93B43DF2E22F76C568</t>
+          <t>QR0853</t>
         </is>
       </c>
       <c r="B124" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C124" t="n">
-        <v>0.8201510934148853</v>
+        <v>0.7988537292210096</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>92873087-Sungai Pertama: 2025-06-16 00:01:00 Gate 2 Fully Closed</t>
+          <t>https://i.lf360.co/BatterySaver</t>
         </is>
       </c>
       <c r="B125" t="n">
         <v>1</v>
       </c>
       <c r="C125" t="n">
-        <v>0.8958870253151325</v>
+        <v>0.5968180637089247</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>H H G G 337 Call From Atlas N3w BOn0s Sl0T --Fr3xx Voucher-- note: C1imm Juni Wsp: 60_17_7078_902 Wsp: 60_17_7075_004</t>
+          <t>25O616 OOO4 (1) bft1511 18/O6 *MPT 37O9=2B GT=6 TT=6 O16232711O</t>
         </is>
       </c>
       <c r="B126" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C126" t="n">
-        <v>0.7877251834588351</v>
+        <v>0.5490984578403002</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Insyaallah ade rezeki lebih Biesayang topup sayangbie&lt;EMO&gt;&lt;EMO&gt;&lt;EMO&gt;</t>
+          <t>Alarm cancelled S/ROOM BURGOGUAD Area 1 16 Jun 0h05</t>
         </is>
       </c>
       <c r="B127" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C127" t="n">
-        <v>0.8594114312143932</v>
+        <v>0.785057280513429</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Bendar mangkang keting mangkang butuh pukik dia.. Nya line ndai nemu clear</t>
+          <t>ကြားရတဲ့သတင်းတွေမကောင်းလို့ အားလုံးကိုစိတ်ပူလို့ ဖုန်းဆက်မိတာပါ စိတ်မကောင်းဘူးပဲ ဒါနောက်ဆုံးပဲ ဖြစ်မှာပါ နှုတ်ဆက်ပါတယ် good bye</t>
         </is>
       </c>
       <c r="B128" t="n">
         <v>0</v>
       </c>
       <c r="C128" t="n">
-        <v>0.6662555769460068</v>
+        <v>0.8044974167617327</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Activation code: 052340</t>
+          <t>lepas tu ws ckp apa? blk terus nk kemas² n tdo... apa maksudnya tu?</t>
         </is>
       </c>
       <c r="B129" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C129" t="n">
-        <v>0.8716536392090156</v>
+        <v>0.8942250867160326</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Mari bersembang di WhatsApp! Ia cepat, mudah dan selamat untuk membuat panggilan dan menghantar mesej secara percuma. Dapatkannya di https://whatsapp.com/dl/code=oA9yVDckSv?mode=c</t>
+          <t>KakaoTalk HgAAABIwAP7uTmgAAAAAAjEABwAAADcxOTE5MwAA</t>
         </is>
       </c>
       <c r="B130" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C130" t="n">
-        <v>0.8370640531858412</v>
+        <v>0.6223733384879595</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>আসুন imo-তে ভিডিও চ্যাট ও টেক্সট করি! বিনামূল্যের অ্যাপটা নিয়ে নিন https://imo.onelink.me/7QOl/ics</t>
+          <t>Ok ...Jaga diri molek ..jgn susoh² Hati... ada masa Kita lepak skali</t>
         </is>
       </c>
       <c r="B131" t="n">
         <v>0</v>
       </c>
       <c r="C131" t="n">
-        <v>0.7515127581911518</v>
+        <v>0.6237796206744677</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>(BOLA) B16/06/99 00:01:23 401#22693 *BS4AAC 1*2 16/06 GE 3447 B5-S0-4A2 T = 14 NT = 14 21,9642920 P456 Points:0086 6429 2041 0230 16/06 GD JP:H NINE JP6+1D 16/06 0498111</t>
+          <t>Cik jamal tk berhenti nurse ni call msej sy cik jamal tlglah cik jamal</t>
         </is>
       </c>
       <c r="B132" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C132" t="n">
-        <v>0.8309686016854135</v>
+        <v>0.873144771602965</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>25O616 OOO1 (1) y3O32 18/O6-21/O6-22/O6 *S (2626)=33B 22S 18/O6 S 2626=3OB(LM) 21/O6 S 2626=3OB(LM) 22/O6 S 2626=3OB(LM) (6262)=33B 22S 18/O6 S 6262=3OB(LM) 21/O6 S 6262=3OB(LM) 22/O6 S 6262=3OB(LM) 67OO=33B 22S OO76=33B 22S GT=642 Q1226267QQ</t>
+          <t>12.45 ambik barang kat luar rumah, jangan tak angkat orang call.</t>
         </is>
       </c>
       <c r="B133" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C133" t="n">
-        <v>0.7425485681370827</v>
+        <v>0.839036728885985</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>tirak please me back ok</t>
+          <t>QR0021</t>
         </is>
       </c>
       <c r="B134" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C134" t="n">
-        <v>0.7348829233715034</v>
+        <v>0.6820978264538282</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>854461697560978</t>
+          <t>SYS ARM; END</t>
         </is>
       </c>
       <c r="B135" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C135" t="n">
-        <v>0.9383058469415463</v>
+        <v>0.8767188300164706</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>25O616 OOO1 (1) skccOO1 18/O6-21/O6-22/O6 *MPT 5129=3B 2S 9215=3B 9215=3B (IBox) 58O8=2B 58O8=2B (IBox) 7822=2B 7822=2B (IBox) GT=171 O1934O2O17</t>
+          <t>F re3 Cr3dlt M€ g@/K1 §§/P u§§ y Was@p - 01_46139668 0ng m@li Gfhjjjkgf</t>
         </is>
       </c>
       <c r="B136" t="n">
         <v>1</v>
       </c>
       <c r="C136" t="n">
-        <v>0.7713657962793843</v>
+        <v>0.7888670901981825</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Bang net ada kredit share topup RM 10 tak untuk digi nombor ni..data abg dah tamat tempoh ni</t>
+          <t>Aku mau yo omong" an karo mbkq yo tak kon glk inpo lemah seng di dol ngono koyok e enek kidol mahku tpi jare mbkq larang Terus aku di takoni la w takok" opo ndwe duek ngono yo tak sauri urung tpi ge pandangan lah ge semangat nek kerjo.. Bukane aku mikir sman matre ora blass yng syngg aku mau arep omong ngonokui me sman tpi sman kesusu mikir lek aku ngono hoalah yng" sepurane tpi yngg yo gae sman nesu tulung di ngerteni aku yng yoo mosok modele koyo aku ndwe pikiran lek sman matre jan" adoh soko jangkauan</t>
         </is>
       </c>
       <c r="B137" t="n">
         <v>0</v>
       </c>
       <c r="C137" t="n">
-        <v>0.5547333271257828</v>
+        <v>0.7642330785068041</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Temn bb tido</t>
+          <t>wlaupn ak prnah mncuba utk brubah dan ak cuba mnjd trbaik utk kau, ak brharap kau nmpak, tp sgalanya mcm sia2 tp gpp ak kn ga ada hati bg kau, tp apa pn kau trsgt2 laa baik spnjg 3tahun kita kwn ni, ak xnafikn kau byk sgt2 buat sgala mcm utk ak. ak sygkn sbnarnya lbih dr siapa pn. mskipn xbrsama lg, ak rasa dh masanya utk ak brubah. ak xmau lg sama siapa pn. ckup laa kau trakhir kali ni. mngkin bg kau kata2 ak cuma ksong, tp ak akn buktikn.</t>
         </is>
       </c>
       <c r="B138" t="n">
         <v>0</v>
       </c>
       <c r="C138" t="n">
-        <v>0.9155834346805032</v>
+        <v>0.7393104393752581</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Satu ja pesan ku jaga diri baik baik</t>
+          <t>Her mobile 012 2418877</t>
         </is>
       </c>
       <c r="B139" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C139" t="n">
-        <v>0.9058347523919095</v>
+        <v>0.8404573617596763</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>780f04ee9776b8f7dog_</t>
+          <t>https://maps.apple.com/?ll=1.62042,103.72699&amp;q=Location</t>
         </is>
       </c>
       <c r="B140" t="n">
         <v>1</v>
       </c>
       <c r="C140" t="n">
-        <v>0.8950482577058277</v>
+        <v>0.5411547241826195</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>晚安,亲爱的老婆&lt;EMO&gt;&lt;EMO&gt;&lt;EMO&gt;&lt;EMO&gt;</t>
+          <t>SIGOS SMS test</t>
         </is>
       </c>
       <c r="B141" t="n">
         <v>0</v>
       </c>
       <c r="C141" t="n">
-        <v>0.7686945003496951</v>
+        <v>0.516990441260801</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>(T)=1342.00 =96.00 (T)=1438.00 15/06-400.00 (T)=1038.00 老板娘 16/06/25</t>
+          <t>https://maps.apple.com/?ll=1.62042,103.72699&amp;q=Location</t>
         </is>
       </c>
       <c r="B142" t="n">
         <v>1</v>
       </c>
       <c r="C142" t="n">
-        <v>0.8990918482331496</v>
+        <v>0.5411547241826195</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Mari bersembang di WhatsApp! Ia cepat, mudah dan selamat untuk membuat panggilan dan menghantar mesej secara percuma. Dapatkannya di https://whatsapp.com/dl/code=v1eRxmmrMs?mode=tac</t>
+          <t>https://maps.apple.com/?ll=1.62042,103.72699&amp;q=Location</t>
         </is>
       </c>
       <c r="B143" t="n">
         <v>1</v>
       </c>
       <c r="C143" t="n">
-        <v>0.8416279136420556</v>
+        <v>0.5411547241826195</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Chat with me on WhatsApp! It lets us message privately and share photos, videos and more. https://whatsapp.com/dl/code=wEI49xspJf?mode=tac</t>
+          <t>https://maps.apple.com/?ll=1.62042,103.72699&amp;q=Location</t>
         </is>
       </c>
       <c r="B144" t="n">
         <v>1</v>
       </c>
       <c r="C144" t="n">
-        <v>0.9344243676837851</v>
+        <v>0.5411547241826195</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Chat with me on WhatsApp! It lets us message privately and share photos, videos and more. https://whatsapp.com/dl/code=wEI49xspJf?mode=tac</t>
+          <t>https://maps.apple.com/?ll=1.62042,103.72699&amp;q=Location</t>
         </is>
       </c>
       <c r="B145" t="n">
         <v>1</v>
       </c>
       <c r="C145" t="n">
-        <v>0.9344243676837851</v>
+        <v>0.5411547241826195</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Mari bersembang di WhatsApp! Ia cepat, mudah dan selamat untuk membuat panggilan dan menghantar mesej secara percuma. Dapatkannya di https://whatsapp.com/dl/code=pHk4cEkwAG?mode=tac</t>
+          <t>夜 13-5 18-10 8-5 30-5 =25</t>
         </is>
       </c>
       <c r="B146" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C146" t="n">
-        <v>0.838850351175049</v>
+        <v>0.7489721955637795</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>MEGA GIVEAWAY TANPA DEPOSIT ! FREE KREDIT KHAS utk member terpilih sahaja. PM amoi kami Rebut skrg sebelum terlepas. Whatsapp : 45.77.242.198</t>
+          <t>https://maps.apple.com/?ll=1.62042,103.72699&amp;q=Location</t>
         </is>
       </c>
       <c r="B147" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C147" t="n">
-        <v>0.5820987600843022</v>
+        <v>0.5411547241826195</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>SIAL GAHAHAHA</t>
+          <t>Mamaa bsk tlng sa bgi rm54 sma jnt HAHA taadi sa kna bgi duit orngg. Bkn sa pnya. Nnti hri mnggu sa bgi mama tu duit, bsk mama byr ja</t>
         </is>
       </c>
       <c r="B148" t="n">
         <v>0</v>
       </c>
       <c r="C148" t="n">
-        <v>0.8733964569402712</v>
+        <v>0.8680508019308907</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>H H G G 337 Call From Atlas N3w BOn0s Sl0T --Fr3xx Voucher-- note: C1imm Juni Wsp: 60_17_7078_902 Wsp: 60_17_7075_004</t>
+          <t>lagi sekali , sy mintak maaf dari hujung rambut smpai hujung kaki.. salah silap sy spnjg dgn awk.. awk boleh buat keputusan utk tidak bersama sy atau masih na teruskan. sbb sy tak nak sampai bila2 gantung mcm ni. dengan takdek perbincangan . to je sy mintak . semua atas awk.</t>
         </is>
       </c>
       <c r="B149" t="n">
         <v>1</v>
       </c>
       <c r="C149" t="n">
-        <v>0.7877251834588351</v>
+        <v>0.7132228432316917</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Safety and health is very important so when you reach home (Penang) please kindly let me know as well as kejashini akka Please be safe and safely reach home ,Thiveya ji Wherever you go please be safe and careful always, stay safe always,Thiveya ji As well as health please take care of your health,Thiveya thangapulla &lt;EMO&gt;</t>
+          <t>Waalaikumsalam kwn man Ney tok.kmk mok tauk lebih benar.man Ney satu</t>
         </is>
       </c>
       <c r="B150" t="n">
         <v>0</v>
       </c>
       <c r="C150" t="n">
-        <v>0.6985541853571904</v>
+        <v>0.6455272616724831</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>243�SCC_AIR_SAT�SCC_AT_12012_18B_RH.HiHi�6/15/2025 10:45:25.220 AM�True�3F ASSEM</t>
+          <t>Mas lihat live aku sekrng mcm mna aku pkai</t>
         </is>
       </c>
       <c r="B151" t="n">
         <v>1</v>
       </c>
       <c r="C151" t="n">
-        <v>0.9028801452370788</v>
+        <v>0.7395773945469993</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>srs a phone kau halal</t>
+          <t>(11,14,15/6) 原本结存+1199 我的3期: -8 我尚结存=[ +1191 ]</t>
         </is>
       </c>
       <c r="B152" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C152" t="n">
-        <v>0.944737848287727</v>
+        <v>0.694049757542147</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>Dear Blood Donor, Greetings from BCCM Tuaran Parish . Please to inform you that our next blood donation campaign will be held on 22nd June 2025 (Sunday) at 1st Floor City Mall from 10am to 5pm. Your participation would be highly appreciated. Tq</t>
+          <t>https://maps.apple.com/?ll=1.62042,103.72699&amp;q=Location</t>
         </is>
       </c>
       <c r="B153" t="n">
         <v>1</v>
       </c>
       <c r="C153" t="n">
-        <v>0.8160476998315082</v>
+        <v>0.5411547241826195</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>IMEI2 74F2880055B253C0D7FCA093DBF6BCB1C34D8AECB6514A7DF2968CBADFBFCA2DB5BBA579F04801FA899F906345A4954DD1BE1F7A6C2AE6AE3C6151AD46BCA0AF</t>
+          <t>N sbb Tu kte still PGL awak biey</t>
         </is>
       </c>
       <c r="B154" t="n">
         <v>0</v>
       </c>
       <c r="C154" t="n">
-        <v>0.8343476244390138</v>
+        <v>0.7168410899023873</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>BALING, DAILY RF= 11.0mm, MONTHLY RF= 67.0mm, BATT = 13.3v 15062025,23:59</t>
+          <t>Demi Allah abg tak membenci syg ...setiap sholat abg doakan yg terbaik utk syg...semuga Selamat setiap perjalan syg peri Dan balik dri Terengganu</t>
         </is>
       </c>
       <c r="B155" t="n">
         <v>1</v>
       </c>
       <c r="C155" t="n">
-        <v>0.8210154788862221</v>
+        <v>0.6380566774029869</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>Amoi sini company goldenbet99,apa kabar sudah bossku,lama dah tak try spin mari.jackpot,free game,Bonusgame menanti anda. Web ; goldenbet99 .com</t>
+          <t>nawaitu ßyifa bibarakati mustofa sallahu alaihi wasalam. bca pd air minum</t>
         </is>
       </c>
       <c r="B156" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C156" t="n">
-        <v>0.592208612117288</v>
+        <v>0.7911794005055565</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>This number is using your phone</t>
+          <t>Bkt.Berlian Res R 24,0 20:26 unet 23.239.111.108 352134012067105 0508 0 1 3 12 62 17600 17600 0.00OK In1=1 In2=0 In3=0</t>
         </is>
       </c>
       <c r="B157" t="n">
         <v>0</v>
       </c>
       <c r="C157" t="n">
-        <v>0.8064370425454527</v>
+        <v>0.6183790149073464</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>Your Credit Has Been Added By 0177173373. Total Added:RM 500. Your New Balance:RM545.1778</t>
+          <t>To join the meeting on Google Meet, click this link: https://meet.google.com/gow-xyon-gdu Or open Meet and enter this code: gow-xyon-gdu</t>
         </is>
       </c>
       <c r="B158" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C158" t="n">
-        <v>0.907321978891685</v>
+        <v>0.5573364080767494</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>"JW8: Upgrade to JW8 VIP! Enjoy seamless transition and exclusive perks. Join now and elevate your VIP experience!" KSL44156</t>
+          <t>Aku cht ni sia2 je bkn no bce kn mmg kmu x nk bce baik aku pun smbg cll tiktok dgn owg lain sbb km7 pun dh x pduli aku kn baik aku smbg owg lain x la aku bosan kn</t>
         </is>
       </c>
       <c r="B159" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C159" t="n">
-        <v>0.9341094519470531</v>
+        <v>0.6379991056303841</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>JW8: Reminder! Your 30% deposit bonus is waiting! Join us now and supercharge your winnings! KSL42049</t>
+          <t>To join the meeting on Google Meet, click this link: https://meet.google.com/gow-xyon-gdu Or open Meet and enter this code: gow-xyon-gdu</t>
         </is>
       </c>
       <c r="B160" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C160" t="n">
-        <v>0.92362977227634</v>
+        <v>0.5573364080767494</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>油面-5包彡棵条-4包</t>
+          <t>i need to clarify things with you ... no wonder your wife going thru hell ippo thaan i knw ur real face</t>
         </is>
       </c>
       <c r="B161" t="n">
         <v>0</v>
       </c>
       <c r="C161" t="n">
-        <v>0.9389020180670167</v>
+        <v>0.8507960023264748</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>Wait pa just add me in whats app pa i will send u all the text 2u pa i see 1st what i said all pa nuu</t>
+          <t>Let's chat on WhatsApp! It's a fast, simple, and secure app we can use to message and call each other for free. Get it at https://whatsapp.com/dl/</t>
         </is>
       </c>
       <c r="B162" t="n">
         <v>1</v>
       </c>
       <c r="C162" t="n">
-        <v>0.6978359327691666</v>
+        <v>0.7937352476735252</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>Amoi sini company goldenbet99,apa kabar sudah bossku,lama dah tak try spin mari.jackpot,free game,Bonusgame menanti anda. Web ; goldenbet99 .com</t>
+          <t>Let's chat on WhatsApp! It's a fast, simple, and secure app we can use to message and call each other for free. Get it at https://whatsapp.com/dl/</t>
         </is>
       </c>
       <c r="B163" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C163" t="n">
-        <v>0.592208612117288</v>
+        <v>0.7937352476735252</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>HAHAHAH TGK" KITE PUN DH TIDO</t>
+          <t>Mas lihat live aku sekrng mcm mna aku pkai</t>
         </is>
       </c>
       <c r="B164" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C164" t="n">
-        <v>0.869382993062021</v>
+        <v>0.7395773945469993</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>帮助大体施棺 随缘</t>
+          <t>Bank loan (offer) - Rm10K - 400K / 5-10 yrs - Debt Consolidate - Hard to get Loan Approve? - Credit card limit burst? - CTOS/ Blacklist issue? No worried, WE CAN SETTLE YOUR PROBLEM REPLY YES for details</t>
         </is>
       </c>
       <c r="B165" t="n">
         <v>0</v>
       </c>
       <c r="C165" t="n">
-        <v>0.8564577201260828</v>
+        <v>0.5991671265940529</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>Dear Blood Donor, Greetings from BCCM Tuaran Parish . Please to inform you that our next blood donation campaign will be held on 22nd June 2025 (Sunday) at 1st Floor City Mall from 10am to 5pm. Your participation would be highly appreciated. Tq</t>
+          <t>Let's chat on WhatsApp! It's a fast, simple, and secure app we can use to message and call each other for free. Get it at https://whatsapp.com/dl/</t>
         </is>
       </c>
       <c r="B166" t="n">
         <v>1</v>
       </c>
       <c r="C166" t="n">
-        <v>0.8160476998315082</v>
+        <v>0.7937352476735252</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>惨了..热热不能睡又想你..怎么办?&lt;EMO&gt;&lt;EMO&gt;&lt;EMO&gt;</t>
+          <t>Sikdaa</t>
         </is>
       </c>
       <c r="B167" t="n">
         <v>0</v>
       </c>
       <c r="C167" t="n">
-        <v>0.9385165105719386</v>
+        <v>0.8934532286505562</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>Alhamdulillah smoga Allah beri rai sihat.</t>
+          <t>[Emergency SOS] Emergency sharing ended. Tap this link to view my last location: https://maps.google.com/maps?f=q&amp;q=5.089113,100.392181.</t>
         </is>
       </c>
       <c r="B168" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C168" t="n">
-        <v>0.8730119001506667</v>
+        <v>0.7582502780575889</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>243�SCC_AIR_SAT�SCC_AT_12012_18B_RH.HiHi�6/15/2025 10:45:25.220 AM�True�3F ASSEM</t>
+          <t>[Emergency SOS] Emergency sharing ended. Tap this link to view my last location: https://maps.google.com/maps?f=q&amp;q=5.089113,100.392181.</t>
         </is>
       </c>
       <c r="B169" t="n">
         <v>1</v>
       </c>
       <c r="C169" t="n">
-        <v>0.9028801452370788</v>
+        <v>0.7582502780575889</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>Mudah: I'm interested in your ad on Mudah Pesona Villa Apartment Unit For Rent, please share more details with me.</t>
+          <t>[Emergency SOS] Emergency sharing ended. Tap this link to view my last location: https://maps.google.com/maps?f=q&amp;q=5.089113,100.392181.</t>
         </is>
       </c>
       <c r="B170" t="n">
         <v>1</v>
       </c>
       <c r="C170" t="n">
-        <v>0.5399263763571717</v>
+        <v>0.7582502780575889</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>Alat dengar anda digunakan oleh kad SIM lain, kedudukan ialah: MCC:502; MNC:13; CELL:14281; LAC:23097</t>
+          <t>14/6=420) 15/6=360) =780_20%-156) Total=-624.00 你的工人=700</t>
         </is>
       </c>
       <c r="B171" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C171" t="n">
-        <v>0.6813463462288205</v>
+        <v>0.6816443024296898</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>01c5f5b63a8635c7dog_</t>
+          <t>Let's chat on WhatsApp! It's a fast, simple, and secure app we can use to message and call each other for free. Get it at https://whatsapp.com/dl/</t>
         </is>
       </c>
       <c r="B172" t="n">
         <v>1</v>
       </c>
       <c r="C172" t="n">
-        <v>0.9407212710929678</v>
+        <v>0.7937352476735252</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>[Emergency SOS] Emergency sharing ended. Tap this link to view my last location: https://maps.google.com/maps?f=q&amp;q=5.089113,100.392181.</t>
+        </is>
+      </c>
+      <c r="B173" t="n">
+        <v>1</v>
+      </c>
+      <c r="C173" t="n">
+        <v>0.7582502780575889</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>Boleh dapatkan maklumat mengenaie diri anda terima kasih</t>
+        </is>
+      </c>
+      <c r="B174" t="n">
+        <v>0</v>
+      </c>
+      <c r="C174" t="n">
+        <v>0.8233518185000283</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>Let's chat on WhatsApp! It's a fast, simple, and secure app we can use to message and call each other for free. Get it at https://whatsapp.com/dl/</t>
+        </is>
+      </c>
+      <c r="B175" t="n">
+        <v>1</v>
+      </c>
+      <c r="C175" t="n">
+        <v>0.7937352476735252</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>Let's chat on WhatsApp! It's a fast, simple, and secure app we can use to message and call each other for free. Get it at https://whatsapp.com/dl/</t>
+        </is>
+      </c>
+      <c r="B176" t="n">
+        <v>1</v>
+      </c>
+      <c r="C176" t="n">
+        <v>0.7937352476735252</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>25O616 OOO5 (1) bft152O 18/O6 *MPT 3685=1B (Box) 3685=1B (IBox) GT=75 TT=75 O16232711O</t>
+        </is>
+      </c>
+      <c r="B177" t="n">
+        <v>1</v>
+      </c>
+      <c r="C177" t="n">
+        <v>0.5173586426396507</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>Amoi sini company goldenbet99,apa kabar sudah bossku,lama dah tak try spin mari.jackpot,free game,Bonusgame menanti anda. Web : goldenbet99 .com</t>
+        </is>
+      </c>
+      <c r="B178" t="n">
+        <v>1</v>
+      </c>
+      <c r="C178" t="n">
+        <v>0.6104651508946556</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>DDY SYA AMBILL SIMM SYAA</t>
+        </is>
+      </c>
+      <c r="B179" t="n">
+        <v>0</v>
+      </c>
+      <c r="C179" t="n">
+        <v>0.765904265819059</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>DDY SYA AMBILL SIMM SYAA</t>
+        </is>
+      </c>
+      <c r="B180" t="n">
+        <v>0</v>
+      </c>
+      <c r="C180" t="n">
+        <v>0.765904265819059</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>FPX OPEN P-250615: Failure rate increase on Database service EFPXPROD:Failure rate increase</t>
+        </is>
+      </c>
+      <c r="B181" t="n">
+        <v>0</v>
+      </c>
+      <c r="C181" t="n">
+        <v>0.8071682931761605</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>588896 kjEwRrpYYz</t>
+        </is>
+      </c>
+      <c r="B182" t="n">
+        <v>1</v>
+      </c>
+      <c r="C182" t="n">
+        <v>0.6885478315968651</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>SEMENYIH BATT LOW!!!=0 15062025,18:21</t>
+        </is>
+      </c>
+      <c r="B183" t="n">
+        <v>0</v>
+      </c>
+      <c r="C183" t="n">
+        <v>0.7621126057486397</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>Let's chat on WhatsApp! It's a fast, simple, and secure app we can use to message and call each other for free. Get it at https://whatsapp.com/dl/</t>
+        </is>
+      </c>
+      <c r="B184" t="n">
+        <v>1</v>
+      </c>
+      <c r="C184" t="n">
+        <v>0.7937352476735252</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>Bank loan (offer) - Rm10K - 400K / 5-10 yrs - Debt Consolidate - Hard to get Loan Approve? - Credit card limit burst? - CTOS/ Blacklist issue? No worried, WE CAN SETTLE YOUR PROBLEM REPLY YES for details</t>
+        </is>
+      </c>
+      <c r="B185" t="n">
+        <v>0</v>
+      </c>
+      <c r="C185" t="n">
+        <v>0.5991671265940529</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>[Emergency SOS] Emergency sharing ended. Tap this link to view my last location: https://maps.google.com/maps?f=q&amp;q=5.089113,100.392181.</t>
+        </is>
+      </c>
+      <c r="B186" t="n">
+        <v>1</v>
+      </c>
+      <c r="C186" t="n">
+        <v>0.7582502780575889</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>[Emergency SOS] Emergency sharing ended. Tap this link to view my last location: https://maps.google.com/maps?f=q&amp;q=5.089113,100.392181.</t>
+        </is>
+      </c>
+      <c r="B187" t="n">
+        <v>1</v>
+      </c>
+      <c r="C187" t="n">
+        <v>0.7582502780575889</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>k la ..maaf ganggu idup awk. jaga diri elok2 bb .. baby mintakk maaf sgt2.. loveusomuch &lt;EMO&gt; assalamualaikum cinta.</t>
+        </is>
+      </c>
+      <c r="B188" t="n">
+        <v>0</v>
+      </c>
+      <c r="C188" t="n">
+        <v>0.7832288705456927</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>FPX OPEN P-250615: Failure rate increase on Database service EFPXPROD:Failure rate increase</t>
+        </is>
+      </c>
+      <c r="B189" t="n">
+        <v>0</v>
+      </c>
+      <c r="C189" t="n">
+        <v>0.7756369077313616</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>Let's chat on WhatsApp! It's a fast, simple, and secure app we can use to message and call each other for free. Get it at https://whatsapp.com/dl/</t>
+        </is>
+      </c>
+      <c r="B190" t="n">
+        <v>1</v>
+      </c>
+      <c r="C190" t="n">
+        <v>0.8821827805887983</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>[Emergency SOS] Emergency sharing ended. Tap this link to view my last location: https://maps.google.com/maps?f=q&amp;q=5.089113,100.392181.</t>
+        </is>
+      </c>
+      <c r="B191" t="n">
+        <v>1</v>
+      </c>
+      <c r="C191" t="n">
+        <v>0.8050231970202253</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>Bkt.Berlian Res R 24,0 20:26 unet 23.239.111.108 352134012067105 0508 0 1 3 12 62 17600 17600 0.00OK In1=1 In2=0 In3=0</t>
+        </is>
+      </c>
+      <c r="B192" t="n">
+        <v>0</v>
+      </c>
+      <c r="C192" t="n">
+        <v>0.5697963201153948</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>Old Insurance policy FREE REVIEW and Consultation * AIA medical coverage * Up to Rm8mil annual limit * No medical checkup (T&amp;C) Reply "YES" for more infos</t>
+        </is>
+      </c>
+      <c r="B193" t="n">
+        <v>1</v>
+      </c>
+      <c r="C193" t="n">
+        <v>0.7138193286310957</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>&lt;0920392&gt; System Armed</t>
+        </is>
+      </c>
+      <c r="B194" t="n">
+        <v>1</v>
+      </c>
+      <c r="C194" t="n">
+        <v>0.8170995748888776</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>Waalaikumsalam kwn man Ney tok.kmk mok tauk lebih benar.man Ney satu</t>
+        </is>
+      </c>
+      <c r="B195" t="n">
+        <v>0</v>
+      </c>
+      <c r="C195" t="n">
+        <v>0.6232140623677447</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>Bank loan (offer) - Rm10K - 400K / 5-10 yrs - Debt Consolidate - Hard to get Loan Approve? - Credit card limit burst? - CTOS/ Blacklist issue? No worried, WE CAN SETTLE YOUR PROBLEM REPLY YES for details</t>
+        </is>
+      </c>
+      <c r="B196" t="n">
+        <v>0</v>
+      </c>
+      <c r="C196" t="n">
+        <v>0.5498748981106951</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>Old Insurance policy FREE REVIEW and Consultation * AIA medical coverage * Up to Rm8mil annual limit * No medical checkup (T&amp;C) Reply "YES" for more infos</t>
+        </is>
+      </c>
+      <c r="B197" t="n">
+        <v>1</v>
+      </c>
+      <c r="C197" t="n">
+        <v>0.7138193286310957</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>Let's chat on Viber. It's my main app for messaging and free calls. Hereမမမမ's the link https://vb.me/letsUseViber</t>
+        </is>
+      </c>
+      <c r="B198" t="n">
+        <v>1</v>
+      </c>
+      <c r="C198" t="n">
+        <v>0.5304356850039289</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>[Emergency SOS] Emergency sharing ended. Tap this link to view my last location: https://maps.google.com/maps?f=q&amp;q=5.089113,100.392181.</t>
+        </is>
+      </c>
+      <c r="B199" t="n">
+        <v>1</v>
+      </c>
+      <c r="C199" t="n">
+        <v>0.8050231970202253</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>Monday, 06/16/2025 at 00:02:17. The Point 3C. AHU 100K5 RET HUMIDITY is in Alarm at PRI1 with a value of 63.2 %RH.</t>
+        </is>
+      </c>
+      <c r="B200" t="n">
+        <v>1</v>
+      </c>
+      <c r="C200" t="n">
+        <v>0.8952036536585615</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>kedong20 爱玉冰30</t>
+        </is>
+      </c>
+      <c r="B201" t="n">
+        <v>0</v>
+      </c>
+      <c r="C201" t="n">
+        <v>0.6809973084080889</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>Line kat sini memang kadang kadang takde hmmm</t>
+        </is>
+      </c>
+      <c r="B202" t="n">
+        <v>0</v>
+      </c>
+      <c r="C202" t="n">
+        <v>0.6049184166539385</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>6/16/2025 12:06:07 AM PHKL Blk A Level 3 IVF Embryology Lab High Temperature Alarm.</t>
+        </is>
+      </c>
+      <c r="B203" t="n">
+        <v>1</v>
+      </c>
+      <c r="C203" t="n">
+        <v>0.7193701303850935</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>Rest leklok tau pastu ws saya nanti bila awak dh ade data ataupun awak missed call je saya kejap pastu saya call awak balik kalau saya terjaga. Goodnight &lt;3</t>
+        </is>
+      </c>
+      <c r="B204" t="n">
+        <v>0</v>
+      </c>
+      <c r="C204" t="n">
+        <v>0.7297881507027819</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>6/16/2025 12:06:07 AM PHKL Blk A Level 3 IVF Embryology Lab High Temperature Alarm.</t>
+        </is>
+      </c>
+      <c r="B205" t="n">
+        <v>1</v>
+      </c>
+      <c r="C205" t="n">
+        <v>0.7193701303850935</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>To join the meeting on Google Meet, click this link: https://meet.google.com/gow-xyon-gdu Or open Meet and enter this code: gow-xyon-gdu</t>
+        </is>
+      </c>
+      <c r="B206" t="n">
+        <v>0</v>
+      </c>
+      <c r="C206" t="n">
+        <v>0.5019080602276995</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>+60 11-1218 7314</t>
+        </is>
+      </c>
+      <c r="B207" t="n">
+        <v>1</v>
+      </c>
+      <c r="C207" t="n">
+        <v>0.8861025012385175</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>6/16/2025 12:06:07 AM PHKL Blk A Level 3 IVF Embryology Lab High Temperature Alarm.</t>
+        </is>
+      </c>
+      <c r="B208" t="n">
+        <v>1</v>
+      </c>
+      <c r="C208" t="n">
+        <v>0.7193666733156965</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>16/06/2025 00:03:01 HARWOOD KUALA BARAM-Branch online after power resumed.</t>
+        </is>
+      </c>
+      <c r="B209" t="n">
+        <v>1</v>
+      </c>
+      <c r="C209" t="n">
+        <v>0.7122377193819807</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>6/16/2025 12:06:07 AM PHKL Blk A Level 3 IVF Embryology Lab High Temperature Alarm.</t>
+        </is>
+      </c>
+      <c r="B210" t="n">
+        <v>1</v>
+      </c>
+      <c r="C210" t="n">
+        <v>0.7193701303850935</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>MCM geli je</t>
+        </is>
+      </c>
+      <c r="B211" t="n">
+        <v>0</v>
+      </c>
+      <c r="C211" t="n">
+        <v>0.6539764665711596</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>U don't deserve a woman like</t>
+        </is>
+      </c>
+      <c r="B212" t="n">
+        <v>0</v>
+      </c>
+      <c r="C212" t="n">
+        <v>0.8338447772610857</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>&lt;0920392&gt; System Armed</t>
+        </is>
+      </c>
+      <c r="B213" t="n">
+        <v>1</v>
+      </c>
+      <c r="C213" t="n">
+        <v>0.8170995748888776</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>Mami..bgtau bang net tolong jap topupkan nombor digi abg ni ha RM 10 dulu,data abg dah tamat tempoh ha..</t>
+        </is>
+      </c>
+      <c r="B214" t="n">
+        <v>1</v>
+      </c>
+      <c r="C214" t="n">
+        <v>0.7476258314501569</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>25O616 OOO6 (2) bq33 18/O6-21/O6-22/O6 *P 8O5O=1B 1S 8O5O=6B (IBox) GT=24</t>
+        </is>
+      </c>
+      <c r="B215" t="n">
+        <v>1</v>
+      </c>
+      <c r="C215" t="n">
+        <v>0.5683646238695905</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>25O616 OOO6 (1) kb213O22 16/O6 /HE 3888=2B GT=2 Q1126388897 Points:OO13 1633 5196 7278</t>
+        </is>
+      </c>
+      <c r="B216" t="n">
+        <v>1</v>
+      </c>
+      <c r="C216" t="n">
+        <v>0.7970710433375165</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>Hi Mendo Buda,,,sorry saya block you WhatsApp dulu ya saya kena belajar untuk tidak mencintai you lagi ,,you jangan cari saya lagi fokus dengan cinta you mendo</t>
+        </is>
+      </c>
+      <c r="B217" t="n">
+        <v>0</v>
+      </c>
+      <c r="C217" t="n">
+        <v>0.58005216351635</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>ALARM S/ROOM BURGOGUAD Area 1 16 Jun 0h05</t>
+        </is>
+      </c>
+      <c r="B218" t="n">
+        <v>1</v>
+      </c>
+      <c r="C218" t="n">
+        <v>0.796003881777458</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>Amoi sini company goldenbet99,apa kabar sudah bossku,lama dah tak try spin mari.jackpot,free game,Bonusgame menanti anda. Web : goldenbet99 .com</t>
+        </is>
+      </c>
+      <c r="B219" t="n">
+        <v>1</v>
+      </c>
+      <c r="C219" t="n">
+        <v>0.641339186514549</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>25O616 OOO6 (3) bq33 18/O6-21/O6-22/O6 *T 1911=3B 2S (Box) GT=6O</t>
+        </is>
+      </c>
+      <c r="B220" t="n">
+        <v>1</v>
+      </c>
+      <c r="C220" t="n">
+        <v>0.7668076790224836</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>Flextronic H1 MsgText : J750_Sensor_3 RH Back to Normal Value : 59.0 %</t>
+        </is>
+      </c>
+      <c r="B221" t="n">
+        <v>1</v>
+      </c>
+      <c r="C221" t="n">
+        <v>0.7744296229731367</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>https://images.app.goo.gl/QJQ6bqWbeMMFs9yh9</t>
+        </is>
+      </c>
+      <c r="B222" t="n">
+        <v>1</v>
+      </c>
+      <c r="C222" t="n">
+        <v>0.5051811580005092</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>Mak ngerak kol 7 aa</t>
+        </is>
+      </c>
+      <c r="B223" t="n">
+        <v>0</v>
+      </c>
+      <c r="C223" t="n">
+        <v>0.8772887792048054</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>Bkt.Berlian Res R 24,0 20:26 unet 23.239.111.108 352134012067105 0508 0 1 3 12 62 17600 17600 0.00OK In1=1 In2=0 In3=0</t>
+        </is>
+      </c>
+      <c r="B224" t="n">
+        <v>0</v>
+      </c>
+      <c r="C224" t="n">
+        <v>0.6311399098095494</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>Mudah: I'm interested in your ad on Mudah Flat Tmn Melati (Partly furnished+Air Cond Near LRT) Ready to move in, please share more details with me.</t>
+        </is>
+      </c>
+      <c r="B225" t="n">
+        <v>0</v>
+      </c>
+      <c r="C225" t="n">
+        <v>0.8403708692249852</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>IU6tZvtQRiix</t>
+        </is>
+      </c>
+      <c r="B226" t="n">
+        <v>0</v>
+      </c>
+      <c r="C226" t="n">
+        <v>0.8166618700680333</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>Mudah: I'm interested in your ad on Mudah Hata Square Female Room Rental Fully Furnished (June 2025), please share more details with me.</t>
+        </is>
+      </c>
+      <c r="B227" t="n">
+        <v>0</v>
+      </c>
+      <c r="C227" t="n">
+        <v>0.5081961508450108</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>To join the meeting on Google Meet, click this link: https://meet.google.com/bxe-hyrj-oxe Or open Meet and enter this code: bxe-hyrj-oxe</t>
+        </is>
+      </c>
+      <c r="B228" t="n">
+        <v>1</v>
+      </c>
+      <c r="C228" t="n">
+        <v>0.6654521469417018</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>To join the meeting on Google Meet, click this link: https://meet.google.com/bxe-hyrj-oxe Or open Meet and enter this code: bxe-hyrj-oxe</t>
+        </is>
+      </c>
+      <c r="B229" t="n">
+        <v>1</v>
+      </c>
+      <c r="C229" t="n">
+        <v>0.6654521469417018</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>Abg hanya menunggu jawapan terakhir dri syg utk berjumpa ..kalau syg tak menjawab permintaan terakhir Abg abg akn Pham tiada lagi hubungan kita.....</t>
+        </is>
+      </c>
+      <c r="B230" t="n">
+        <v>0</v>
+      </c>
+      <c r="C230" t="n">
+        <v>0.8409186657127934</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>Boleh dapatkan maklumat mengenaie diri anda terima kasih</t>
+        </is>
+      </c>
+      <c r="B231" t="n">
+        <v>0</v>
+      </c>
+      <c r="C231" t="n">
+        <v>0.8493267353233891</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>(311720) lezwrxOKjl</t>
+        </is>
+      </c>
+      <c r="B232" t="n">
+        <v>1</v>
+      </c>
+      <c r="C232" t="n">
+        <v>0.629185283595602</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>F re3 Cr3dlt M€ g@/K1 §§/P u§§ y Was@p - 01_46139668 0ng m@li Jajwnsmz</t>
+        </is>
+      </c>
+      <c r="B233" t="n">
+        <v>1</v>
+      </c>
+      <c r="C233" t="n">
+        <v>0.7677073721232814</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>jgn awak mok mcm iii</t>
+        </is>
+      </c>
+      <c r="B234" t="n">
+        <v>1</v>
+      </c>
+      <c r="C234" t="n">
+        <v>0.7663739566150112</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>END - 06/15 22:58 AC2:No connection</t>
+        </is>
+      </c>
+      <c r="B235" t="n">
+        <v>1</v>
+      </c>
+      <c r="C235" t="n">
+        <v>0.8918451313319606</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>rm30 can?</t>
+        </is>
+      </c>
+      <c r="B236" t="n">
+        <v>0</v>
+      </c>
+      <c r="C236" t="n">
+        <v>0.8095768447575169</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>Bank loan (offer) - Rm10K - 400K / 5-10 yrs - Debt Consolidate - Hard to get Loan Approve? - Credit card limit burst? - CTOS/ Blacklist issue? No worried, WE CAN SETTLE YOUR PROBLEM REPLY YES for details</t>
+        </is>
+      </c>
+      <c r="B237" t="n">
+        <v>0</v>
+      </c>
+      <c r="C237" t="n">
+        <v>0.626309877222498</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>112184102410 maybank</t>
+        </is>
+      </c>
+      <c r="B238" t="n">
+        <v>1</v>
+      </c>
+      <c r="C238" t="n">
+        <v>0.7690163497271938</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>Name : Ajit Budget : as low as possible when move in : 1july How many ppl stay : 8 Nepal friend or family : workers Occupation : security Working company name/ school name : security company Local / Foreigner : Race : nepal Tenancy 1 or 2 years : 2</t>
+        </is>
+      </c>
+      <c r="B239" t="n">
+        <v>1</v>
+      </c>
+      <c r="C239" t="n">
+        <v>0.5471590999904079</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>Satgi lepas tutup kedai abg P lewat skit,abg skit tumit jalan banyak 2/3hari ni</t>
+        </is>
+      </c>
+      <c r="B240" t="n">
+        <v>0</v>
+      </c>
+      <c r="C240" t="n">
+        <v>0.8161616082844334</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>Beli number baru,,, number Lama abaikan.. Whassup ko pun keli dah bolh Baca.. Pandai sgt</t>
+        </is>
+      </c>
+      <c r="B241" t="n">
+        <v>0</v>
+      </c>
+      <c r="C241" t="n">
+        <v>0.8663669731077748</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>Company Kami sedia Free Angpao dan Bonus Special. Sila Claim dekat WS amoi sekarang : 01 13762 3807!</t>
+        </is>
+      </c>
+      <c r="B242" t="n">
+        <v>0</v>
+      </c>
+      <c r="C242" t="n">
+        <v>0.6387143190559941</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>IMEI : 862004070888606 Location is http://www.google.com/maps/place/2.9094171,101.5637074 Your Location is : Latitude is 2.9094171, Longitude is 101.5637074 Location time : 2025-06-16 12:06:50 AM</t>
+        </is>
+      </c>
+      <c r="B243" t="n">
+        <v>1</v>
+      </c>
+      <c r="C243" t="n">
+        <v>0.5726050381007595</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>Ayo chat di WhatsApp, aplikasi yang cepat, sederhana, dan aman untuk berkirim pesan dan menelepon secara gratis. Dapatkan di https://whatsapp.com/dl/code=XGMOPQanYv?mode=c</t>
+        </is>
+      </c>
+      <c r="B244" t="n">
+        <v>0</v>
+      </c>
+      <c r="C244" t="n">
+        <v>0.6905160601791935</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>f6cbb53539260847dog_</t>
+        </is>
+      </c>
+      <c r="B245" t="n">
+        <v>1</v>
+      </c>
+      <c r="C245" t="n">
+        <v>0.577918136531393</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>Bank loan (offer) - Rm10K - 400K / 5-10 yrs - Debt Consolidate - Hard to get Loan Approve? - Credit card limit burst? - CTOS/ Blacklist issue? No worried, WE CAN SETTLE YOUR PROBLEM REPLY YES for details</t>
+        </is>
+      </c>
+      <c r="B246" t="n">
+        <v>0</v>
+      </c>
+      <c r="C246" t="n">
+        <v>0.626309877222498</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>https://images.app.goo.gl/QJQ6bqWbeMMFs9yh9</t>
+        </is>
+      </c>
+      <c r="B247" t="n">
+        <v>1</v>
+      </c>
+      <c r="C247" t="n">
+        <v>0.5051811580005092</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>Tu ak ckp ak MMG dah tak blh nk belah la dgn prgai bbi sial pukimak KO ni....nk kurang AJK 24jam dgn ak lpas tu nk maki ak 24jam woiiii sial KO ingt ak ni tmpat maki KO ke pukimak anjing....ape KO ckp ko nk bawak Myvi KO kan ok cun...KO bawak ok...ak tak kan ambit punye pukimak babi....sbb KO tak ad hrmat ak cukup la ak tgk KO punye pergai MMG sampai ke mmpus tak kan berubah punye sial....so skrg ni keputusan ak muktamad ak tak kan dtg ambit ko nye sial....</t>
+        </is>
+      </c>
+      <c r="B248" t="n">
+        <v>0</v>
+      </c>
+      <c r="C248" t="n">
+        <v>0.5646182056126194</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>(585200) AmowZBAEX</t>
+        </is>
+      </c>
+      <c r="B249" t="n">
+        <v>0</v>
+      </c>
+      <c r="C249" t="n">
+        <v>0.5866782191743559</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>(T)=249.00 阿水 16/06/25</t>
+        </is>
+      </c>
+      <c r="B250" t="n">
+        <v>1</v>
+      </c>
+      <c r="C250" t="n">
+        <v>0.7353277679930025</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>Mudah: I'm interested in your ad on Mudah 2007 Perodua MYVI 1.3 EZ (A), please share more details with me.</t>
+        </is>
+      </c>
+      <c r="B251" t="n">
+        <v>1</v>
+      </c>
+      <c r="C251" t="n">
+        <v>0.6768153783331209</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>Tengok live mantap joran tiktok. Abg fon xd line</t>
+        </is>
+      </c>
+      <c r="B252" t="n">
+        <v>1</v>
+      </c>
+      <c r="C252" t="n">
+        <v>0.8030220743665987</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>Balance:(-298), Bet:(-132), Total:(-430), Mau transfer lagi dah tauke,dah bnyk amount..tq</t>
+        </is>
+      </c>
+      <c r="B253" t="n">
+        <v>0</v>
+      </c>
+      <c r="C253" t="n">
+        <v>0.6220074418534941</v>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>To join the meeting on Google Meet, click this link: https://meet.google.com/bxe-hyrj-oxe Or open Meet and enter this code: bxe-hyrj-oxe</t>
+        </is>
+      </c>
+      <c r="B254" t="n">
+        <v>1</v>
+      </c>
+      <c r="C254" t="n">
+        <v>0.6359874483595186</v>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>Mudah: I'm interested in your ad on Mudah Land in Beranang, Ulu Langat, Selangor, please share more details with me.</t>
+        </is>
+      </c>
+      <c r="B255" t="n">
+        <v>0</v>
+      </c>
+      <c r="C255" t="n">
+        <v>0.5436365130891508</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>BX99:您被选了(chye666)!恭喜您获得228次免费旋转。存RM50就解锁!bx99my{dot}com</t>
+        </is>
+      </c>
+      <c r="B256" t="n">
+        <v>0</v>
+      </c>
+      <c r="C256" t="n">
+        <v>0.6059200886239714</v>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>Rumah Pam Taman Cendana Suction Low Recovery</t>
+        </is>
+      </c>
+      <c r="B257" t="n">
+        <v>1</v>
+      </c>
+      <c r="C257" t="n">
+        <v>0.6065377470503145</v>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>BX99: (ID: yonglee04) Congrats, you are one of todays lucky picks. Deposit RM50 to get 228 FREE Spins. Dont miss out! bx99my{dot}com</t>
+        </is>
+      </c>
+      <c r="B258" t="n">
+        <v>1</v>
+      </c>
+      <c r="C258" t="n">
+        <v>0.7526456591139131</v>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>BX99:您被选了(hui173)!恭喜您获得228次免费旋转。存RM50就解锁!bx99my{dot}com</t>
+        </is>
+      </c>
+      <c r="B259" t="n">
+        <v>1</v>
+      </c>
+      <c r="C259" t="n">
+        <v>0.5264093753347688</v>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>U388: 嘿! 您升级后的RM50免费积分感到孤独。赶快在它们离开前领取吧!u388my{dot}com</t>
+        </is>
+      </c>
+      <c r="B260" t="n">
+        <v>1</v>
+      </c>
+      <c r="C260" t="n">
+        <v>0.7078223701963716</v>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>Ari 2023 sampai 2025 agi mh enda nmu puas bula..sampai mati.mh d nya bula</t>
+        </is>
+      </c>
+      <c r="B261" t="n">
+        <v>0</v>
+      </c>
+      <c r="C261" t="n">
+        <v>0.614550304745645</v>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>明天4000我不太可能,我最快也要等到我新山的工完,我还可以安排3000给你,不过这个是月尾的事了 如果你是说2/300,明天星期一,还行,我明天要去收钱,可以2/300</t>
+        </is>
+      </c>
+      <c r="B262" t="n">
+        <v>0</v>
+      </c>
+      <c r="C262" t="n">
+        <v>0.61100496086976</v>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>Bank loan (offer) - Rm10K - 400K / 5-10 yrs - Debt Consolidate - Hard to get Loan Approve? - Credit card limit burst? - CTOS/ Blacklist issue? No worried, WE CAN SETTLE YOUR PROBLEM REPLY YES for details</t>
+        </is>
+      </c>
+      <c r="B263" t="n">
+        <v>0</v>
+      </c>
+      <c r="C263" t="n">
+        <v>0.6906784001340575</v>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>最后的机会!只需存款RM50即可获得238次免费旋转。优惠今晚到期。立即在12huatmy{dot}com领取!</t>
+        </is>
+      </c>
+      <c r="B264" t="n">
+        <v>0</v>
+      </c>
+      <c r="C264" t="n">
+        <v>0.860946846341104</v>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>15/6 Talang - 250 Syukeri - 50 Rani - 50 Pait kangkong - 50 Saidon - 100 ( tng ) Abu shamah - 50 Fikri fatin - 100 Koyong - 50</t>
+        </is>
+      </c>
+      <c r="B265" t="n">
+        <v>0</v>
+      </c>
+      <c r="C265" t="n">
+        <v>0.5857158425798125</v>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>HARAP TAK SALAH LAGI</t>
+        </is>
+      </c>
+      <c r="B266" t="n">
+        <v>0</v>
+      </c>
+      <c r="C266" t="n">
+        <v>0.7292320552816099</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>Dok.Mana..Buat15</t>
+        </is>
+      </c>
+      <c r="B267" t="n">
+        <v>0</v>
+      </c>
+      <c r="C267" t="n">
+        <v>0.5348485830774016</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>BX99: (ID: suhiom88) Congrats, you are one of todays lucky picks. Deposit RM50 to get 228 FREE Spins. Dont miss out! bx99my{dot}com</t>
+        </is>
+      </c>
+      <c r="B268" t="n">
+        <v>1</v>
+      </c>
+      <c r="C268" t="n">
+        <v>0.58967201676467</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>ACE66: We missed you! Here's RM50 free credit to kickstart your winning journey with us. Claim at ace66my{dot}com now!</t>
+        </is>
+      </c>
+      <c r="B269" t="n">
+        <v>0</v>
+      </c>
+      <c r="C269" t="n">
+        <v>0.7031427446355528</v>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>Assalamualaikum Aji apa khabar ini Ape.ini daripada no 0199682615.ini no baru sy</t>
+        </is>
+      </c>
+      <c r="B270" t="n">
+        <v>1</v>
+      </c>
+      <c r="C270" t="n">
+        <v>0.6391259905348116</v>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>FPX RESOLVED P-250615: Failure rate increase on Database service EFPXPROD:Failure rate increase</t>
+        </is>
+      </c>
+      <c r="B271" t="n">
+        <v>0</v>
+      </c>
+      <c r="C271" t="n">
+        <v>0.7151490572442717</v>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>9----15-6 rm - 198 198 +90= - 288</t>
+        </is>
+      </c>
+      <c r="B272" t="n">
+        <v>1</v>
+      </c>
+      <c r="C272" t="n">
+        <v>0.6213074800024324</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>Jgn tnye npe kte ttp PGL awak biey ye</t>
+        </is>
+      </c>
+      <c r="B273" t="n">
+        <v>0</v>
+      </c>
+      <c r="C273" t="n">
+        <v>0.6958115521421141</v>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>#vivo#simc##862241033847002#1#89601624050700854110#</t>
+        </is>
+      </c>
+      <c r="B274" t="n">
+        <v>1</v>
+      </c>
+      <c r="C274" t="n">
+        <v>0.7418716427336031</v>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>FPX RESOLVED P-250615: Failure rate increase on Database service EFPXPROD:Failure rate increase</t>
+        </is>
+      </c>
+      <c r="B275" t="n">
+        <v>0</v>
+      </c>
+      <c r="C275" t="n">
+        <v>0.7151490572442717</v>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>380</t>
+        </is>
+      </c>
+      <c r="B276" t="n">
+        <v>0</v>
+      </c>
+      <c r="C276" t="n">
+        <v>0.7789318684091276</v>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>196242 GnZwmVwXwj</t>
+        </is>
+      </c>
+      <c r="B277" t="n">
+        <v>1</v>
+      </c>
+      <c r="C277" t="n">
+        <v>0.822940933371573</v>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>https://images.app.goo.gl/sGYYfKrpJYe4wMc76</t>
+        </is>
+      </c>
+      <c r="B278" t="n">
+        <v>1</v>
+      </c>
+      <c r="C278" t="n">
+        <v>0.5885683771620088</v>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>Company Kami sedia Free Angpao dan Bonus Special. Sila Claim dekat WS amoi sekarang : 01 13762 3807!</t>
+        </is>
+      </c>
+      <c r="B279" t="n">
+        <v>0</v>
+      </c>
+      <c r="C279" t="n">
+        <v>0.6798649552812285</v>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>2957+126+174=3257</t>
+        </is>
+      </c>
+      <c r="B280" t="n">
+        <v>1</v>
+      </c>
+      <c r="C280" t="n">
+        <v>0.7114272591123872</v>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>Welcome to I BC22: Level up your gaming experience, win like a PRO! Discover exciting promotions and hottest games at ibc22mys{dot}com now!</t>
+        </is>
+      </c>
+      <c r="B281" t="n">
+        <v>1</v>
+      </c>
+      <c r="C281" t="n">
+        <v>0.5180269357214266</v>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>9----15-6 rm 420</t>
+        </is>
+      </c>
+      <c r="B282" t="n">
+        <v>0</v>
+      </c>
+      <c r="C282" t="n">
+        <v>0.6315223697175688</v>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>To join the meeting on Google Meet, click this link: https://meet.google.com/gow-xyon-gdu Or open Meet and enter this code: gow-xyon-gdu</t>
+        </is>
+      </c>
+      <c r="B283" t="n">
+        <v>0</v>
+      </c>
+      <c r="C283" t="n">
+        <v>0.5848308924188322</v>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>To join the meeting on Google Meet, click this link: https://meet.google.com/gow-xyon-gdu Or open Meet and enter this code: gow-xyon-gdu</t>
+        </is>
+      </c>
+      <c r="B284" t="n">
+        <v>0</v>
+      </c>
+      <c r="C284" t="n">
+        <v>0.5848308924188322</v>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>‎Let's chat on WhatsApp! It's a fast, simple, and secure app we can use to message and call each other for free. Get it at</t>
+        </is>
+      </c>
+      <c r="B285" t="n">
+        <v>1</v>
+      </c>
+      <c r="C285" t="n">
+        <v>0.5677910856456662</v>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>BX99: (ID: ra1244) Congrats, you are one of todays lucky picks. Deposit RM50 to get 228 FREE Spins. Dont miss out! bx99my{dot}com</t>
+        </is>
+      </c>
+      <c r="B286" t="n">
+        <v>1</v>
+      </c>
+      <c r="C286" t="n">
+        <v>0.6608713082523251</v>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>5Why you blocked me? king I just need RM300 now and let me secure a place by paying a deposit tomorrow me!in and put it this into your calculation. I need to confirm and pay the deposit tomorrow morning</t>
+        </is>
+      </c>
+      <c r="B287" t="n">
+        <v>1</v>
+      </c>
+      <c r="C287" t="n">
+        <v>0.5556946210117245</v>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>Company Kami sedia Free Angpao dan Bonus Special. Sila Claim dekat WS amoi sekarang : 01 13762 3807!</t>
+        </is>
+      </c>
+      <c r="B288" t="n">
+        <v>0</v>
+      </c>
+      <c r="C288" t="n">
+        <v>0.6754754968433475</v>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>BX99:您被选了(nms413191)!恭喜您获得228次免费旋转。存RM50就解锁!bx99my{dot}com</t>
+        </is>
+      </c>
+      <c r="B289" t="n">
+        <v>1</v>
+      </c>
+      <c r="C289" t="n">
+        <v>0.6643276623935604</v>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>Leela pa and u add me in whatsapp 1st then i can send u what tje conversation actual was</t>
+        </is>
+      </c>
+      <c r="B290" t="n">
+        <v>0</v>
+      </c>
+      <c r="C290" t="n">
+        <v>0.796002287462244</v>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>*123*849934199814250#</t>
+        </is>
+      </c>
+      <c r="B291" t="n">
+        <v>0</v>
+      </c>
+      <c r="C291" t="n">
+        <v>0.6676377542762851</v>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>Nk ajak kwn baru dia tidak ada duit</t>
+        </is>
+      </c>
+      <c r="B292" t="n">
+        <v>0</v>
+      </c>
+      <c r="C292" t="n">
+        <v>0.7004537769107914</v>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>Selamat Hari Lahir. Selamat bertambah usia. Semoga apa yang kau semogakan, tersemoga. Semoga terus suksess dalam apa jua. Sihat, berbahagia &amp; kuat selalu. Thank you sudah jadi kawan yang baik utk beberapa hari. Selepas tu, dont know lah jadi apa suda. Its not the same Hafiz Ikhwan. Semoga perangai yang tak baik, cepat2 lah diubah. Semoga masih sempat utk insaf &amp; jadi manusia yang berguna. Oh yaa, aku ada text ibu kau. Tanya kau suka makan apa. Ibu cakqp, kau suka brownies. And i think i will cook brownies for you. Sudi tak terima? Saja tanya awal, kang tak terima. Aku tak buat lah. Memandangkan esok aku dah apply cuti, pastu ko teda pun d Tawau. So i'll celebrate n menikmati cuti itu. Nanti ko balik roger lah, i'll belanja u makan. Itupun kalau sudi lah. Kalau tak, its okey. Tak paksa. Hmm tu jaaa laa, selamat hari lahir beib. ly</t>
+        </is>
+      </c>
+      <c r="B293" t="n">
+        <v>1</v>
+      </c>
+      <c r="C293" t="n">
+        <v>0.5286313704700375</v>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>Ari 2023 sampai 2025 agi mh enda nmu puas bula..sampai mati.mh d nya bula</t>
+        </is>
+      </c>
+      <c r="B294" t="n">
+        <v>0</v>
+      </c>
+      <c r="C294" t="n">
+        <v>0.6270473190097904</v>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>Bik noh rah mulek bituh jagak noh</t>
+        </is>
+      </c>
+      <c r="B295" t="n">
+        <v>1</v>
+      </c>
+      <c r="C295" t="n">
+        <v>0.7248385361881161</v>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>Amoi sini company goldenbet99,apa kabar sudah bossku,lama dah tak try spin mari.jackpot,free game,Bonusgame menanti anda. Web ; goldenbet99 .com</t>
+        </is>
+      </c>
+      <c r="B296" t="n">
+        <v>1</v>
+      </c>
+      <c r="C296" t="n">
+        <v>0.5087528042049313</v>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>&lt;0528752&gt; AC Power Failure</t>
+        </is>
+      </c>
+      <c r="B297" t="n">
+        <v>1</v>
+      </c>
+      <c r="C297" t="n">
+        <v>0.8598671964855099</v>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>TOWER SG SELANGOR, S.Mode=NORWL DANGER=219.84m, RF LIGHT=1.5mm, RFDaily= 0.0mm, RFCumm= 52.5mm, Batt Nor= 12.8Vdc, 000, 16062025,00:04</t>
+        </is>
+      </c>
+      <c r="B298" t="n">
+        <v>1</v>
+      </c>
+      <c r="C298" t="n">
+        <v>0.7977310828418637</v>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>Company Kami sedia Free Angpao dan Bonus Special. Sila Claim dekat WS amoi sekarang : 01 13762 3807!</t>
+        </is>
+      </c>
+      <c r="B299" t="n">
+        <v>0</v>
+      </c>
+      <c r="C299" t="n">
+        <v>0.6754754968433475</v>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>Mudah: I'm interested in your ad on Mudah Anak Tupai, please share more details with me.</t>
+        </is>
+      </c>
+      <c r="B300" t="n">
+        <v>0</v>
+      </c>
+      <c r="C300" t="n">
+        <v>0.6327979155330753</v>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>#vivo#simc##862241033847002#1#89601624050700854110#</t>
+        </is>
+      </c>
+      <c r="B301" t="n">
+        <v>1</v>
+      </c>
+      <c r="C301" t="n">
+        <v>0.7289137057514096</v>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>&lt;0528752&gt; AC Power Restored</t>
+        </is>
+      </c>
+      <c r="B302" t="n">
+        <v>1</v>
+      </c>
+      <c r="C302" t="n">
+        <v>0.6852596215457821</v>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>https://images.app.goo.gl/sGYYfKrpJYe4wMc76</t>
+        </is>
+      </c>
+      <c r="B303" t="n">
+        <v>1</v>
+      </c>
+      <c r="C303" t="n">
+        <v>0.573215823575964</v>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>Ma da nyaa kjn adp MU tuui²...ma da nyaa tiwas de adp MU...bukan nyaa doi byr..</t>
+        </is>
+      </c>
+      <c r="B304" t="n">
+        <v>0</v>
+      </c>
+      <c r="C304" t="n">
+        <v>0.7342231460361576</v>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="inlineStr">
+        <is>
+          <t>Ngan number blkg tu skali</t>
+        </is>
+      </c>
+      <c r="B305" t="n">
+        <v>0</v>
+      </c>
+      <c r="C305" t="n">
+        <v>0.8715505190639591</v>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="inlineStr">
+        <is>
+          <t>Company Kami sedia Free Angpao dan Bonus Special. Sila Claim dekat WS amoi sekarang : 01 13762 3807!</t>
+        </is>
+      </c>
+      <c r="B306" t="n">
+        <v>0</v>
+      </c>
+      <c r="C306" t="n">
+        <v>0.6754754372387027</v>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="inlineStr">
+        <is>
+          <t>http://maps.google.com/maps?f=q&amp;q=5.849513,118.039284</t>
+        </is>
+      </c>
+      <c r="B307" t="n">
+        <v>0</v>
+      </c>
+      <c r="C307" t="n">
+        <v>0.7352361865787601</v>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="inlineStr">
+        <is>
+          <t>http://maps.google.com/maps?f=q&amp;q=5.849513,118.039284</t>
+        </is>
+      </c>
+      <c r="B308" t="n">
+        <v>0</v>
+      </c>
+      <c r="C308" t="n">
+        <v>0.7352361865787601</v>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="inlineStr">
+        <is>
+          <t>F re3 Cr3dlt M€ g@/K1 §§/P u§§ y Was@p - 01_46139668 0ng m@li Jajwnsns</t>
+        </is>
+      </c>
+      <c r="B309" t="n">
+        <v>1</v>
+      </c>
+      <c r="C309" t="n">
+        <v>0.7344719580860043</v>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="inlineStr">
+        <is>
+          <t>To join the meeting on Google Meet, click this link: https://meet.google.com/gow-xyon-gdu Or open Meet and enter this code: gow-xyon-gdu</t>
+        </is>
+      </c>
+      <c r="B310" t="n">
+        <v>0</v>
+      </c>
+      <c r="C310" t="n">
+        <v>0.592966992452631</v>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="inlineStr">
+        <is>
+          <t>E T: Wlcm u, MAX-M u=123281882465 p=TTtt2773 on:16/06 00:09:51</t>
+        </is>
+      </c>
+      <c r="B311" t="n">
+        <v>1</v>
+      </c>
+      <c r="C311" t="n">
+        <v>0.8118397406787777</v>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="inlineStr">
+        <is>
+          <t>Let's chat on WhatsApp! It's a fast, simple, and secure app we can use to message and call each other for free. Get it at https://whatsapp.com/dl/</t>
+        </is>
+      </c>
+      <c r="B312" t="n">
+        <v>1</v>
+      </c>
+      <c r="C312" t="n">
+        <v>0.8777228595604866</v>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="inlineStr">
+        <is>
+          <t>160166186588,Rohani binti Hassan @ serbane</t>
+        </is>
+      </c>
+      <c r="B313" t="n">
+        <v>0</v>
+      </c>
+      <c r="C313" t="n">
+        <v>0.5244084594855339</v>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="inlineStr">
+        <is>
+          <t>l ALWAYS LOVE U G009</t>
+        </is>
+      </c>
+      <c r="B314" t="n">
+        <v>0</v>
+      </c>
+      <c r="C314" t="n">
+        <v>0.6268931625494988</v>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="inlineStr">
+        <is>
+          <t>义烧30 花生9 豆沙3 加央3</t>
+        </is>
+      </c>
+      <c r="B315" t="n">
+        <v>0</v>
+      </c>
+      <c r="C315" t="n">
+        <v>0.8605949280867607</v>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="inlineStr">
+        <is>
+          <t>Ku bruk abis mkn tek alu mndik. bak mndik bruk nyaman sa nyawa tok. Mkn lh mun dh lmk x mkn hahahaha aok eh mun dh minat x kesah nk oh p mok jaga juak lh tkt ajak mun dh xda org minat gk nk cehhh bebual hahaha</t>
+        </is>
+      </c>
+      <c r="B316" t="n">
+        <v>0</v>
+      </c>
+      <c r="C316" t="n">
+        <v>0.8888407794842751</v>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="inlineStr">
+        <is>
+          <t>Company Kami sedia Free Angpao dan Bonus Special. Sila Claim dekat WS amoi sekarang : 01 13762 3807!</t>
+        </is>
+      </c>
+      <c r="B317" t="n">
+        <v>0</v>
+      </c>
+      <c r="C317" t="n">
+        <v>0.6327659485945732</v>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="inlineStr">
+        <is>
+          <t>Ayo chat di WhatsApp, aplikasi yang cepat, sederhana, dan aman untuk berkirim pesan dan menelepon secara gratis. Dapatkan di https://whatsapp.com/dl/code=wPUUTXFumG?mode=c</t>
+        </is>
+      </c>
+      <c r="B318" t="n">
+        <v>0</v>
+      </c>
+      <c r="C318" t="n">
+        <v>0.6500362156043084</v>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="inlineStr">
+        <is>
+          <t>16号了咯,你到底要进钱给我吗</t>
+        </is>
+      </c>
+      <c r="B319" t="n">
+        <v>0</v>
+      </c>
+      <c r="C319" t="n">
+        <v>0.7321086822161705</v>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="inlineStr">
+        <is>
+          <t>595291+5 407412+7</t>
+        </is>
+      </c>
+      <c r="B320" t="n">
+        <v>1</v>
+      </c>
+      <c r="C320" t="n">
+        <v>0.7751322986474006</v>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="inlineStr">
+        <is>
+          <t>Nk tido la ni ats katil ni hah</t>
+        </is>
+      </c>
+      <c r="B321" t="n">
+        <v>0</v>
+      </c>
+      <c r="C321" t="n">
+        <v>0.733792871058944</v>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="inlineStr">
+        <is>
+          <t>Slmt mlm sygg.jg diri.ore mtk mg slh slp ore nga sygg</t>
+        </is>
+      </c>
+      <c r="B322" t="n">
+        <v>0</v>
+      </c>
+      <c r="C322" t="n">
+        <v>0.8590444622645409</v>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="inlineStr">
+        <is>
+          <t>#vivo#simc##862241033847002#1#89601624050700854110#</t>
+        </is>
+      </c>
+      <c r="B323" t="n">
+        <v>1</v>
+      </c>
+      <c r="C323" t="n">
+        <v>0.7438079120507209</v>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="inlineStr">
+        <is>
+          <t>1 ,L2 FMC 19 R1 TMP 02 (CIMB-SVR1),IN CRITICAL MODE, Monday, June 16, 2025 12:11:13 AM.</t>
+        </is>
+      </c>
+      <c r="B324" t="n">
+        <v>1</v>
+      </c>
+      <c r="C324" t="n">
+        <v>0.728294074713227</v>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="inlineStr">
+        <is>
+          <t>Call From HQ Jessy Congratulations For You FRxx P01N TRY Gam3 Whatsap : 6 0 1 3 4 4 4 4 1 8 8</t>
+        </is>
+      </c>
+      <c r="B325" t="n">
+        <v>1</v>
+      </c>
+      <c r="C325" t="n">
+        <v>0.6195907594552009</v>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="inlineStr">
+        <is>
+          <t>BX99:您被选了(bonnieliew)!恭喜您获得228次免费旋转。存RM50就解锁!bx99my{dot}com</t>
+        </is>
+      </c>
+      <c r="B326" t="n">
+        <v>0</v>
+      </c>
+      <c r="C326" t="n">
+        <v>0.5227786896834404</v>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="inlineStr">
+        <is>
+          <t>https://images.app.goo.gl/3fsFEcNTAXyoPA4Z8</t>
+        </is>
+      </c>
+      <c r="B327" t="n">
+        <v>0</v>
+      </c>
+      <c r="C327" t="n">
+        <v>0.526801824391845</v>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="inlineStr">
+        <is>
+          <t>Amoi sini company goldenbet99,apa kabar sudah bossku,lama dah tak try spin mari.jackpot,free game,Bonusgame menanti anda. Web ; goldenbet99 .com</t>
+        </is>
+      </c>
+      <c r="B328" t="n">
+        <v>1</v>
+      </c>
+      <c r="C328" t="n">
+        <v>0.5072237851014106</v>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="inlineStr">
+        <is>
+          <t>Company Kami sedia Free Angpao dan Bonus Special. Sila Claim dekat WS amoi sekarang : 01 13762 3807!</t>
+        </is>
+      </c>
+      <c r="B329" t="n">
+        <v>0</v>
+      </c>
+      <c r="C329" t="n">
+        <v>0.6327659485945732</v>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="inlineStr">
+        <is>
+          <t>1 ,L2 FMC 19 R1 TMP 02 (CIMB-SVR1),IN CRITICAL MODE, Monday, June 16, 2025 12:11:13 AM.</t>
+        </is>
+      </c>
+      <c r="B330" t="n">
+        <v>1</v>
+      </c>
+      <c r="C330" t="n">
+        <v>0.728294074713227</v>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="inlineStr">
+        <is>
+          <t>HIJACK.HIJACK.HIJACK. KeyOff 24.9V 0km/h N5.09748,E100.44873 http://map.dftracker.com/?loc=3923365642E484</t>
+        </is>
+      </c>
+      <c r="B331" t="n">
+        <v>1</v>
+      </c>
+      <c r="C331" t="n">
+        <v>0.8781408073296516</v>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="inlineStr">
+        <is>
+          <t>Rm374</t>
+        </is>
+      </c>
+      <c r="B332" t="n">
+        <v>1</v>
+      </c>
+      <c r="C332" t="n">
+        <v>0.8473207952370613</v>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="inlineStr">
+        <is>
+          <t>RM0 ZUS Coffee: Welcome to ZUS Coffee! Your 4 digits verification code is 4089. Enjoy!</t>
+        </is>
+      </c>
+      <c r="B333" t="n">
+        <v>1</v>
+      </c>
+      <c r="C333" t="n">
+        <v>0.8877298833718269</v>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="inlineStr">
+        <is>
+          <t>Bereh2 . Lps ni ak bg blke brg mu. ckup ah snpai sni je. halal kan blke smua hk mu pnh v ke ak slme nie</t>
+        </is>
+      </c>
+      <c r="B334" t="n">
+        <v>0</v>
+      </c>
+      <c r="C334" t="n">
+        <v>0.8516078887591393</v>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="inlineStr">
+        <is>
+          <t>Can't locate you on WhatsApp</t>
+        </is>
+      </c>
+      <c r="B335" t="n">
+        <v>0</v>
+      </c>
+      <c r="C335" t="n">
+        <v>0.8859366921792061</v>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="inlineStr">
+        <is>
+          <t>Company Kami sedia Free Angpao dan Bonus Special. Sila Claim dekat WS amoi sekarang : 01 13762 3807!</t>
+        </is>
+      </c>
+      <c r="B336" t="n">
+        <v>0</v>
+      </c>
+      <c r="C336" t="n">
+        <v>0.6327659485945732</v>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="inlineStr">
+        <is>
+          <t>SLMT HARI BAPA SYGG+LOVE U MORE</t>
+        </is>
+      </c>
+      <c r="B337" t="n">
+        <v>0</v>
+      </c>
+      <c r="C337" t="n">
+        <v>0.8984616099009545</v>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="inlineStr">
+        <is>
+          <t>https://play.google.com/store/apps/details?id=castle.heroes.tower.defense.kingdom.magic.battle.archer</t>
+        </is>
+      </c>
+      <c r="B338" t="n">
+        <v>1</v>
+      </c>
+      <c r="C338" t="n">
+        <v>0.5048782827248542</v>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="inlineStr">
+        <is>
+          <t>https://play.google.com/store/apps/details?id=castle.heroes.tower.defense.kingdom.magic.battle.archer</t>
+        </is>
+      </c>
+      <c r="B339" t="n">
+        <v>1</v>
+      </c>
+      <c r="C339" t="n">
+        <v>0.5048782827248542</v>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="inlineStr">
+        <is>
+          <t>Wlkmslm ct blm gaji lagi atta kurang duit bulan ini</t>
+        </is>
+      </c>
+      <c r="B340" t="n">
+        <v>0</v>
+      </c>
+      <c r="C340" t="n">
+        <v>0.7088066337714226</v>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="inlineStr">
+        <is>
+          <t>Arming with keyswitch #1 Your Alarm Site SST PERIMETER 16 Jun 0h13</t>
+        </is>
+      </c>
+      <c r="B341" t="n">
+        <v>0</v>
+      </c>
+      <c r="C341" t="n">
+        <v>0.7304432092318566</v>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="inlineStr">
+        <is>
+          <t>Line bb habis, nnti bb chat blik nehh</t>
+        </is>
+      </c>
+      <c r="B342" t="n">
+        <v>0</v>
+      </c>
+      <c r="C342" t="n">
+        <v>0.7271357176909478</v>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="inlineStr">
+        <is>
+          <t>To join the meeting on Google Meet, click this link: https://meet.google.com/gow-xyon-gdu Or open Meet and enter this code: gow-xyon-gdu</t>
+        </is>
+      </c>
+      <c r="B343" t="n">
+        <v>0</v>
+      </c>
+      <c r="C343" t="n">
+        <v>0.6445202340746863</v>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="inlineStr">
+        <is>
+          <t>To join the meeting on Google Meet, click this link: https://meet.google.com/gow-xyon-gdu Or open Meet and enter this code: gow-xyon-gdu</t>
+        </is>
+      </c>
+      <c r="B344" t="n">
+        <v>0</v>
+      </c>
+      <c r="C344" t="n">
+        <v>0.6445202340746863</v>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="inlineStr">
+        <is>
+          <t>Nagios:eth9 Bandwidth - Outbound Host: exadomdbracp5 IP: 10.188.201.123 CRITICAL: Bytes_sent was 1206.05 MB/s 16/06/2025 00:10:38</t>
+        </is>
+      </c>
+      <c r="B345" t="n">
+        <v>0</v>
+      </c>
+      <c r="C345" t="n">
+        <v>0.736812364068125</v>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" t="inlineStr">
+        <is>
+          <t>betoi x d nafikan….imam nawawi ada riwayatkn dlm kita ibnu sunni kitab amal seharian….dari Anas…rasulullah saw setiap kali slesai solat selalu ngusap dahi dngn tngn kanan smbil mngucap.....tapi hadis ni daif bang....dan bukan daif biasa....daif jiddan....klau daif biasa abg nk amal ikut aa xdak msalah....sanad hadis ni terrrrlalu lemah....klu x silap sbbnya dua prawi hadis ni zaidul ammi dngn salam al tawil bmsalah kdua prawi ni....dan nasib baik time imam nawawi riwayat hadis ni dia letak skali nama2 prawi hadis supya bole semak status hadis yg ada.....klu hadis ni skdar daif biasa ja sya pn nk bramal abg oii...untuk fadail amal....tpi ni bukan daif biasa....ikot aa sya dh bgi pnerangan atas abg aa nk ikot atau x....wallahualam</t>
+        </is>
+      </c>
+      <c r="B346" t="n">
+        <v>0</v>
+      </c>
+      <c r="C346" t="n">
+        <v>0.8865351786280615</v>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="inlineStr">
+        <is>
+          <t>Call From HQ Jessy Congratulations For You FRxx P01N TRY Gam3 Whatsap : 6 0 1 3 4 4 4 4 1 8 8</t>
+        </is>
+      </c>
+      <c r="B347" t="n">
+        <v>1</v>
+      </c>
+      <c r="C347" t="n">
+        <v>0.5459061155652063</v>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="inlineStr">
+        <is>
+          <t>ওয়ালাইকুমুস সালাম আসসালামু আলাইকুম কে আপনি? এবং কাকে চাই?</t>
+        </is>
+      </c>
+      <c r="B348" t="n">
+        <v>0</v>
+      </c>
+      <c r="C348" t="n">
+        <v>0.8728025962973578</v>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="inlineStr">
+        <is>
+          <t>&lt;0528752&gt; AC Power Failure</t>
+        </is>
+      </c>
+      <c r="B349" t="n">
+        <v>1</v>
+      </c>
+      <c r="C349" t="n">
+        <v>0.7814093122815149</v>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="inlineStr">
+        <is>
+          <t>Nagios:eth9 Bandwidth - Outbound Host: exadomdbracp5 IP: 10.188.201.123 CRITICAL: Bytes_sent was 1206.05 MB/s 16/06/2025 00:10:38</t>
+        </is>
+      </c>
+      <c r="B350" t="n">
+        <v>0</v>
+      </c>
+      <c r="C350" t="n">
+        <v>0.736812364068125</v>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="inlineStr">
+        <is>
+          <t>Nagios:eth9 Bandwidth - Outbound Host: exadomdbracp5 IP: 10.188.201.123 CRITICAL: Bytes_sent was 1206.05 MB/s 16/06/2025 00:10:38</t>
+        </is>
+      </c>
+      <c r="B351" t="n">
+        <v>0</v>
+      </c>
+      <c r="C351" t="n">
+        <v>0.736812364068125</v>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" t="inlineStr">
+        <is>
+          <t>#vivo#simc##862241033847002#1#89601624050700854110#</t>
+        </is>
+      </c>
+      <c r="B352" t="n">
+        <v>1</v>
+      </c>
+      <c r="C352" t="n">
+        <v>0.6699446330403345</v>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="inlineStr">
+        <is>
+          <t>&lt;0528752&gt; AC Power Restored</t>
+        </is>
+      </c>
+      <c r="B353" t="n">
+        <v>1</v>
+      </c>
+      <c r="C353" t="n">
+        <v>0.6193467269276636</v>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="inlineStr">
+        <is>
+          <t>Call From HQ Jessy Congratulations For You FRxx P01N TRY Gam3 Whatsap : 6 0 1 3 4 4 4 4 1 8 8</t>
+        </is>
+      </c>
+      <c r="B354" t="n">
+        <v>1</v>
+      </c>
+      <c r="C354" t="n">
+        <v>0.5459061155652063</v>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="inlineStr">
+        <is>
+          <t>https://images.app.goo.gl/3fsFEcNTAXyoPA4Z8</t>
+        </is>
+      </c>
+      <c r="B355" t="n">
+        <v>0</v>
+      </c>
+      <c r="C355" t="n">
+        <v>0.5966895332003577</v>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="inlineStr">
+        <is>
+          <t>Lulisan hg jd mcm mn</t>
+        </is>
+      </c>
+      <c r="B356" t="n">
+        <v>0</v>
+      </c>
+      <c r="C356" t="n">
+        <v>0.8792976548338873</v>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="inlineStr">
+        <is>
+          <t>明早出门是吗?注意安全</t>
+        </is>
+      </c>
+      <c r="B357" t="n">
+        <v>0</v>
+      </c>
+      <c r="C357" t="n">
+        <v>0.7028707375193579</v>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="inlineStr">
+        <is>
+          <t>‎Mari bersembang di WhatsApp! Ia cepat, mudah dan selamat untuk membuat panggilan dan menghantar mesej secara percuma. Dapatkannya di</t>
+        </is>
+      </c>
+      <c r="B358" t="n">
+        <v>1</v>
+      </c>
+      <c r="C358" t="n">
+        <v>0.7218469868039148</v>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="inlineStr">
+        <is>
+          <t>U388: 嘿! 您升级后的RM50免费积分感到孤独。赶快在它们离开前领取吧!u388my{dot}com</t>
+        </is>
+      </c>
+      <c r="B359" t="n">
+        <v>1</v>
+      </c>
+      <c r="C359" t="n">
+        <v>0.6729929337834375</v>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="inlineStr">
+        <is>
+          <t>&lt;0528752&gt; AC Power Failure</t>
+        </is>
+      </c>
+      <c r="B360" t="n">
+        <v>1</v>
+      </c>
+      <c r="C360" t="n">
+        <v>0.7814093122815149</v>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" t="inlineStr">
+        <is>
+          <t>Tak pun kau duduk je dalam bilik kau tu diam2 , dia panggil ke buat bodh je kau diam jee .. mak tak bagi aku kawan dan jumpa dia dah .</t>
+        </is>
+      </c>
+      <c r="B361" t="n">
+        <v>0</v>
+      </c>
+      <c r="C361" t="n">
+        <v>0.8219634701872809</v>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" t="inlineStr">
+        <is>
+          <t>&lt;0528752&gt; AC Power Restored</t>
+        </is>
+      </c>
+      <c r="B362" t="n">
+        <v>1</v>
+      </c>
+      <c r="C362" t="n">
+        <v>0.619346071276571</v>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" t="inlineStr">
+        <is>
+          <t>UOB-RSA Token User: Your QR Code import/ZIP File Password is !Numb456</t>
+        </is>
+      </c>
+      <c r="B363" t="n">
+        <v>0</v>
+      </c>
+      <c r="C363" t="n">
+        <v>0.5319907178545935</v>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" t="inlineStr">
+        <is>
+          <t>*V 2.1.0* Stn Name:BANTING 16/06/2025 00:12:02 Status:RF START Int=9.0mm/60min Daily=7.0mm Monthly=102.0mm Yearly=998.0mm Bat:13.2V</t>
+        </is>
+      </c>
+      <c r="B364" t="n">
+        <v>1</v>
+      </c>
+      <c r="C364" t="n">
+        <v>0.8490828762387292</v>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" t="inlineStr">
+        <is>
+          <t>https://play.google.com/store/apps/details?id=castle.heroes.tower.defense.kingdom.magic.battle.archer</t>
+        </is>
+      </c>
+      <c r="B365" t="n">
+        <v>0</v>
+      </c>
+      <c r="C365" t="n">
+        <v>0.5624122132922156</v>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" t="inlineStr">
+        <is>
+          <t>xblock laa aku deactive semua social media aku...ws no se lg ade je qil 4413 tu..</t>
+        </is>
+      </c>
+      <c r="B366" t="n">
+        <v>0</v>
+      </c>
+      <c r="C366" t="n">
+        <v>0.6755233516360266</v>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" t="inlineStr">
+        <is>
+          <t>‎Mari bersembang di WhatsApp! Ia cepat, mudah dan selamat untuk membuat panggilan dan menghantar mesej secara percuma. Dapatkannya di</t>
+        </is>
+      </c>
+      <c r="B367" t="n">
+        <v>1</v>
+      </c>
+      <c r="C367" t="n">
+        <v>0.7218469868039148</v>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" t="inlineStr">
+        <is>
+          <t>OPEN P-2506236: Process unavailable on Process WebLogic CAMSdomain ReflexManagedServer1:Process unavailable</t>
+        </is>
+      </c>
+      <c r="B368" t="n">
+        <v>1</v>
+      </c>
+      <c r="C368" t="n">
+        <v>0.7746053228711145</v>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" t="inlineStr">
+        <is>
+          <t>https://share.icloud.com/photos/001PVwZTx7M8sCAAum-c7_2rA</t>
+        </is>
+      </c>
+      <c r="B369" t="n">
+        <v>0</v>
+      </c>
+      <c r="C369" t="n">
+        <v>0.8615509678984625</v>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" t="inlineStr">
+        <is>
+          <t>https://share.icloud.com/photos/001PVwZTx7M8sCAAum-c7_2rA</t>
+        </is>
+      </c>
+      <c r="B370" t="n">
+        <v>0</v>
+      </c>
+      <c r="C370" t="n">
+        <v>0.8615509678984625</v>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" t="inlineStr">
+        <is>
+          <t>https://share.icloud.com/photos/001PVwZTx7M8sCAAum-c7_2rA</t>
+        </is>
+      </c>
+      <c r="B371" t="n">
+        <v>0</v>
+      </c>
+      <c r="C371" t="n">
+        <v>0.8615509678984625</v>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" t="inlineStr">
+        <is>
+          <t>Selamat Malam, assalamualaikum</t>
+        </is>
+      </c>
+      <c r="B372" t="n">
+        <v>0</v>
+      </c>
+      <c r="C372" t="n">
+        <v>0.8471347798968298</v>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" t="inlineStr">
+        <is>
+          <t>https://share.icloud.com/photos/001PVwZTx7M8sCAAum-c7_2rA</t>
+        </is>
+      </c>
+      <c r="B373" t="n">
+        <v>0</v>
+      </c>
+      <c r="C373" t="n">
+        <v>0.8615509678984625</v>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" t="inlineStr">
+        <is>
+          <t>‎Let's chat on WhatsApp! It's a fast, simple, and secure app we can use to message and call each other for free. Get it at</t>
+        </is>
+      </c>
+      <c r="B374" t="n">
+        <v>1</v>
+      </c>
+      <c r="C374" t="n">
+        <v>0.5626952538823145</v>
       </c>
     </row>
   </sheetData>

--- a/data/unlabel/unlabel_data.xlsx
+++ b/data/unlabel/unlabel_data.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C374"/>
+  <dimension ref="A1:C323"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,807 +448,807 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Let's chat on WhatsApp! It's a fast, simple, and secure app we can use to message and call each other for free. Get it at https://whatsapp.com/dl/</t>
+          <t>https://temu.com/s/Ax5rP10Tege3uUd</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>0.7983353284853723</v>
+        <v>0.7441857919800906</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Amoi sini company goldenbet99,apa kabar sudah bossku,lama dah tak try spin mari.jackpot,free game,Bonusgame menanti anda. Web ; goldenbet99 .com</t>
+          <t>To join the meeting on Google Meet, click this link: https://meet.google.com/gow-xyon-gdu Or open Meet and enter this code: gow-xyon-gdu</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C3" t="n">
-        <v>0.6317334321993615</v>
+        <v>0.7086298928368716</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Let's chat on WhatsApp! It's a fast, simple, and secure app we can use to message and call each other for free. Get it at https://whatsapp.com/dl/</t>
+          <t>https://temu.com/s/Ax5rP10Tege3uUd</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C4" t="n">
-        <v>0.7983353284853723</v>
+        <v>0.7441857919800906</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>{Kasino-77} : Weekend Big W1n Package! Claim 1st Bns Slot 3O%</t>
+          <t>https://temu.com/s/Ax5rP10Tege3uUd</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C5" t="n">
-        <v>0.7444172648447778</v>
+        <v>0.7441857919800906</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>နင်လိုမိန်းမငါ့နဲ့ပျက်ပီ</t>
+          <t>https://temu.com/s/Ax5rP10Tege3uUd</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>0</v>
       </c>
       <c r="C6" t="n">
-        <v>0.806330219123957</v>
+        <v>0.7441857919800906</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>没看到那性感叻</t>
+          <t>NK DTG SERVIS BLH KE AYU</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>0</v>
       </c>
       <c r="C7" t="n">
-        <v>0.6167427750569556</v>
+        <v>0.7021383509743838</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Air lbih</t>
+          <t>https://temu.com/s/Ax5rP10Tege3uUd</t>
         </is>
       </c>
       <c r="B8" t="n">
         <v>0</v>
       </c>
       <c r="C8" t="n">
-        <v>0.848418340299723</v>
+        <v>0.7441857919800906</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Sorry k mun akw minak btak bie mumeng</t>
+          <t>https://images.app.goo.gl/nbNkyb5j611ywntr8</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C9" t="n">
-        <v>0.728383794214132</v>
+        <v>0.7423646912682681</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>89 dragon</t>
+          <t>Call From HQ Jessy Congratulations For You FRxx P01N TRY Gam3 Whatsap : 6 0 1 3 4 4 4 4 1 8 8</t>
         </is>
       </c>
       <c r="B10" t="n">
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>0.894444152925608</v>
+        <v>0.5216650829423098</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Let's chat on WhatsApp! It's a fast, simple, and secure app we can use to message and call each other for free. Get it at https://whatsapp.com/dl/</t>
+          <t>Amoi sini company goldenbet99,apa kabar sudah bossku,lama dah tak try spin mari.jackpot,free game,Bonusgame menanti anda. Web ; goldenbet99 .com</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>0.7983353284853723</v>
+        <v>0.6442074046242862</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Pls bagi Mak fon kejap boleh....nanti Miss call...sy call balik..tq</t>
+          <t>&lt;0528752&gt; AC Power Failure</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C12" t="n">
-        <v>0.8585644664508079</v>
+        <v>0.7062027587782712</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Let's chat on WhatsApp! It's a fast, simple, and secure app we can use to message and call each other for free. Get it at https://whatsapp.com/dl/</t>
+          <t>https://temu.com/s/Ax5rP10Tege3uUd</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>0.7983353284853723</v>
+        <v>0.7441857919800906</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Empangan Batu - ID:WPKL1001RF 2025-06-16 00:00:53 RF Light Rain PassHour:1mm</t>
+          <t>&lt;0528752&gt; AC Power Restored</t>
         </is>
       </c>
       <c r="B14" t="n">
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>0.5338092593210961</v>
+        <v>0.5447595848929258</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Ada kes oncall di green zone.pt nama nusaibah 6 tahun.laceration kt lower lip</t>
+          <t>#vivo#simc##862241033847002#1#89601624050700854110#</t>
         </is>
       </c>
       <c r="B15" t="n">
         <v>1</v>
       </c>
       <c r="C15" t="n">
-        <v>0.8739547876375939</v>
+        <v>0.5939794316183896</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Let's chat on WhatsApp! It's a fast, simple, and secure app we can use to message and call each other for free. Get it at https://whatsapp.com/dl/</t>
+          <t>Fr66 RM 50 dah masuk 1D! Kla1m Now!New Cus 80% C4sh2u 3v.ent Open! AFB x 0NEG0LD KLA1M: 016 - 367 6116 Stop SMS? Reply STOP. ffneank;</t>
         </is>
       </c>
       <c r="B16" t="n">
         <v>1</v>
       </c>
       <c r="C16" t="n">
-        <v>0.7983353284853723</v>
+        <v>0.886268986691174</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>742</t>
+          <t>MBS66: 登录有惊喜「50个无法拒绝的理由」您的账户已获得免费奖金RM50(仅限今日)立即前往MBS66my{dot}com领取!</t>
         </is>
       </c>
       <c r="B17" t="n">
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>0.5735026451092933</v>
+        <v>0.6377769575226931</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>1763, Jalan Jambu 24 81400 Senai 柔佛州 马来西亚</t>
+          <t>OPEN P-2506236: Process unavailable on Process WebLogic CAMSdomain ReflexManagedServer1:Process unavailable</t>
         </is>
       </c>
       <c r="B18" t="n">
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>0.7762748745936181</v>
+        <v>0.7161218657385678</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Mudah: I'm interested in your ad on Mudah Flat Pandan Mewah, please share more details with me.</t>
+          <t>REG-REQ?v=3;t=F2BC72F356E50F67BBECE2736033B56EBDE73C3A4288FD8D23C3238C52E9831F;r=1714407122</t>
         </is>
       </c>
       <c r="B19" t="n">
         <v>1</v>
       </c>
       <c r="C19" t="n">
-        <v>0.6532077936190392</v>
+        <v>0.8881138696562619</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Ayo chat di WhatsApp, aplikasi yang cepat, sederhana, dan aman untuk berkirim pesan dan menelepon secara gratis. Dapatkan di https://whatsapp.com/dl/</t>
+          <t>2033</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C20" t="n">
-        <v>0.6300301404935096</v>
+        <v>0.7395542397391172</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Ayo chat di WhatsApp, aplikasi yang cepat, sederhana, dan aman untuk berkirim pesan dan menelepon secara gratis. Dapatkan di https://whatsapp.com/dl/</t>
+          <t>GSM Alarm System in good working condition.</t>
         </is>
       </c>
       <c r="B21" t="n">
         <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>0.6300301404935096</v>
+        <v>0.6415306196320681</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Ayo chat di WhatsApp, aplikasi yang cepat, sederhana, dan aman untuk berkirim pesan dan menelepon secara gratis. Dapatkan di https://whatsapp.com/dl/</t>
+          <t>RESOLVED P-2506236: Process unavailable on Process WebLogic CAMSdomain ReflexManagedServer1:Process unavailable</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C22" t="n">
-        <v>0.6300301404935096</v>
+        <v>0.8649329080473752</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>sikmok2</t>
+          <t>REG-REQ?v=3;t=F2BC72F356E50F67BBECE2736033B56EBDE73C3A4288FD8D23C3238C52E9831F;r=1714407122</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C23" t="n">
-        <v>0.7342517825108741</v>
+        <v>0.8881138696562619</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Let's chat on WhatsApp! It's a fast, simple, and secure app we can use to message and call each other for free. Get it at https://whatsapp.com/dl/</t>
+          <t>&lt;0528752&gt; AC Power Failure</t>
         </is>
       </c>
       <c r="B24" t="n">
         <v>1</v>
       </c>
       <c r="C24" t="n">
-        <v>0.7983353284853723</v>
+        <v>0.7062027587782712</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Takpelah. Saya tau dah ada yg temankan awak sleepcall that's why taknak dgr suda suara perempuan yg gaya mcm sial babi ni. Takpelah, sorry ganggu awak dgn c dia. Okaylah, thanks sebab sudi dgrkan suara awak utk kali yg terakhir. Okaylah saya akan menjauh dan undur diri duluan</t>
+          <t>REG-REQ?v=3;t=F2BC72F356E50F67BBECE2736033B56EBDE73C3A4288FD8D23C3238C52E9831F;r=1714407122</t>
         </is>
       </c>
       <c r="B25" t="n">
         <v>1</v>
       </c>
       <c r="C25" t="n">
-        <v>0.5046023277300622</v>
+        <v>0.8881138696562619</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>E T: Wlcm u, MAX-M u=1441627946Q6 p=EEee7673 on:16/06 00:01:29</t>
+          <t>B121=1087</t>
         </is>
       </c>
       <c r="B26" t="n">
         <v>1</v>
       </c>
       <c r="C26" t="n">
-        <v>0.7761575130480554</v>
+        <v>0.714167906273541</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Bendar mangkang keting mangkang butuh pukik dia.. Nya line ndai nemu clear</t>
+          <t>&lt;0528752&gt; AC Power Restored</t>
         </is>
       </c>
       <c r="B27" t="n">
         <v>1</v>
       </c>
       <c r="C27" t="n">
-        <v>0.7950637487429406</v>
+        <v>0.5447595848929258</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>tirak please me back ok</t>
+          <t>Send this code to verify your phone number with Google. Do not edit this message. (lBCIuzAHqfy5)</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C28" t="n">
-        <v>0.7647222133618568</v>
+        <v>0.8713160886656613</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>854461697560978</t>
+          <t>Amoi sini company goldenbet99,apa kabar sudah bossku,lama dah tak try spin mari.jackpot,free game,Bonusgame menanti anda. Web ; goldenbet99 .com</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C29" t="n">
-        <v>0.8353436140078332</v>
+        <v>0.6442074046242862</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>晚安,亲爱的老婆&lt;EMO&gt;&lt;EMO&gt;&lt;EMO&gt;&lt;EMO&gt;</t>
+          <t>Set your Life360 location permissions to 'Always' for Life360 to work correctly.</t>
         </is>
       </c>
       <c r="B30" t="n">
         <v>1</v>
       </c>
       <c r="C30" t="n">
-        <v>0.5935865787524011</v>
+        <v>0.8023144140135617</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Safety and health is very important so when you reach home (Penang) please kindly let me know as well as kejashini akka Please be safe and safely reach home ,Thiveya ji Wherever you go please be safe and careful always, stay safe always,Thiveya ji As well as health please take care of your health,Thiveya thangapulla &lt;EMO&gt;</t>
+          <t>https://i.lf360.co/LocationPermission</t>
         </is>
       </c>
       <c r="B31" t="n">
         <v>0</v>
       </c>
       <c r="C31" t="n">
-        <v>0.5116615148526404</v>
+        <v>0.8667694196808963</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Amoi sini company goldenbet99,apa kabar sudah bossku,lama dah tak try spin mari.jackpot,free game,Bonusgame menanti anda. Web ; goldenbet99 .com</t>
+          <t>https://i.lf360.co/LocationPermission</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C32" t="n">
-        <v>0.6317334321993615</v>
+        <v>0.8667706415761142</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Amoi sini company goldenbet99,apa kabar sudah bossku,lama dah tak try spin mari.jackpot,free game,Bonusgame menanti anda. Web ; goldenbet99 .com</t>
+          <t>https://i.lf360.co/LocationPermission</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C33" t="n">
-        <v>0.6317334321993615</v>
+        <v>0.8667706415761142</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Mudah: I'm interested in your ad on Mudah Pesona Villa Apartment Unit For Rent, please share more details with me.</t>
+          <t>https://i.lf360.co/LocationPermission</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C34" t="n">
-        <v>0.6832302955645349</v>
+        <v>0.8667694196808963</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Amoi sini company goldenbet99,apa kabar sudah bossku,lama dah tak try spin mari.jackpot,free game,Bonusgame menanti anda. Web ; goldenbet99 .com</t>
+          <t>HENG2 844 JOM CUBA LUCK ADA FREE 8 WS - 60-16-954-6041</t>
         </is>
       </c>
       <c r="B35" t="n">
         <v>1</v>
       </c>
       <c r="C35" t="n">
-        <v>0.5124115143220297</v>
+        <v>0.8789174690138669</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Takpelah. Saya tau dah ada yg temankan awak sleepcall that's why taknak dgr suda suara perempuan yg gaya mcm sial babi ni. Takpelah, sorry ganggu awak dgn c dia. Okaylah, thanks sebab sudi dgrkan suara awak utk kali yg terakhir. Okaylah saya akan menjauh dan undur diri duluan</t>
+          <t>https://i.lf360.co/LocationPermission</t>
         </is>
       </c>
       <c r="B36" t="n">
         <v>0</v>
       </c>
       <c r="C36" t="n">
-        <v>0.6064002718527445</v>
+        <v>0.8667706415761142</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>(764090) okywpwzPoV</t>
+          <t>xPortalNet:2025/06/16|00:13:16|COMMAND CTR ENT|COMMAND CTR ENT|FFFFFFFFFFFFFFFF|(PE)Door Left Open</t>
         </is>
       </c>
       <c r="B37" t="n">
         <v>1</v>
       </c>
       <c r="C37" t="n">
-        <v>0.7623781357209555</v>
+        <v>0.8583556547057004</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Name : Ajit Budget : as low as possible when move in : 1july How many ppl stay : 8 Nepal friend or family : workers Occupation : security Working company name/ school name : security company Local / Foreigner : Race : nepal Tenancy 1 or 2 years : 2</t>
+          <t>https://i.lf360.co/LocationPermission</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C38" t="n">
-        <v>0.5326576624314657</v>
+        <v>0.8667694196808963</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>BX99:您被选了(ong111)!恭喜您获得228次免费旋转。存RM50就解锁!bx99my{dot}com</t>
+          <t>25O616 OO12 (1) py8O8 18/O6-21/O6-22/O6 *MPT 4272=1.O2B 2724=1.O2B 223O=1.O2B 4272=1.O2B (IBox) 223O=1.O2B (IBox) GT=45.9O</t>
         </is>
       </c>
       <c r="B39" t="n">
         <v>0</v>
       </c>
       <c r="C39" t="n">
-        <v>0.5293791498739847</v>
+        <v>0.6433262095559268</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Oklah....goodluck kenal laki lain...aku doakan impian hang kawin dan jadi anjing pada azam tercapai. Azam lelaki terhebat kan</t>
+          <t>011-1413 4732 ni no arissa</t>
         </is>
       </c>
       <c r="B40" t="n">
         <v>0</v>
       </c>
       <c r="C40" t="n">
-        <v>0.8593468870718607</v>
+        <v>0.7779207692254214</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Ayo chat di WhatsApp, aplikasi yang cepat, sederhana, dan aman untuk berkirim pesan dan menelepon secara gratis. Dapatkan di https://whatsapp.com/dl/</t>
+          <t>Let's chat on WhatsApp! It's a fast, simple, and secure app we can use to message and call each other for free. Get it at https://whatsapp.com/dl/</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C41" t="n">
-        <v>0.7370392288763651</v>
+        <v>0.7418096198927732</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>BX99:您被选了(marioccc)!恭喜您获得228次免费旋转。存RM50就解锁!bx99my{dot}com</t>
+          <t>Amoi sini company goldenbet99,apa kabar sudah bossku,lama dah tak try spin mari.jackpot,free game,Bonusgame menanti anda. Web ; goldenbet99 .com</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C42" t="n">
-        <v>0.722986975709664</v>
+        <v>0.6442074046242862</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Let's use Meet to video chat: https://duo.app.goo.gl/2Dtc2LZ</t>
+          <t>Let's chat on WhatsApp! It's a fast, simple, and secure app we can use to message and call each other for free. Get it at https://whatsapp.com/dl/</t>
         </is>
       </c>
       <c r="B43" t="n">
         <v>1</v>
       </c>
       <c r="C43" t="n">
-        <v>0.8778616581361166</v>
+        <v>0.7418096198927732</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>好消息!您的限时优惠从188次免费旋转增加至208次,仅需存款RM50!立即在12HUATmy{dot}com领取!</t>
+          <t>{Kasino-77} : Weekend Big W1n Package! Claim 1st Bns Slot 3O%</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C44" t="n">
-        <v>0.778443256417977</v>
+        <v>0.5291489229310183</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Let's use Meet to video chat: https://duo.app.goo.gl/2Dtc2LZ</t>
+          <t>Sorry k mun akw minak btak bie mumeng</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C45" t="n">
-        <v>0.8778616581361166</v>
+        <v>0.7687868044484286</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>selamat ulang tahun kelahiran ya roma syg. moga kau panjang umur, murah rezeki dan diberikan kesihatan yg baik. dihari yg indah ak mau mntak maaf ya kt kau sbb slama 3tahun kita brkwan ak xprnah lakukan apa pn yg baik utk kau dan ak pn xtau nk explain apa lg sbb ak ckap ap pn mcm takda gunanya gara2 ak prnah tpu kau. maafkn ak yaa roma. ak harap kau bisa bhgia tnpa ak di samping kau dan ak brharap ada yg bisa bhgiakn kau hgga akhir hayat kau yaa. maafkn ak dan ak ikhlas maksudkn. terima kasih dh byk brkorban utk ak. ak sayangkn kau dr dlu ikhlas dan xprnah ada niat jahat. tu aja ak bisa ckap.</t>
+          <t>Let's chat on WhatsApp! It's a fast, simple, and secure app we can use to message and call each other for free. Get it at https://whatsapp.com/dl/</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C46" t="n">
-        <v>0.8310553040106424</v>
+        <v>0.7418096198927732</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Ok ...Jaga diri molek ..jgn susoh² Hati... ada masa Kita lepak skali</t>
+          <t>Let's chat on WhatsApp! It's a fast, simple, and secure app we can use to message and call each other for free. Get it at https://whatsapp.com/dl/</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C47" t="n">
-        <v>0.6720697488386759</v>
+        <v>0.7418096198927732</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Jom cuba aplikasi WhatsApp Business, saya menggunakannya untuk berhubung dengan pelanggan saya. Dapatkannya secara percuma di https://whatsapp.com/biz/</t>
+          <t>Empangan Batu - ID:WPKL1001RF 2025-06-16 00:00:53 RF Light Rain PassHour:1mm</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C48" t="n">
-        <v>0.7957651410500876</v>
+        <v>0.6774156556237368</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Jom cuba aplikasi WhatsApp Business, saya menggunakannya untuk berhubung dengan pelanggan saya. Dapatkannya secara percuma di https://whatsapp.com/biz/</t>
+          <t>Ada kes oncall di green zone.pt nama nusaibah 6 tahun.laceration kt lower lip</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C49" t="n">
-        <v>0.7957651410500876</v>
+        <v>0.5481092796433596</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Ok ...Jaga diri molek ..jgn susoh² Hati... ada masa Kita lepak skali</t>
+          <t>Let's chat on WhatsApp! It's a fast, simple, and secure app we can use to message and call each other for free. Get it at https://whatsapp.com/dl/</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C50" t="n">
-        <v>0.6720697488386759</v>
+        <v>0.7418097987067075</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>HAHAHHAHA INI BUDAK SUKA TIDO PUKUL 4 PAGII NI</t>
+          <t>742</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C51" t="n">
-        <v>0.5155193005006186</v>
+        <v>0.7687757775891452</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>https://maps.apple.com/?ll=1.62042,103.72699&amp;q=Location</t>
+          <t>1763, Jalan Jambu 24 81400 Senai 柔佛州 马来西亚</t>
         </is>
       </c>
       <c r="B52" t="n">
         <v>0</v>
       </c>
       <c r="C52" t="n">
-        <v>0.5289406981070169</v>
+        <v>0.5381994114030032</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>https://maps.apple.com/?ll=1.62042,103.72699&amp;q=Location</t>
+          <t>Mudah: I'm interested in your ad on Mudah Flat Pandan Mewah, please share more details with me.</t>
         </is>
       </c>
       <c r="B53" t="n">
         <v>0</v>
       </c>
       <c r="C53" t="n">
-        <v>0.5289406981070169</v>
+        <v>0.5915003881562381</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>https://maps.apple.com/?ll=1.62042,103.72699&amp;q=Location</t>
+          <t>Ayo chat di WhatsApp, aplikasi yang cepat, sederhana, dan aman untuk berkirim pesan dan menelepon secara gratis. Dapatkan di https://whatsapp.com/dl/</t>
         </is>
       </c>
       <c r="B54" t="n">
         <v>0</v>
       </c>
       <c r="C54" t="n">
-        <v>0.5289406981070169</v>
+        <v>0.6099825964081912</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>https://maps.apple.com/?ll=1.62042,103.72699&amp;q=Location</t>
+          <t>Ayo chat di WhatsApp, aplikasi yang cepat, sederhana, dan aman untuk berkirim pesan dan menelepon secara gratis. Dapatkan di https://whatsapp.com/dl/</t>
         </is>
       </c>
       <c r="B55" t="n">
         <v>0</v>
       </c>
       <c r="C55" t="n">
-        <v>0.5289410557348856</v>
+        <v>0.6099825964081912</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>7 thun bersabar, last2 sbb hal online..putus Tahniah.. Bye!</t>
+          <t>Ayo chat di WhatsApp, aplikasi yang cepat, sederhana, dan aman untuk berkirim pesan dan menelepon secara gratis. Dapatkan di https://whatsapp.com/dl/</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C56" t="n">
-        <v>0.5192491207520834</v>
+        <v>0.6099825964081912</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>E T: Wlcm u, MAX-M u=1441653931Q6 p=IIii2672 on:16/06 00:02:35</t>
+          <t>Let's chat on WhatsApp! It's a fast, simple, and secure app we can use to message and call each other for free. Get it at https://whatsapp.com/dl/</t>
         </is>
       </c>
       <c r="B57" t="n">
         <v>1</v>
       </c>
       <c r="C57" t="n">
-        <v>0.6583528314034811</v>
+        <v>0.7418096198927732</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>4那享受当小三虐妻的求主推到火海去那被后伤害我和婚姻求主不要放过他们以恶报善火&lt;EMO&gt;海去你看到恶计淫 pls come to those against the hurt our marriage opress spouse Abba Jesus saw, UArise!</t>
+          <t>Takpelah. Saya tau dah ada yg temankan awak sleepcall that's why taknak dgr suda suara perempuan yg gaya mcm sial babi ni. Takpelah, sorry ganggu awak dgn c dia. Okaylah, thanks sebab sudi dgrkan suara awak utk kali yg terakhir. Okaylah saya akan menjauh dan undur diri duluan</t>
         </is>
       </c>
       <c r="B58" t="n">
         <v>0</v>
       </c>
       <c r="C58" t="n">
-        <v>0.7681363429625162</v>
+        <v>0.8461435303795962</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>https://maps.apple.com/?ll=1.62042,103.72699&amp;q=Location</t>
+          <t>E T: Wlcm u, MAX-M u=1441627946Q6 p=EEee7673 on:16/06 00:01:29</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C59" t="n">
-        <v>0.5289406981070169</v>
+        <v>0.5855098500143857</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Ok ...Jaga diri molek ..jgn susoh² Hati... ada masa Kita lepak skali</t>
+          <t>Bendar mangkang keting mangkang butuh pukik dia.. Nya line ndai nemu clear</t>
         </is>
       </c>
       <c r="B60" t="n">
         <v>0</v>
       </c>
       <c r="C60" t="n">
-        <v>0.6720697488386759</v>
+        <v>0.6826826200593142</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Amoi sini company goldenbet99,apa kabar sudah bossku,lama dah tak try spin mari.jackpot,free game,Bonusgame menanti anda. Web ; goldenbet99 .com</t>
+          <t>854461697560978</t>
         </is>
       </c>
       <c r="B61" t="n">
         <v>1</v>
       </c>
       <c r="C61" t="n">
-        <v>0.5124115143220297</v>
+        <v>0.598238004673657</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Bos ni nmor Wasap saye 01116514506 ni saye budak Indonesia</t>
+          <t>晚安,亲爱的老婆&lt;EMO&gt;&lt;EMO&gt;&lt;EMO&gt;&lt;EMO&gt;</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C62" t="n">
-        <v>0.656510392228829</v>
+        <v>0.6937436328042178</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Jom cuba aplikasi WhatsApp Business, saya menggunakannya untuk berhubung dengan pelanggan saya. Dapatkannya secara percuma di https://whatsapp.com/biz/</t>
+          <t>Safety and health is very important so when you reach home (Penang) please kindly let me know as well as kejashini akka Please be safe and safely reach home ,Thiveya ji Wherever you go please be safe and careful always, stay safe always,Thiveya ji As well as health please take care of your health,Thiveya thangapulla &lt;EMO&gt;</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C63" t="n">
-        <v>0.7957651410500876</v>
+        <v>0.8376371131051211</v>
       </c>
     </row>
     <row r="64">
@@ -1258,751 +1258,751 @@
         </is>
       </c>
       <c r="B64" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C64" t="n">
-        <v>0.5124115143220297</v>
+        <v>0.6442074046242862</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>sy ta slh kan awk klau awk na benci sy . tak nak contact sy da lepas ni. da sy mintak maaf klau hadir sy dlm idup awk, buat idup awk beban. insAllah. sy ada rezeki lepas ni. sy ta janji , tpi sy cuba tolong bayar balik duit2 yg awk keluar utk sy dgn ank. spnjg awk dgn sy.</t>
+          <t>Amoi sini company goldenbet99,apa kabar sudah bossku,lama dah tak try spin mari.jackpot,free game,Bonusgame menanti anda. Web ; goldenbet99 .com</t>
         </is>
       </c>
       <c r="B65" t="n">
         <v>0</v>
       </c>
       <c r="C65" t="n">
-        <v>0.5249406900007852</v>
+        <v>0.6442074046242862</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Amoi sini company goldenbet99,apa kabar sudah bossku,lama dah tak try spin mari.jackpot,free game,Bonusgame menanti anda. Web ; goldenbet99 .com</t>
+          <t>Mudah: I'm interested in your ad on Mudah Pesona Villa Apartment Unit For Rent, please share more details with me.</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C66" t="n">
-        <v>0.5561876463185136</v>
+        <v>0.5953492388833194</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Ok ...Jaga diri molek ..jgn susoh² Hati... ada masa Kita lepak skali</t>
+          <t>Amoi sini company goldenbet99,apa kabar sudah bossku,lama dah tak try spin mari.jackpot,free game,Bonusgame menanti anda. Web ; goldenbet99 .com</t>
         </is>
       </c>
       <c r="B67" t="n">
         <v>0</v>
       </c>
       <c r="C67" t="n">
-        <v>0.6249765289534743</v>
+        <v>0.6442074046242862</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Ok ...Jaga diri molek ..jgn susoh² Hati... ada masa Kita lepak skali</t>
+          <t>Takpelah. Saya tau dah ada yg temankan awak sleepcall that's why taknak dgr suda suara perempuan yg gaya mcm sial babi ni. Takpelah, sorry ganggu awak dgn c dia. Okaylah, thanks sebab sudi dgrkan suara awak utk kali yg terakhir. Okaylah saya akan menjauh dan undur diri duluan</t>
         </is>
       </c>
       <c r="B68" t="n">
         <v>0</v>
       </c>
       <c r="C68" t="n">
-        <v>0.6249760223139937</v>
+        <v>0.8461435303795962</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>https://youtube.com/shorts/fuqANpZirh8?si=iQQrb0BO1qZukNSX</t>
+          <t>(764090) okywpwzPoV</t>
         </is>
       </c>
       <c r="B69" t="n">
         <v>1</v>
       </c>
       <c r="C69" t="n">
-        <v>0.672743992734987</v>
+        <v>0.5670626296889157</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>HAPPY BIRTHDAY UNGKU SEMOGA PNJG UMUR SORRY AKU TK JOIN TADi</t>
+          <t>Name : Ajit Budget : as low as possible when move in : 1july How many ppl stay : 8 Nepal friend or family : workers Occupation : security Working company name/ school name : security company Local / Foreigner : Race : nepal Tenancy 1 or 2 years : 2</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C70" t="n">
-        <v>0.7055777477513139</v>
+        <v>0.6734838352311282</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>https://youtube.com/shorts/fuqANpZirh8?si=iQQrb0BO1qZukNSX</t>
+          <t>BX99:您被选了(ong111)!恭喜您获得228次免费旋转。存RM50就解锁!bx99my{dot}com</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C71" t="n">
-        <v>0.672743992734987</v>
+        <v>0.5701539383042483</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>https://youtube.com/shorts/fuqANpZirh8?si=iQQrb0BO1qZukNSX</t>
+          <t>Ayo chat di WhatsApp, aplikasi yang cepat, sederhana, dan aman untuk berkirim pesan dan menelepon secara gratis. Dapatkan di https://whatsapp.com/dl/</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C72" t="n">
-        <v>0.672743992734987</v>
+        <v>0.6099825964081912</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Hampir 3 bln mas buat aku mcm ni</t>
+          <t>BX99:您被选了(marioccc)!恭喜您获得228次免费旋转。存RM50就解锁!bx99my{dot}com</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C73" t="n">
-        <v>0.8973616195429976</v>
+        <v>0.626545561779675</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>https://youtube.com/shorts/fuqANpZirh8?si=iQQrb0BO1qZukNSX</t>
+          <t>Let's use Meet to video chat: https://duo.app.goo.gl/2Dtc2LZ</t>
         </is>
       </c>
       <c r="B74" t="n">
         <v>1</v>
       </c>
       <c r="C74" t="n">
-        <v>0.672743992734987</v>
+        <v>0.8493722810637326</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>https://youtube.com/shorts/fuqANpZirh8?si=iQQrb0BO1qZukNSX</t>
+          <t>好消息!您的限时优惠从188次免费旋转增加至208次,仅需存款RM50!立即在12HUATmy{dot}com领取!</t>
         </is>
       </c>
       <c r="B75" t="n">
         <v>1</v>
       </c>
       <c r="C75" t="n">
-        <v>0.672743992734987</v>
+        <v>0.7141624226462217</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>https://youtube.com/shorts/fuqANpZirh8?si=iQQrb0BO1qZukNSX</t>
+          <t>Let's use Meet to video chat: https://duo.app.goo.gl/2Dtc2LZ</t>
         </is>
       </c>
       <c r="B76" t="n">
         <v>1</v>
       </c>
       <c r="C76" t="n">
-        <v>0.672743992734987</v>
+        <v>0.8493722810637326</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Salam sayang aku ni mcm mana c nana ada kurang sudah</t>
+          <t>Jom cuba aplikasi WhatsApp Business, saya menggunakannya untuk berhubung dengan pelanggan saya. Dapatkannya secara percuma di https://whatsapp.com/biz/</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C77" t="n">
-        <v>0.6113076639880355</v>
+        <v>0.6740808620344968</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Salam sayang aku ni mcm mana c nana ada kurang sudah</t>
+          <t>Jom cuba aplikasi WhatsApp Business, saya menggunakannya untuk berhubung dengan pelanggan saya. Dapatkannya secara percuma di https://whatsapp.com/biz/</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C78" t="n">
-        <v>0.6113076639880355</v>
+        <v>0.6740808620344968</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Jangan rosakkan diri . bukan tkdk jalan lain adaa . laniee kita perlukan masaa , syg sentiasa doaakan yg terbaik utk biy . syg maafkn segalaa salah silap biy . syg tkpenah pendam sikit pon . syg cumaa nk yg trbaik jaa utk biy</t>
+          <t>HAHAHHAHA INI BUDAK SUKA TIDO PUKUL 4 PAGII NI</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C79" t="n">
-        <v>0.7081667947064225</v>
+        <v>0.7646361456025271</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Ok ...Jaga diri molek ..jgn susoh² Hati... ada masa Kita lepak skali</t>
+          <t>https://maps.apple.com/?ll=1.62042,103.72699&amp;q=Location</t>
         </is>
       </c>
       <c r="B80" t="n">
         <v>0</v>
       </c>
       <c r="C80" t="n">
-        <v>0.6249765289534743</v>
+        <v>0.6215847597230105</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Bos ni nmor Wasap saye 01116514506 ni saye budak Indonesia</t>
+          <t>https://maps.apple.com/?ll=1.62042,103.72699&amp;q=Location</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C81" t="n">
-        <v>0.6931705641041581</v>
+        <v>0.6215844020951419</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Amoi sini company goldenbet99,apa kabar sudah bossku,lama dah tak try spin mari.jackpot,free game,Bonusgame menanti anda. Web ; goldenbet99 .com</t>
+          <t>https://maps.apple.com/?ll=1.62042,103.72699&amp;q=Location</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C82" t="n">
-        <v>0.5561876463185136</v>
+        <v>0.6215844020951419</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Bgsa ktrunan sawan gila bbi mmg mcm to lh prgai bbto hdop pun sial ape xde ape lgi duit ..hdop mnpu mcm to lh ..hdop pun x berkat mcm to lh</t>
+          <t>https://maps.apple.com/?ll=1.62042,103.72699&amp;q=Location</t>
         </is>
       </c>
       <c r="B83" t="n">
         <v>0</v>
       </c>
       <c r="C83" t="n">
-        <v>0.6217015219439681</v>
+        <v>0.6215844020951419</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>上 WhatsApp 对话!使用此快速、简便且安全的应用免费发消息和进行通话。下载:https://whatsapp.com/dl/</t>
+          <t>7 thun bersabar, last2 sbb hal online..putus Tahniah.. Bye!</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C84" t="n">
-        <v>0.8773306774388139</v>
+        <v>0.7185264096367984</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>KakaoTalk HgAAABIwALXuTmgAAAAAAjEABwAAADMzMTg4NQAA</t>
+          <t>E T: Wlcm u, MAX-M u=1441653931Q6 p=IIii2672 on:16/06 00:02:35</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C85" t="n">
-        <v>0.7582788301219161</v>
+        <v>0.5476928486716123</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>tirak please call me back ok</t>
+          <t>https://maps.apple.com/?ll=1.62042,103.72699&amp;q=Location</t>
         </is>
       </c>
       <c r="B86" t="n">
         <v>0</v>
       </c>
       <c r="C86" t="n">
-        <v>0.7734016013850387</v>
+        <v>0.6215847597230105</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>1166 ABAwdEyBez</t>
+          <t>Amoi sini company goldenbet99,apa kabar sudah bossku,lama dah tak try spin mari.jackpot,free game,Bonusgame menanti anda. Web ; goldenbet99 .com</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C87" t="n">
-        <v>0.6755719351063554</v>
+        <v>0.6442074046242862</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Credit percuma tunggu anda mari claim, PM Jana skrg! WS: 01 137623420</t>
+          <t>Bos ni nmor Wasap saye 01116514506 ni saye budak Indonesia</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C88" t="n">
-        <v>0.5289785432110612</v>
+        <v>0.6149426565278201</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Ok ...Jaga diri molek ..jgn susoh² Hati... ada masa Kita lepak skali</t>
+          <t>Jom cuba aplikasi WhatsApp Business, saya menggunakannya untuk berhubung dengan pelanggan saya. Dapatkannya secara percuma di https://whatsapp.com/biz/</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C89" t="n">
-        <v>0.6249760223139937</v>
+        <v>0.6740808620344968</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Ok ...Jaga diri molek ..jgn susoh² Hati... ada masa Kita lepak skali</t>
+          <t>Amoi sini company goldenbet99,apa kabar sudah bossku,lama dah tak try spin mari.jackpot,free game,Bonusgame menanti anda. Web ; goldenbet99 .com</t>
         </is>
       </c>
       <c r="B90" t="n">
         <v>0</v>
       </c>
       <c r="C90" t="n">
-        <v>0.6249760223139937</v>
+        <v>0.6442074046242862</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>BX99:您被选了(ycchong)!恭喜您获得228次免费旋转。存RM50就解锁!bx99my{dot}com</t>
+          <t>sy ta slh kan awk klau awk na benci sy . tak nak contact sy da lepas ni. da sy mintak maaf klau hadir sy dlm idup awk, buat idup awk beban. insAllah. sy ada rezeki lepas ni. sy ta janji , tpi sy cuba tolong bayar balik duit2 yg awk keluar utk sy dgn ank. spnjg awk dgn sy.</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C91" t="n">
-        <v>0.5127223896275346</v>
+        <v>0.8489025399792819</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Dear tenant, please fill up tenant background. I will check with owner and looking unit for you&lt;EMO&gt; Name : Ajit Budget : as low as possible when move in : 1july How many ppl stay : 8 Nepal friend or family : workers Occupation : security Working company name/ school name : security company Local / Foreigner : Race : nepal Tenancy 1 or 2 years : 2</t>
+          <t>Amoi sini company goldenbet99,apa kabar sudah bossku,lama dah tak try spin mari.jackpot,free game,Bonusgame menanti anda. Web ; goldenbet99 .com</t>
         </is>
       </c>
       <c r="B92" t="n">
         <v>0</v>
       </c>
       <c r="C92" t="n">
-        <v>0.5273876023997481</v>
+        <v>0.6442074046242862</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Ok ...Jaga diri molek ..jgn susoh² Hati... ada masa Kita lepak skali</t>
+          <t>https://youtube.com/shorts/fuqANpZirh8?si=iQQrb0BO1qZukNSX</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C93" t="n">
-        <v>0.6249765289534743</v>
+        <v>0.5182364120375486</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>https://images.app.goo.gl/tAviyQQ2vsZb75Qw8</t>
+          <t>HAPPY BIRTHDAY UNGKU SEMOGA PNJG UMUR SORRY AKU TK JOIN TADi</t>
         </is>
       </c>
       <c r="B94" t="n">
         <v>0</v>
       </c>
       <c r="C94" t="n">
-        <v>0.5719411206950362</v>
+        <v>0.5953827962983279</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>https://maps.apple.com/?ll=1.32480,103.91279&amp;q=Location</t>
+          <t>https://youtube.com/shorts/fuqANpZirh8?si=iQQrb0BO1qZukNSX</t>
         </is>
       </c>
       <c r="B95" t="n">
         <v>1</v>
       </c>
       <c r="C95" t="n">
-        <v>0.5955420302639787</v>
+        <v>0.5182364120375486</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Ok ...Jaga diri molek ..jgn susoh² Hati... ada masa Kita lepak skali</t>
+          <t>https://youtube.com/shorts/fuqANpZirh8?si=iQQrb0BO1qZukNSX</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C96" t="n">
-        <v>0.6249765289534743</v>
+        <v>0.5182364120375486</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Ok ...Jaga diri molek ..jgn susoh² Hati... ada masa Kita lepak skali</t>
+          <t>https://youtube.com/shorts/fuqANpZirh8?si=iQQrb0BO1qZukNSX</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C97" t="n">
-        <v>0.6249760223139937</v>
+        <v>0.5182364120375486</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>inimuhammat01116384619muhammat semau orang mari tolong mari inidurga hari hari tujihbuli maruthai semau orang mari tolong mari tolong</t>
+          <t>https://youtube.com/shorts/fuqANpZirh8?si=iQQrb0BO1qZukNSX</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C98" t="n">
-        <v>0.8997632373841769</v>
+        <v>0.5182364120375486</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Amoi sini company goldenbet99,apa kabar sudah bossku,lama dah tak try spin mari.jackpot,free game,Bonusgame menanti anda. Web ; goldenbet99 .com</t>
+          <t>https://youtube.com/shorts/fuqANpZirh8?si=iQQrb0BO1qZukNSX</t>
         </is>
       </c>
       <c r="B99" t="n">
         <v>1</v>
       </c>
       <c r="C99" t="n">
-        <v>0.5945115427700514</v>
+        <v>0.5182364120375486</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>(522003) LGzwYKxLMG</t>
+          <t>Salam sayang aku ni mcm mana c nana ada kurang sudah</t>
         </is>
       </c>
       <c r="B100" t="n">
         <v>0</v>
       </c>
       <c r="C100" t="n">
-        <v>0.6366351504596239</v>
+        <v>0.8944300279725222</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Mamaa bsk tlng sa bgi rm54 sma jnt HAHA taadi sa kna bgi duit orngg. Bkn sa pnya. Nnti hri mnggu sa bgi mama tu duit, bsk mama byr ja</t>
+          <t>Salam sayang aku ni mcm mana c nana ada kurang sudah</t>
         </is>
       </c>
       <c r="B101" t="n">
         <v>0</v>
       </c>
       <c r="C101" t="n">
-        <v>0.8670931269200808</v>
+        <v>0.8944300279725222</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>inimuhammat01116384619muhammat semau orang mari tolong mari inidurga hari hari tujihbuli maruthai semau orang mari tolong mari tolong</t>
+          <t>Jangan rosakkan diri . bukan tkdk jalan lain adaa . laniee kita perlukan masaa , syg sentiasa doaakan yg terbaik utk biy . syg maafkn segalaa salah silap biy . syg tkpenah pendam sikit pon . syg cumaa nk yg trbaik jaa utk biy</t>
         </is>
       </c>
       <c r="B102" t="n">
         <v>0</v>
       </c>
       <c r="C102" t="n">
-        <v>0.8997632373841769</v>
+        <v>0.6815672979462771</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Ok ...Jaga diri molek ..jgn susoh² Hati... ada masa Kita lepak skali</t>
+          <t>Bos ni nmor Wasap saye 01116514506 ni saye budak Indonesia</t>
         </is>
       </c>
       <c r="B103" t="n">
         <v>0</v>
       </c>
       <c r="C103" t="n">
-        <v>0.6237796206744677</v>
+        <v>0.6149426565278201</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>1367800000764</t>
+          <t>Amoi sini company goldenbet99,apa kabar sudah bossku,lama dah tak try spin mari.jackpot,free game,Bonusgame menanti anda. Web ; goldenbet99 .com</t>
         </is>
       </c>
       <c r="B104" t="n">
         <v>0</v>
       </c>
       <c r="C104" t="n">
-        <v>0.690739359405852</v>
+        <v>0.6442074046242862</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Mcm mna mo ubah blikk p imessge ni cinta</t>
+          <t>上 WhatsApp 对话!使用此快速、简便且安全的应用免费发消息和进行通话。下载:https://whatsapp.com/dl/</t>
         </is>
       </c>
       <c r="B105" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C105" t="n">
-        <v>0.8061758835586077</v>
+        <v>0.8494533433806272</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>BX99: (ID: ryan678) Congrats, you are one of todays lucky picks. Deposit RM50 to get 228 FREE Spins. Dont miss out! bx99my{dot}com</t>
+          <t>KakaoTalk HgAAABIwALXuTmgAAAAAAjEABwAAADMzMTg4NQAA</t>
         </is>
       </c>
       <c r="B106" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C106" t="n">
-        <v>0.8702712993351454</v>
+        <v>0.8294519648659854</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Amoi sini company goldenbet99,apa kabar sudah bossku,lama dah tak try spin mari.jackpot,free game,Bonusgame menanti anda. Web ; goldenbet99 .com</t>
+          <t>1166 ABAwdEyBez</t>
         </is>
       </c>
       <c r="B107" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C107" t="n">
-        <v>0.5945115427700514</v>
+        <v>0.5680017337906985</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Bkt.Berlian Res R 24,0 20:26 unet 23.239.111.108 352134012067105 0508 0 1 3 12 62 17600 17600 0.00OK In1=1 In2=0 In3=0</t>
+          <t>Credit percuma tunggu anda mari claim, PM Jana skrg! WS: 01 137623420</t>
         </is>
       </c>
       <c r="B108" t="n">
         <v>0</v>
       </c>
       <c r="C108" t="n">
-        <v>0.628415550735808</v>
+        <v>0.6599350438225894</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Boleh dapatkan maklumat mengenaie diri anda terima kasih</t>
+          <t>BX99:您被选了(ycchong)!恭喜您获得228次免费旋转。存RM50就解锁!bx99my{dot}com</t>
         </is>
       </c>
       <c r="B109" t="n">
         <v>0</v>
       </c>
       <c r="C109" t="n">
-        <v>0.8164299984248644</v>
+        <v>0.5737821922410159</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>KakaoTalk HgAAABIwAP7uTmgAAAAAAjEABwAAADcxOTE5MwAA</t>
+          <t>Dear tenant, please fill up tenant background. I will check with owner and looking unit for you&lt;EMO&gt; Name : Ajit Budget : as low as possible when move in : 1july How many ppl stay : 8 Nepal friend or family : workers Occupation : security Working company name/ school name : security company Local / Foreigner : Race : nepal Tenancy 1 or 2 years : 2</t>
         </is>
       </c>
       <c r="B110" t="n">
         <v>0</v>
       </c>
       <c r="C110" t="n">
-        <v>0.6223733384879595</v>
+        <v>0.7527179882634311</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>BX99:您被选了(jcvoon88)!恭喜您获得228次免费旋转。存RM50就解锁!bx99my{dot}com</t>
+          <t>https://images.app.goo.gl/tAviyQQ2vsZb75Qw8</t>
         </is>
       </c>
       <c r="B111" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C111" t="n">
-        <v>0.7585540752140516</v>
+        <v>0.6849556431878238</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>KakaoTalk HgAAABIwAP7uTmgAAAAAAjEABwAAADcxOTE5MwAA</t>
+          <t>https://maps.apple.com/?ll=1.32480,103.91279&amp;q=Location</t>
         </is>
       </c>
       <c r="B112" t="n">
         <v>0</v>
       </c>
       <c r="C112" t="n">
-        <v>0.6223733384879595</v>
+        <v>0.5628834829438357</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>https://i.lf360.co/BatterySaver</t>
+          <t>Amoi sini company goldenbet99,apa kabar sudah bossku,lama dah tak try spin mari.jackpot,free game,Bonusgame menanti anda. Web ; goldenbet99 .com</t>
         </is>
       </c>
       <c r="B113" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C113" t="n">
-        <v>0.5968180637089247</v>
+        <v>0.6442074046242862</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>https://i.lf360.co/BatterySaver</t>
+          <t>(522003) LGzwYKxLMG</t>
         </is>
       </c>
       <c r="B114" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C114" t="n">
-        <v>0.5968180637089247</v>
+        <v>0.8090076313126712</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>https://i.lf360.co/BatterySaver</t>
+          <t>1367800000764</t>
         </is>
       </c>
       <c r="B115" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C115" t="n">
-        <v>0.5968180637089247</v>
+        <v>0.874572293530765</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>https://i.lf360.co/BatterySaver</t>
+          <t>BX99: (ID: ryan678) Congrats, you are one of todays lucky picks. Deposit RM50 to get 228 FREE Spins. Dont miss out! bx99my{dot}com</t>
         </is>
       </c>
       <c r="B116" t="n">
         <v>1</v>
       </c>
       <c r="C116" t="n">
-        <v>0.5968180637089247</v>
+        <v>0.6673193707358213</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Ok ...Jaga diri molek ..jgn susoh² Hati... ada masa Kita lepak skali</t>
+          <t>Amoi sini company goldenbet99,apa kabar sudah bossku,lama dah tak try spin mari.jackpot,free game,Bonusgame menanti anda. Web ; goldenbet99 .com</t>
         </is>
       </c>
       <c r="B117" t="n">
         <v>0</v>
       </c>
       <c r="C117" t="n">
-        <v>0.6237796206744677</v>
+        <v>0.6442074046242862</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Salam love. Mek dh blt ke bilit. Kmk dh cuci mka n kaki. Kepak gilak kmk. Esok pg jak kmk iron baju. Doakan kmk sentiasa dimudahkan class &amp; exam. Supaya kmk berlapang dada &amp; masik ilmu. Love u n miss u</t>
+          <t>Bkt.Berlian Res R 24,0 20:26 unet 23.239.111.108 352134012067105 0508 0 1 3 12 62 17600 17600 0.00OK In1=1 In2=0 In3=0</t>
         </is>
       </c>
       <c r="B118" t="n">
         <v>0</v>
       </c>
       <c r="C118" t="n">
-        <v>0.5431432385715014</v>
+        <v>0.8228144512284427</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Ok ...Jaga diri molek ..jgn susoh² Hati... ada masa Kita lepak skali</t>
+          <t>KakaoTalk HgAAABIwAP7uTmgAAAAAAjEABwAAADcxOTE5MwAA</t>
         </is>
       </c>
       <c r="B119" t="n">
         <v>0</v>
       </c>
       <c r="C119" t="n">
-        <v>0.6237796206744677</v>
+        <v>0.7481278643716006</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Credit percuma tunggu anda mari claim, PM Jana skrg! WS: 01 137623420</t>
+          <t>BX99:您被选了(jcvoon88)!恭喜您获得228次免费旋转。存RM50就解锁!bx99my{dot}com</t>
         </is>
       </c>
       <c r="B120" t="n">
         <v>1</v>
       </c>
       <c r="C120" t="n">
-        <v>0.5652156810490125</v>
+        <v>0.600113882054028</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Mai lah sni gilak</t>
+          <t>KakaoTalk HgAAABIwAP7uTmgAAAAAAjEABwAAADcxOTE5MwAA</t>
         </is>
       </c>
       <c r="B121" t="n">
         <v>0</v>
       </c>
       <c r="C121" t="n">
-        <v>0.7512793798717028</v>
+        <v>0.7481278643716006</v>
       </c>
     </row>
     <row r="122">
@@ -2012,36 +2012,36 @@
         </is>
       </c>
       <c r="B122" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C122" t="n">
-        <v>0.5968180637089247</v>
+        <v>0.5331226453889041</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>https://maps.apple.com/?ll=1.32006,103.84447&amp;q=Location</t>
+          <t>https://i.lf360.co/BatterySaver</t>
         </is>
       </c>
       <c r="B123" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C123" t="n">
-        <v>0.6185624341694349</v>
+        <v>0.5331226453889041</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>QR0853</t>
+          <t>https://i.lf360.co/BatterySaver</t>
         </is>
       </c>
       <c r="B124" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C124" t="n">
-        <v>0.7988537292210096</v>
+        <v>0.5331226453889041</v>
       </c>
     </row>
     <row r="125">
@@ -2051,140 +2051,140 @@
         </is>
       </c>
       <c r="B125" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C125" t="n">
-        <v>0.5968180637089247</v>
+        <v>0.5331226453889041</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>25O616 OOO4 (1) bft1511 18/O6 *MPT 37O9=2B GT=6 TT=6 O16232711O</t>
+          <t>Salam love. Mek dh blt ke bilit. Kmk dh cuci mka n kaki. Kepak gilak kmk. Esok pg jak kmk iron baju. Doakan kmk sentiasa dimudahkan class &amp; exam. Supaya kmk berlapang dada &amp; masik ilmu. Love u n miss u</t>
         </is>
       </c>
       <c r="B126" t="n">
         <v>0</v>
       </c>
       <c r="C126" t="n">
-        <v>0.5490984578403002</v>
+        <v>0.8478500709641604</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Alarm cancelled S/ROOM BURGOGUAD Area 1 16 Jun 0h05</t>
+          <t>Credit percuma tunggu anda mari claim, PM Jana skrg! WS: 01 137623420</t>
         </is>
       </c>
       <c r="B127" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C127" t="n">
-        <v>0.785057280513429</v>
+        <v>0.6599350438225894</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>ကြားရတဲ့သတင်းတွေမကောင်းလို့ အားလုံးကိုစိတ်ပူလို့ ဖုန်းဆက်မိတာပါ စိတ်မကောင်းဘူးပဲ ဒါနောက်ဆုံးပဲ ဖြစ်မှာပါ နှုတ်ဆက်ပါတယ် good bye</t>
+          <t>https://i.lf360.co/BatterySaver</t>
         </is>
       </c>
       <c r="B128" t="n">
         <v>0</v>
       </c>
       <c r="C128" t="n">
-        <v>0.8044974167617327</v>
+        <v>0.5331226453889041</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>lepas tu ws ckp apa? blk terus nk kemas² n tdo... apa maksudnya tu?</t>
+          <t>https://maps.apple.com/?ll=1.32006,103.84447&amp;q=Location</t>
         </is>
       </c>
       <c r="B129" t="n">
         <v>0</v>
       </c>
       <c r="C129" t="n">
-        <v>0.8942250867160326</v>
+        <v>0.5447612271416812</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>KakaoTalk HgAAABIwAP7uTmgAAAAAAjEABwAAADcxOTE5MwAA</t>
+          <t>QR0853</t>
         </is>
       </c>
       <c r="B130" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C130" t="n">
-        <v>0.6223733384879595</v>
+        <v>0.587083949078259</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Ok ...Jaga diri molek ..jgn susoh² Hati... ada masa Kita lepak skali</t>
+          <t>https://i.lf360.co/BatterySaver</t>
         </is>
       </c>
       <c r="B131" t="n">
         <v>0</v>
       </c>
       <c r="C131" t="n">
-        <v>0.6237796206744677</v>
+        <v>0.5331226453889041</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Cik jamal tk berhenti nurse ni call msej sy cik jamal tlglah cik jamal</t>
+          <t>25O616 OOO4 (1) bft1511 18/O6 *MPT 37O9=2B GT=6 TT=6 O16232711O</t>
         </is>
       </c>
       <c r="B132" t="n">
         <v>0</v>
       </c>
       <c r="C132" t="n">
-        <v>0.873144771602965</v>
+        <v>0.7376017437089114</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>12.45 ambik barang kat luar rumah, jangan tak angkat orang call.</t>
+          <t>Alarm cancelled S/ROOM BURGOGUAD Area 1 16 Jun 0h05</t>
         </is>
       </c>
       <c r="B133" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C133" t="n">
-        <v>0.839036728885985</v>
+        <v>0.5180702938925595</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>QR0021</t>
+          <t>KakaoTalk HgAAABIwAP7uTmgAAAAAAjEABwAAADcxOTE5MwAA</t>
         </is>
       </c>
       <c r="B134" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C134" t="n">
-        <v>0.6820978264538282</v>
+        <v>0.7481278643716006</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>SYS ARM; END</t>
+          <t>QR0021</t>
         </is>
       </c>
       <c r="B135" t="n">
         <v>0</v>
       </c>
       <c r="C135" t="n">
-        <v>0.8767188300164706</v>
+        <v>0.5128464565385012</v>
       </c>
     </row>
     <row r="136">
@@ -2197,46 +2197,46 @@
         <v>1</v>
       </c>
       <c r="C136" t="n">
-        <v>0.7888670901981825</v>
+        <v>0.5347610845457883</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Aku mau yo omong" an karo mbkq yo tak kon glk inpo lemah seng di dol ngono koyok e enek kidol mahku tpi jare mbkq larang Terus aku di takoni la w takok" opo ndwe duek ngono yo tak sauri urung tpi ge pandangan lah ge semangat nek kerjo.. Bukane aku mikir sman matre ora blass yng syngg aku mau arep omong ngonokui me sman tpi sman kesusu mikir lek aku ngono hoalah yng" sepurane tpi yngg yo gae sman nesu tulung di ngerteni aku yng yoo mosok modele koyo aku ndwe pikiran lek sman matre jan" adoh soko jangkauan</t>
+          <t>Her mobile 012 2418877</t>
         </is>
       </c>
       <c r="B137" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C137" t="n">
-        <v>0.7642330785068041</v>
+        <v>0.5694972410094113</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>wlaupn ak prnah mncuba utk brubah dan ak cuba mnjd trbaik utk kau, ak brharap kau nmpak, tp sgalanya mcm sia2 tp gpp ak kn ga ada hati bg kau, tp apa pn kau trsgt2 laa baik spnjg 3tahun kita kwn ni, ak xnafikn kau byk sgt2 buat sgala mcm utk ak. ak sygkn sbnarnya lbih dr siapa pn. mskipn xbrsama lg, ak rasa dh masanya utk ak brubah. ak xmau lg sama siapa pn. ckup laa kau trakhir kali ni. mngkin bg kau kata2 ak cuma ksong, tp ak akn buktikn.</t>
+          <t>https://maps.apple.com/?ll=1.62042,103.72699&amp;q=Location</t>
         </is>
       </c>
       <c r="B138" t="n">
         <v>0</v>
       </c>
       <c r="C138" t="n">
-        <v>0.7393104393752581</v>
+        <v>0.6215844020951419</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Her mobile 012 2418877</t>
+          <t>SIGOS SMS test</t>
         </is>
       </c>
       <c r="B139" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C139" t="n">
-        <v>0.8404573617596763</v>
+        <v>0.7647515401948123</v>
       </c>
     </row>
     <row r="140">
@@ -2246,23 +2246,23 @@
         </is>
       </c>
       <c r="B140" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C140" t="n">
-        <v>0.5411547241826195</v>
+        <v>0.6215844020951419</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>SIGOS SMS test</t>
+          <t>https://maps.apple.com/?ll=1.62042,103.72699&amp;q=Location</t>
         </is>
       </c>
       <c r="B141" t="n">
         <v>0</v>
       </c>
       <c r="C141" t="n">
-        <v>0.516990441260801</v>
+        <v>0.6215844020951419</v>
       </c>
     </row>
     <row r="142">
@@ -2272,10 +2272,10 @@
         </is>
       </c>
       <c r="B142" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C142" t="n">
-        <v>0.5411547241826195</v>
+        <v>0.6215844020951419</v>
       </c>
     </row>
     <row r="143">
@@ -2285,10 +2285,10 @@
         </is>
       </c>
       <c r="B143" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C143" t="n">
-        <v>0.5411547241826195</v>
+        <v>0.6215844020951419</v>
       </c>
     </row>
     <row r="144">
@@ -2298,244 +2298,244 @@
         </is>
       </c>
       <c r="B144" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C144" t="n">
-        <v>0.5411547241826195</v>
+        <v>0.6215847597230105</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>https://maps.apple.com/?ll=1.62042,103.72699&amp;q=Location</t>
+          <t>lagi sekali , sy mintak maaf dari hujung rambut smpai hujung kaki.. salah silap sy spnjg dgn awk.. awk boleh buat keputusan utk tidak bersama sy atau masih na teruskan. sbb sy tak nak sampai bila2 gantung mcm ni. dengan takdek perbincangan . to je sy mintak . semua atas awk.</t>
         </is>
       </c>
       <c r="B145" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C145" t="n">
-        <v>0.5411547241826195</v>
+        <v>0.6362938747513919</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>夜 13-5 18-10 8-5 30-5 =25</t>
+          <t>Mas lihat live aku sekrng mcm mna aku pkai</t>
         </is>
       </c>
       <c r="B146" t="n">
         <v>0</v>
       </c>
       <c r="C146" t="n">
-        <v>0.7489721955637795</v>
+        <v>0.5669062600243716</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>https://maps.apple.com/?ll=1.62042,103.72699&amp;q=Location</t>
+          <t>(11,14,15/6) 原本结存+1199 我的3期: -8 我尚结存=[ +1191 ]</t>
         </is>
       </c>
       <c r="B147" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C147" t="n">
-        <v>0.5411547241826195</v>
+        <v>0.5684560999978213</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Mamaa bsk tlng sa bgi rm54 sma jnt HAHA taadi sa kna bgi duit orngg. Bkn sa pnya. Nnti hri mnggu sa bgi mama tu duit, bsk mama byr ja</t>
+          <t>https://maps.apple.com/?ll=1.62042,103.72699&amp;q=Location</t>
         </is>
       </c>
       <c r="B148" t="n">
         <v>0</v>
       </c>
       <c r="C148" t="n">
-        <v>0.8680508019308907</v>
+        <v>0.6215847597230105</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>lagi sekali , sy mintak maaf dari hujung rambut smpai hujung kaki.. salah silap sy spnjg dgn awk.. awk boleh buat keputusan utk tidak bersama sy atau masih na teruskan. sbb sy tak nak sampai bila2 gantung mcm ni. dengan takdek perbincangan . to je sy mintak . semua atas awk.</t>
+          <t>Demi Allah abg tak membenci syg ...setiap sholat abg doakan yg terbaik utk syg...semuga Selamat setiap perjalan syg peri Dan balik dri Terengganu</t>
         </is>
       </c>
       <c r="B149" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C149" t="n">
-        <v>0.7132228432316917</v>
+        <v>0.7224099204648166</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Waalaikumsalam kwn man Ney tok.kmk mok tauk lebih benar.man Ney satu</t>
+          <t>nawaitu ßyifa bibarakati mustofa sallahu alaihi wasalam. bca pd air minum</t>
         </is>
       </c>
       <c r="B150" t="n">
         <v>0</v>
       </c>
       <c r="C150" t="n">
-        <v>0.6455272616724831</v>
+        <v>0.5547202692139773</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Mas lihat live aku sekrng mcm mna aku pkai</t>
+          <t>Bkt.Berlian Res R 24,0 20:26 unet 23.239.111.108 352134012067105 0508 0 1 3 12 62 17600 17600 0.00OK In1=1 In2=0 In3=0</t>
         </is>
       </c>
       <c r="B151" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C151" t="n">
-        <v>0.7395773945469993</v>
+        <v>0.8228144512284427</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>(11,14,15/6) 原本结存+1199 我的3期: -8 我尚结存=[ +1191 ]</t>
+          <t>To join the meeting on Google Meet, click this link: https://meet.google.com/gow-xyon-gdu Or open Meet and enter this code: gow-xyon-gdu</t>
         </is>
       </c>
       <c r="B152" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C152" t="n">
-        <v>0.694049757542147</v>
+        <v>0.7086298928368716</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>https://maps.apple.com/?ll=1.62042,103.72699&amp;q=Location</t>
+          <t>To join the meeting on Google Meet, click this link: https://meet.google.com/gow-xyon-gdu Or open Meet and enter this code: gow-xyon-gdu</t>
         </is>
       </c>
       <c r="B153" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C153" t="n">
-        <v>0.5411547241826195</v>
+        <v>0.7086298928368716</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>N sbb Tu kte still PGL awak biey</t>
+          <t>Let's chat on WhatsApp! It's a fast, simple, and secure app we can use to message and call each other for free. Get it at https://whatsapp.com/dl/</t>
         </is>
       </c>
       <c r="B154" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C154" t="n">
-        <v>0.7168410899023873</v>
+        <v>0.7418096198927732</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>Demi Allah abg tak membenci syg ...setiap sholat abg doakan yg terbaik utk syg...semuga Selamat setiap perjalan syg peri Dan balik dri Terengganu</t>
+          <t>Let's chat on WhatsApp! It's a fast, simple, and secure app we can use to message and call each other for free. Get it at https://whatsapp.com/dl/</t>
         </is>
       </c>
       <c r="B155" t="n">
         <v>1</v>
       </c>
       <c r="C155" t="n">
-        <v>0.6380566774029869</v>
+        <v>0.7418096198927732</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>nawaitu ßyifa bibarakati mustofa sallahu alaihi wasalam. bca pd air minum</t>
+          <t>Mas lihat live aku sekrng mcm mna aku pkai</t>
         </is>
       </c>
       <c r="B156" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C156" t="n">
-        <v>0.7911794005055565</v>
+        <v>0.5669062600243716</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>Bkt.Berlian Res R 24,0 20:26 unet 23.239.111.108 352134012067105 0508 0 1 3 12 62 17600 17600 0.00OK In1=1 In2=0 In3=0</t>
+          <t>Bank loan (offer) - Rm10K - 400K / 5-10 yrs - Debt Consolidate - Hard to get Loan Approve? - Credit card limit burst? - CTOS/ Blacklist issue? No worried, WE CAN SETTLE YOUR PROBLEM REPLY YES for details</t>
         </is>
       </c>
       <c r="B157" t="n">
         <v>0</v>
       </c>
       <c r="C157" t="n">
-        <v>0.6183790149073464</v>
+        <v>0.7748755083192019</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>To join the meeting on Google Meet, click this link: https://meet.google.com/gow-xyon-gdu Or open Meet and enter this code: gow-xyon-gdu</t>
+          <t>Let's chat on WhatsApp! It's a fast, simple, and secure app we can use to message and call each other for free. Get it at https://whatsapp.com/dl/</t>
         </is>
       </c>
       <c r="B158" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C158" t="n">
-        <v>0.5573364080767494</v>
+        <v>0.7418096198927732</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>Aku cht ni sia2 je bkn no bce kn mmg kmu x nk bce baik aku pun smbg cll tiktok dgn owg lain sbb km7 pun dh x pduli aku kn baik aku smbg owg lain x la aku bosan kn</t>
+          <t>[Emergency SOS] Emergency sharing ended. Tap this link to view my last location: https://maps.google.com/maps?f=q&amp;q=5.089113,100.392181.</t>
         </is>
       </c>
       <c r="B159" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C159" t="n">
-        <v>0.6379991056303841</v>
+        <v>0.5776166453253598</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>To join the meeting on Google Meet, click this link: https://meet.google.com/gow-xyon-gdu Or open Meet and enter this code: gow-xyon-gdu</t>
+          <t>[Emergency SOS] Emergency sharing ended. Tap this link to view my last location: https://maps.google.com/maps?f=q&amp;q=5.089113,100.392181.</t>
         </is>
       </c>
       <c r="B160" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C160" t="n">
-        <v>0.5573364080767494</v>
+        <v>0.5776166453253598</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>i need to clarify things with you ... no wonder your wife going thru hell ippo thaan i knw ur real face</t>
+          <t>[Emergency SOS] Emergency sharing ended. Tap this link to view my last location: https://maps.google.com/maps?f=q&amp;q=5.089113,100.392181.</t>
         </is>
       </c>
       <c r="B161" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C161" t="n">
-        <v>0.8507960023264748</v>
+        <v>0.5776166453253598</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>Let's chat on WhatsApp! It's a fast, simple, and secure app we can use to message and call each other for free. Get it at https://whatsapp.com/dl/</t>
+          <t>14/6=420) 15/6=360) =780_20%-156) Total=-624.00 你的工人=700</t>
         </is>
       </c>
       <c r="B162" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C162" t="n">
-        <v>0.7937352476735252</v>
+        <v>0.5633007154572635</v>
       </c>
     </row>
     <row r="163">
@@ -2548,33 +2548,33 @@
         <v>1</v>
       </c>
       <c r="C163" t="n">
-        <v>0.7937352476735252</v>
+        <v>0.7418096198927732</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>Mas lihat live aku sekrng mcm mna aku pkai</t>
+          <t>[Emergency SOS] Emergency sharing ended. Tap this link to view my last location: https://maps.google.com/maps?f=q&amp;q=5.089113,100.392181.</t>
         </is>
       </c>
       <c r="B164" t="n">
         <v>1</v>
       </c>
       <c r="C164" t="n">
-        <v>0.7395773945469993</v>
+        <v>0.5776166453253598</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>Bank loan (offer) - Rm10K - 400K / 5-10 yrs - Debt Consolidate - Hard to get Loan Approve? - Credit card limit burst? - CTOS/ Blacklist issue? No worried, WE CAN SETTLE YOUR PROBLEM REPLY YES for details</t>
+          <t>Let's chat on WhatsApp! It's a fast, simple, and secure app we can use to message and call each other for free. Get it at https://whatsapp.com/dl/</t>
         </is>
       </c>
       <c r="B165" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C165" t="n">
-        <v>0.5991671265940529</v>
+        <v>0.7418096198927732</v>
       </c>
     </row>
     <row r="166">
@@ -2587,85 +2587,85 @@
         <v>1</v>
       </c>
       <c r="C166" t="n">
-        <v>0.7937352476735252</v>
+        <v>0.7418096198927732</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>Sikdaa</t>
+          <t>25O616 OOO5 (1) bft152O 18/O6 *MPT 3685=1B (Box) 3685=1B (IBox) GT=75 TT=75 O16232711O</t>
         </is>
       </c>
       <c r="B167" t="n">
         <v>0</v>
       </c>
       <c r="C167" t="n">
-        <v>0.8934532286505562</v>
+        <v>0.6961604819405703</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>[Emergency SOS] Emergency sharing ended. Tap this link to view my last location: https://maps.google.com/maps?f=q&amp;q=5.089113,100.392181.</t>
+          <t>Amoi sini company goldenbet99,apa kabar sudah bossku,lama dah tak try spin mari.jackpot,free game,Bonusgame menanti anda. Web : goldenbet99 .com</t>
         </is>
       </c>
       <c r="B168" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C168" t="n">
-        <v>0.7582502780575889</v>
+        <v>0.6423963770974307</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>[Emergency SOS] Emergency sharing ended. Tap this link to view my last location: https://maps.google.com/maps?f=q&amp;q=5.089113,100.392181.</t>
+          <t>588896 kjEwRrpYYz</t>
         </is>
       </c>
       <c r="B169" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C169" t="n">
-        <v>0.7582502780575889</v>
+        <v>0.5413895712006717</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>[Emergency SOS] Emergency sharing ended. Tap this link to view my last location: https://maps.google.com/maps?f=q&amp;q=5.089113,100.392181.</t>
+          <t>Let's chat on WhatsApp! It's a fast, simple, and secure app we can use to message and call each other for free. Get it at https://whatsapp.com/dl/</t>
         </is>
       </c>
       <c r="B170" t="n">
         <v>1</v>
       </c>
       <c r="C170" t="n">
-        <v>0.7582502780575889</v>
+        <v>0.7418096198927732</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>14/6=420) 15/6=360) =780_20%-156) Total=-624.00 你的工人=700</t>
+          <t>Bank loan (offer) - Rm10K - 400K / 5-10 yrs - Debt Consolidate - Hard to get Loan Approve? - Credit card limit burst? - CTOS/ Blacklist issue? No worried, WE CAN SETTLE YOUR PROBLEM REPLY YES for details</t>
         </is>
       </c>
       <c r="B171" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C171" t="n">
-        <v>0.6816443024296898</v>
+        <v>0.7748755083192019</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>Let's chat on WhatsApp! It's a fast, simple, and secure app we can use to message and call each other for free. Get it at https://whatsapp.com/dl/</t>
+          <t>[Emergency SOS] Emergency sharing ended. Tap this link to view my last location: https://maps.google.com/maps?f=q&amp;q=5.089113,100.392181.</t>
         </is>
       </c>
       <c r="B172" t="n">
         <v>1</v>
       </c>
       <c r="C172" t="n">
-        <v>0.7937352476735252</v>
+        <v>0.5776166453253598</v>
       </c>
     </row>
     <row r="173">
@@ -2678,1138 +2678,1138 @@
         <v>1</v>
       </c>
       <c r="C173" t="n">
-        <v>0.7582502780575889</v>
+        <v>0.5776166453253598</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>Boleh dapatkan maklumat mengenaie diri anda terima kasih</t>
+          <t>Let's chat on WhatsApp! It's a fast, simple, and secure app we can use to message and call each other for free. Get it at https://whatsapp.com/dl/</t>
         </is>
       </c>
       <c r="B174" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C174" t="n">
-        <v>0.8233518185000283</v>
+        <v>0.7418096198927732</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>Let's chat on WhatsApp! It's a fast, simple, and secure app we can use to message and call each other for free. Get it at https://whatsapp.com/dl/</t>
+          <t>[Emergency SOS] Emergency sharing ended. Tap this link to view my last location: https://maps.google.com/maps?f=q&amp;q=5.089113,100.392181.</t>
         </is>
       </c>
       <c r="B175" t="n">
         <v>1</v>
       </c>
       <c r="C175" t="n">
-        <v>0.7937352476735252</v>
+        <v>0.5776166453253598</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>Let's chat on WhatsApp! It's a fast, simple, and secure app we can use to message and call each other for free. Get it at https://whatsapp.com/dl/</t>
+          <t>Bkt.Berlian Res R 24,0 20:26 unet 23.239.111.108 352134012067105 0508 0 1 3 12 62 17600 17600 0.00OK In1=1 In2=0 In3=0</t>
         </is>
       </c>
       <c r="B176" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C176" t="n">
-        <v>0.7937352476735252</v>
+        <v>0.8228144512284427</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>25O616 OOO5 (1) bft152O 18/O6 *MPT 3685=1B (Box) 3685=1B (IBox) GT=75 TT=75 O16232711O</t>
+          <t>Old Insurance policy FREE REVIEW and Consultation * AIA medical coverage * Up to Rm8mil annual limit * No medical checkup (T&amp;C) Reply "YES" for more infos</t>
         </is>
       </c>
       <c r="B177" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C177" t="n">
-        <v>0.5173586426396507</v>
+        <v>0.5224437580216555</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>Amoi sini company goldenbet99,apa kabar sudah bossku,lama dah tak try spin mari.jackpot,free game,Bonusgame menanti anda. Web : goldenbet99 .com</t>
+          <t>&lt;0920392&gt; System Armed</t>
         </is>
       </c>
       <c r="B178" t="n">
         <v>1</v>
       </c>
       <c r="C178" t="n">
-        <v>0.6104651508946556</v>
+        <v>0.5442500843893857</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>DDY SYA AMBILL SIMM SYAA</t>
+          <t>Bank loan (offer) - Rm10K - 400K / 5-10 yrs - Debt Consolidate - Hard to get Loan Approve? - Credit card limit burst? - CTOS/ Blacklist issue? No worried, WE CAN SETTLE YOUR PROBLEM REPLY YES for details</t>
         </is>
       </c>
       <c r="B179" t="n">
         <v>0</v>
       </c>
       <c r="C179" t="n">
-        <v>0.765904265819059</v>
+        <v>0.77487535930759</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>DDY SYA AMBILL SIMM SYAA</t>
+          <t>Old Insurance policy FREE REVIEW and Consultation * AIA medical coverage * Up to Rm8mil annual limit * No medical checkup (T&amp;C) Reply "YES" for more infos</t>
         </is>
       </c>
       <c r="B180" t="n">
         <v>0</v>
       </c>
       <c r="C180" t="n">
-        <v>0.765904265819059</v>
+        <v>0.5224437580216555</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>FPX OPEN P-250615: Failure rate increase on Database service EFPXPROD:Failure rate increase</t>
+          <t>Let's chat on Viber. It's my main app for messaging and free calls. Hereမမမမ's the link https://vb.me/letsUseViber</t>
         </is>
       </c>
       <c r="B181" t="n">
         <v>0</v>
       </c>
       <c r="C181" t="n">
-        <v>0.8071682931761605</v>
+        <v>0.6300166711915164</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>588896 kjEwRrpYYz</t>
+          <t>[Emergency SOS] Emergency sharing ended. Tap this link to view my last location: https://maps.google.com/maps?f=q&amp;q=5.089113,100.392181.</t>
         </is>
       </c>
       <c r="B182" t="n">
         <v>1</v>
       </c>
       <c r="C182" t="n">
-        <v>0.6885478315968651</v>
+        <v>0.5776166453253598</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>SEMENYIH BATT LOW!!!=0 15062025,18:21</t>
+          <t>Monday, 06/16/2025 at 00:02:17. The Point 3C. AHU 100K5 RET HUMIDITY is in Alarm at PRI1 with a value of 63.2 %RH.</t>
         </is>
       </c>
       <c r="B183" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C183" t="n">
-        <v>0.7621126057486397</v>
+        <v>0.6285232438933225</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>Let's chat on WhatsApp! It's a fast, simple, and secure app we can use to message and call each other for free. Get it at https://whatsapp.com/dl/</t>
+          <t>6/16/2025 12:06:07 AM PHKL Blk A Level 3 IVF Embryology Lab High Temperature Alarm.</t>
         </is>
       </c>
       <c r="B184" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C184" t="n">
-        <v>0.7937352476735252</v>
+        <v>0.5384991631615786</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>Bank loan (offer) - Rm10K - 400K / 5-10 yrs - Debt Consolidate - Hard to get Loan Approve? - Credit card limit burst? - CTOS/ Blacklist issue? No worried, WE CAN SETTLE YOUR PROBLEM REPLY YES for details</t>
+          <t>6/16/2025 12:06:07 AM PHKL Blk A Level 3 IVF Embryology Lab High Temperature Alarm.</t>
         </is>
       </c>
       <c r="B185" t="n">
         <v>0</v>
       </c>
       <c r="C185" t="n">
-        <v>0.5991671265940529</v>
+        <v>0.5384991631615786</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>[Emergency SOS] Emergency sharing ended. Tap this link to view my last location: https://maps.google.com/maps?f=q&amp;q=5.089113,100.392181.</t>
+          <t>To join the meeting on Google Meet, click this link: https://meet.google.com/gow-xyon-gdu Or open Meet and enter this code: gow-xyon-gdu</t>
         </is>
       </c>
       <c r="B186" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C186" t="n">
-        <v>0.7582502780575889</v>
+        <v>0.7086298928368716</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>[Emergency SOS] Emergency sharing ended. Tap this link to view my last location: https://maps.google.com/maps?f=q&amp;q=5.089113,100.392181.</t>
+          <t>+60 11-1218 7314</t>
         </is>
       </c>
       <c r="B187" t="n">
         <v>1</v>
       </c>
       <c r="C187" t="n">
-        <v>0.7582502780575889</v>
+        <v>0.614397717941937</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>k la ..maaf ganggu idup awk. jaga diri elok2 bb .. baby mintakk maaf sgt2.. loveusomuch &lt;EMO&gt; assalamualaikum cinta.</t>
+          <t>6/16/2025 12:06:07 AM PHKL Blk A Level 3 IVF Embryology Lab High Temperature Alarm.</t>
         </is>
       </c>
       <c r="B188" t="n">
         <v>0</v>
       </c>
       <c r="C188" t="n">
-        <v>0.7832288705456927</v>
+        <v>0.5384991631615786</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>FPX OPEN P-250615: Failure rate increase on Database service EFPXPROD:Failure rate increase</t>
+          <t>16/06/2025 00:03:01 HARWOOD KUALA BARAM-Branch online after power resumed.</t>
         </is>
       </c>
       <c r="B189" t="n">
         <v>0</v>
       </c>
       <c r="C189" t="n">
-        <v>0.7756369077313616</v>
+        <v>0.5481674537766604</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>Let's chat on WhatsApp! It's a fast, simple, and secure app we can use to message and call each other for free. Get it at https://whatsapp.com/dl/</t>
+          <t>6/16/2025 12:06:07 AM PHKL Blk A Level 3 IVF Embryology Lab High Temperature Alarm.</t>
         </is>
       </c>
       <c r="B190" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C190" t="n">
-        <v>0.8821827805887983</v>
+        <v>0.5384991631615786</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>[Emergency SOS] Emergency sharing ended. Tap this link to view my last location: https://maps.google.com/maps?f=q&amp;q=5.089113,100.392181.</t>
+          <t>&lt;0920392&gt; System Armed</t>
         </is>
       </c>
       <c r="B191" t="n">
         <v>1</v>
       </c>
       <c r="C191" t="n">
-        <v>0.8050231970202253</v>
+        <v>0.5442479386221738</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>Bkt.Berlian Res R 24,0 20:26 unet 23.239.111.108 352134012067105 0508 0 1 3 12 62 17600 17600 0.00OK In1=1 In2=0 In3=0</t>
+          <t>Mami..bgtau bang net tolong jap topupkan nombor digi abg ni ha RM 10 dulu,data abg dah tamat tempoh ha..</t>
         </is>
       </c>
       <c r="B192" t="n">
         <v>0</v>
       </c>
       <c r="C192" t="n">
-        <v>0.5697963201153948</v>
+        <v>0.5937445030320315</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>Old Insurance policy FREE REVIEW and Consultation * AIA medical coverage * Up to Rm8mil annual limit * No medical checkup (T&amp;C) Reply "YES" for more infos</t>
+          <t>25O616 OOO6 (2) bq33 18/O6-21/O6-22/O6 *P 8O5O=1B 1S 8O5O=6B (IBox) GT=24</t>
         </is>
       </c>
       <c r="B193" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C193" t="n">
-        <v>0.7138193286310957</v>
+        <v>0.6881497964966922</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>&lt;0920392&gt; System Armed</t>
+          <t>25O616 OOO6 (1) kb213O22 16/O6 /HE 3888=2B GT=2 Q1126388897 Points:OO13 1633 5196 7278</t>
         </is>
       </c>
       <c r="B194" t="n">
         <v>1</v>
       </c>
       <c r="C194" t="n">
-        <v>0.8170995748888776</v>
+        <v>0.5258121623885007</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>Waalaikumsalam kwn man Ney tok.kmk mok tauk lebih benar.man Ney satu</t>
+          <t>Hi Mendo Buda,,,sorry saya block you WhatsApp dulu ya saya kena belajar untuk tidak mencintai you lagi ,,you jangan cari saya lagi fokus dengan cinta you mendo</t>
         </is>
       </c>
       <c r="B195" t="n">
         <v>0</v>
       </c>
       <c r="C195" t="n">
-        <v>0.6232140623677447</v>
+        <v>0.8156004712689547</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>Bank loan (offer) - Rm10K - 400K / 5-10 yrs - Debt Consolidate - Hard to get Loan Approve? - Credit card limit burst? - CTOS/ Blacklist issue? No worried, WE CAN SETTLE YOUR PROBLEM REPLY YES for details</t>
+          <t>ALARM S/ROOM BURGOGUAD Area 1 16 Jun 0h05</t>
         </is>
       </c>
       <c r="B196" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C196" t="n">
-        <v>0.5498748981106951</v>
+        <v>0.5050448312651487</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>Old Insurance policy FREE REVIEW and Consultation * AIA medical coverage * Up to Rm8mil annual limit * No medical checkup (T&amp;C) Reply "YES" for more infos</t>
+          <t>Amoi sini company goldenbet99,apa kabar sudah bossku,lama dah tak try spin mari.jackpot,free game,Bonusgame menanti anda. Web : goldenbet99 .com</t>
         </is>
       </c>
       <c r="B197" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C197" t="n">
-        <v>0.7138193286310957</v>
+        <v>0.6423963770974307</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>Let's chat on Viber. It's my main app for messaging and free calls. Hereမမမမ's the link https://vb.me/letsUseViber</t>
+          <t>25O616 OOO6 (3) bq33 18/O6-21/O6-22/O6 *T 1911=3B 2S (Box) GT=6O</t>
         </is>
       </c>
       <c r="B198" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C198" t="n">
-        <v>0.5304356850039289</v>
+        <v>0.5139351949799685</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>[Emergency SOS] Emergency sharing ended. Tap this link to view my last location: https://maps.google.com/maps?f=q&amp;q=5.089113,100.392181.</t>
+          <t>Flextronic H1 MsgText : J750_Sensor_3 RH Back to Normal Value : 59.0 %</t>
         </is>
       </c>
       <c r="B199" t="n">
         <v>1</v>
       </c>
       <c r="C199" t="n">
-        <v>0.8050231970202253</v>
+        <v>0.5231757893454404</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>Monday, 06/16/2025 at 00:02:17. The Point 3C. AHU 100K5 RET HUMIDITY is in Alarm at PRI1 with a value of 63.2 %RH.</t>
+          <t>https://images.app.goo.gl/QJQ6bqWbeMMFs9yh9</t>
         </is>
       </c>
       <c r="B200" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C200" t="n">
-        <v>0.8952036536585615</v>
+        <v>0.6585372552979617</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>kedong20 爱玉冰30</t>
+          <t>Bkt.Berlian Res R 24,0 20:26 unet 23.239.111.108 352134012067105 0508 0 1 3 12 62 17600 17600 0.00OK In1=1 In2=0 In3=0</t>
         </is>
       </c>
       <c r="B201" t="n">
         <v>0</v>
       </c>
       <c r="C201" t="n">
-        <v>0.6809973084080889</v>
+        <v>0.8228144512284427</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>Line kat sini memang kadang kadang takde hmmm</t>
+          <t>Mudah: I'm interested in your ad on Mudah Hata Square Female Room Rental Fully Furnished (June 2025), please share more details with me.</t>
         </is>
       </c>
       <c r="B202" t="n">
         <v>0</v>
       </c>
       <c r="C202" t="n">
-        <v>0.6049184166539385</v>
+        <v>0.6875219211686282</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>6/16/2025 12:06:07 AM PHKL Blk A Level 3 IVF Embryology Lab High Temperature Alarm.</t>
+          <t>To join the meeting on Google Meet, click this link: https://meet.google.com/bxe-hyrj-oxe Or open Meet and enter this code: bxe-hyrj-oxe</t>
         </is>
       </c>
       <c r="B203" t="n">
         <v>1</v>
       </c>
       <c r="C203" t="n">
-        <v>0.7193701303850935</v>
+        <v>0.5132360591780515</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>Rest leklok tau pastu ws saya nanti bila awak dh ade data ataupun awak missed call je saya kejap pastu saya call awak balik kalau saya terjaga. Goodnight &lt;3</t>
+          <t>To join the meeting on Google Meet, click this link: https://meet.google.com/bxe-hyrj-oxe Or open Meet and enter this code: bxe-hyrj-oxe</t>
         </is>
       </c>
       <c r="B204" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C204" t="n">
-        <v>0.7297881507027819</v>
+        <v>0.5132360591780515</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>6/16/2025 12:06:07 AM PHKL Blk A Level 3 IVF Embryology Lab High Temperature Alarm.</t>
+          <t>(311720) lezwrxOKjl</t>
         </is>
       </c>
       <c r="B205" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C205" t="n">
-        <v>0.7193701303850935</v>
+        <v>0.5787431464303164</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>To join the meeting on Google Meet, click this link: https://meet.google.com/gow-xyon-gdu Or open Meet and enter this code: gow-xyon-gdu</t>
+          <t>F re3 Cr3dlt M€ g@/K1 §§/P u§§ y Was@p - 01_46139668 0ng m@li Jajwnsmz</t>
         </is>
       </c>
       <c r="B206" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C206" t="n">
-        <v>0.5019080602276995</v>
+        <v>0.5365986957442136</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>+60 11-1218 7314</t>
+          <t>jgn awak mok mcm iii</t>
         </is>
       </c>
       <c r="B207" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C207" t="n">
-        <v>0.8861025012385175</v>
+        <v>0.5352125630486636</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>6/16/2025 12:06:07 AM PHKL Blk A Level 3 IVF Embryology Lab High Temperature Alarm.</t>
+          <t>END - 06/15 22:58 AC2:No connection</t>
         </is>
       </c>
       <c r="B208" t="n">
         <v>1</v>
       </c>
       <c r="C208" t="n">
-        <v>0.7193666733156965</v>
+        <v>0.6812291278731198</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>16/06/2025 00:03:01 HARWOOD KUALA BARAM-Branch online after power resumed.</t>
+          <t>Bank loan (offer) - Rm10K - 400K / 5-10 yrs - Debt Consolidate - Hard to get Loan Approve? - Credit card limit burst? - CTOS/ Blacklist issue? No worried, WE CAN SETTLE YOUR PROBLEM REPLY YES for details</t>
         </is>
       </c>
       <c r="B209" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C209" t="n">
-        <v>0.7122377193819807</v>
+        <v>0.7748755083192019</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>6/16/2025 12:06:07 AM PHKL Blk A Level 3 IVF Embryology Lab High Temperature Alarm.</t>
+          <t>112184102410 maybank</t>
         </is>
       </c>
       <c r="B210" t="n">
         <v>1</v>
       </c>
       <c r="C210" t="n">
-        <v>0.7193701303850935</v>
+        <v>0.5375658407103391</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>MCM geli je</t>
+          <t>Name : Ajit Budget : as low as possible when move in : 1july How many ppl stay : 8 Nepal friend or family : workers Occupation : security Working company name/ school name : security company Local / Foreigner : Race : nepal Tenancy 1 or 2 years : 2</t>
         </is>
       </c>
       <c r="B211" t="n">
         <v>0</v>
       </c>
       <c r="C211" t="n">
-        <v>0.6539764665711596</v>
+        <v>0.6734850273240237</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>U don't deserve a woman like</t>
+          <t>Company Kami sedia Free Angpao dan Bonus Special. Sila Claim dekat WS amoi sekarang : 01 13762 3807!</t>
         </is>
       </c>
       <c r="B212" t="n">
         <v>0</v>
       </c>
       <c r="C212" t="n">
-        <v>0.8338447772610857</v>
+        <v>0.7623925075638919</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>&lt;0920392&gt; System Armed</t>
+          <t>IMEI : 862004070888606 Location is http://www.google.com/maps/place/2.9094171,101.5637074 Your Location is : Latitude is 2.9094171, Longitude is 101.5637074 Location time : 2025-06-16 12:06:50 AM</t>
         </is>
       </c>
       <c r="B213" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C213" t="n">
-        <v>0.8170995748888776</v>
+        <v>0.6015893087494998</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>Mami..bgtau bang net tolong jap topupkan nombor digi abg ni ha RM 10 dulu,data abg dah tamat tempoh ha..</t>
+          <t>Ayo chat di WhatsApp, aplikasi yang cepat, sederhana, dan aman untuk berkirim pesan dan menelepon secara gratis. Dapatkan di https://whatsapp.com/dl/code=XGMOPQanYv?mode=c</t>
         </is>
       </c>
       <c r="B214" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C214" t="n">
-        <v>0.7476258314501569</v>
+        <v>0.6836774215806155</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>25O616 OOO6 (2) bq33 18/O6-21/O6-22/O6 *P 8O5O=1B 1S 8O5O=6B (IBox) GT=24</t>
+          <t>f6cbb53539260847dog_</t>
         </is>
       </c>
       <c r="B215" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C215" t="n">
-        <v>0.5683646238695905</v>
+        <v>0.6040565834153323</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>25O616 OOO6 (1) kb213O22 16/O6 /HE 3888=2B GT=2 Q1126388897 Points:OO13 1633 5196 7278</t>
+          <t>Bank loan (offer) - Rm10K - 400K / 5-10 yrs - Debt Consolidate - Hard to get Loan Approve? - Credit card limit burst? - CTOS/ Blacklist issue? No worried, WE CAN SETTLE YOUR PROBLEM REPLY YES for details</t>
         </is>
       </c>
       <c r="B216" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C216" t="n">
-        <v>0.7970710433375165</v>
+        <v>0.7748755083192019</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>Hi Mendo Buda,,,sorry saya block you WhatsApp dulu ya saya kena belajar untuk tidak mencintai you lagi ,,you jangan cari saya lagi fokus dengan cinta you mendo</t>
+          <t>https://images.app.goo.gl/QJQ6bqWbeMMFs9yh9</t>
         </is>
       </c>
       <c r="B217" t="n">
         <v>0</v>
       </c>
       <c r="C217" t="n">
-        <v>0.58005216351635</v>
+        <v>0.6585372552979617</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>ALARM S/ROOM BURGOGUAD Area 1 16 Jun 0h05</t>
+          <t>Tu ak ckp ak MMG dah tak blh nk belah la dgn prgai bbi sial pukimak KO ni....nk kurang AJK 24jam dgn ak lpas tu nk maki ak 24jam woiiii sial KO ingt ak ni tmpat maki KO ke pukimak anjing....ape KO ckp ko nk bawak Myvi KO kan ok cun...KO bawak ok...ak tak kan ambit punye pukimak babi....sbb KO tak ad hrmat ak cukup la ak tgk KO punye pergai MMG sampai ke mmpus tak kan berubah punye sial....so skrg ni keputusan ak muktamad ak tak kan dtg ambit ko nye sial....</t>
         </is>
       </c>
       <c r="B218" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C218" t="n">
-        <v>0.796003881777458</v>
+        <v>0.874505566130939</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>Amoi sini company goldenbet99,apa kabar sudah bossku,lama dah tak try spin mari.jackpot,free game,Bonusgame menanti anda. Web : goldenbet99 .com</t>
+          <t>(585200) AmowZBAEX</t>
         </is>
       </c>
       <c r="B219" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C219" t="n">
-        <v>0.641339186514549</v>
+        <v>0.7252358064759402</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>25O616 OOO6 (3) bq33 18/O6-21/O6-22/O6 *T 1911=3B 2S (Box) GT=6O</t>
+          <t>(T)=249.00 阿水 16/06/25</t>
         </is>
       </c>
       <c r="B220" t="n">
         <v>1</v>
       </c>
       <c r="C220" t="n">
-        <v>0.7668076790224836</v>
+        <v>0.5907609596144529</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>Flextronic H1 MsgText : J750_Sensor_3 RH Back to Normal Value : 59.0 %</t>
+          <t>Mudah: I'm interested in your ad on Mudah 2007 Perodua MYVI 1.3 EZ (A), please share more details with me.</t>
         </is>
       </c>
       <c r="B221" t="n">
         <v>1</v>
       </c>
       <c r="C221" t="n">
-        <v>0.7744296229731367</v>
+        <v>0.53076149367207</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>https://images.app.goo.gl/QJQ6bqWbeMMFs9yh9</t>
+          <t>Tengok live mantap joran tiktok. Abg fon xd line</t>
         </is>
       </c>
       <c r="B222" t="n">
         <v>1</v>
       </c>
       <c r="C222" t="n">
-        <v>0.5051811580005092</v>
+        <v>0.6091398730170102</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>Mak ngerak kol 7 aa</t>
+          <t>Balance:(-298), Bet:(-132), Total:(-430), Mau transfer lagi dah tauke,dah bnyk amount..tq</t>
         </is>
       </c>
       <c r="B223" t="n">
         <v>0</v>
       </c>
       <c r="C223" t="n">
-        <v>0.8772887792048054</v>
+        <v>0.7258812055695681</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>Bkt.Berlian Res R 24,0 20:26 unet 23.239.111.108 352134012067105 0508 0 1 3 12 62 17600 17600 0.00OK In1=1 In2=0 In3=0</t>
+          <t>To join the meeting on Google Meet, click this link: https://meet.google.com/bxe-hyrj-oxe Or open Meet and enter this code: bxe-hyrj-oxe</t>
         </is>
       </c>
       <c r="B224" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C224" t="n">
-        <v>0.6311399098095494</v>
+        <v>0.5132361187826963</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>Mudah: I'm interested in your ad on Mudah Flat Tmn Melati (Partly furnished+Air Cond Near LRT) Ready to move in, please share more details with me.</t>
+          <t>Mudah: I'm interested in your ad on Mudah Land in Beranang, Ulu Langat, Selangor, please share more details with me.</t>
         </is>
       </c>
       <c r="B225" t="n">
         <v>0</v>
       </c>
       <c r="C225" t="n">
-        <v>0.8403708692249852</v>
+        <v>0.6610363588441043</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>IU6tZvtQRiix</t>
+          <t>BX99:您被选了(chye666)!恭喜您获得228次免费旋转。存RM50就解锁!bx99my{dot}com</t>
         </is>
       </c>
       <c r="B226" t="n">
         <v>0</v>
       </c>
       <c r="C226" t="n">
-        <v>0.8166618700680333</v>
+        <v>0.6802301869500308</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>Mudah: I'm interested in your ad on Mudah Hata Square Female Room Rental Fully Furnished (June 2025), please share more details with me.</t>
+          <t>Rumah Pam Taman Cendana Suction Low Recovery</t>
         </is>
       </c>
       <c r="B227" t="n">
         <v>0</v>
       </c>
       <c r="C227" t="n">
-        <v>0.5081961508450108</v>
+        <v>0.5596161947358279</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>To join the meeting on Google Meet, click this link: https://meet.google.com/bxe-hyrj-oxe Or open Meet and enter this code: bxe-hyrj-oxe</t>
+          <t>BX99: (ID: yonglee04) Congrats, you are one of todays lucky picks. Deposit RM50 to get 228 FREE Spins. Dont miss out! bx99my{dot}com</t>
         </is>
       </c>
       <c r="B228" t="n">
         <v>1</v>
       </c>
       <c r="C228" t="n">
-        <v>0.6654521469417018</v>
+        <v>0.6403908266913266</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>To join the meeting on Google Meet, click this link: https://meet.google.com/bxe-hyrj-oxe Or open Meet and enter this code: bxe-hyrj-oxe</t>
+          <t>BX99:您被选了(hui173)!恭喜您获得228次免费旋转。存RM50就解锁!bx99my{dot}com</t>
         </is>
       </c>
       <c r="B229" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C229" t="n">
-        <v>0.6654521469417018</v>
+        <v>0.5500613317597537</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>Abg hanya menunggu jawapan terakhir dri syg utk berjumpa ..kalau syg tak menjawab permintaan terakhir Abg abg akn Pham tiada lagi hubungan kita.....</t>
+          <t>U388: 嘿! 您升级后的RM50免费积分感到孤独。赶快在它们离开前领取吧!u388my{dot}com</t>
         </is>
       </c>
       <c r="B230" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C230" t="n">
-        <v>0.8409186657127934</v>
+        <v>0.6092501416098447</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>Boleh dapatkan maklumat mengenaie diri anda terima kasih</t>
+          <t>Ari 2023 sampai 2025 agi mh enda nmu puas bula..sampai mati.mh d nya bula</t>
         </is>
       </c>
       <c r="B231" t="n">
         <v>0</v>
       </c>
       <c r="C231" t="n">
-        <v>0.8493267353233891</v>
+        <v>0.8054012522805362</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>(311720) lezwrxOKjl</t>
+          <t>明天4000我不太可能,我最快也要等到我新山的工完,我还可以安排3000给你,不过这个是月尾的事了 如果你是说2/300,明天星期一,还行,我明天要去收钱,可以2/300</t>
         </is>
       </c>
       <c r="B232" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C232" t="n">
-        <v>0.629185283595602</v>
+        <v>0.7410620317567019</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>F re3 Cr3dlt M€ g@/K1 §§/P u§§ y Was@p - 01_46139668 0ng m@li Jajwnsmz</t>
+          <t>Bank loan (offer) - Rm10K - 400K / 5-10 yrs - Debt Consolidate - Hard to get Loan Approve? - Credit card limit burst? - CTOS/ Blacklist issue? No worried, WE CAN SETTLE YOUR PROBLEM REPLY YES for details</t>
         </is>
       </c>
       <c r="B233" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C233" t="n">
-        <v>0.7677073721232814</v>
+        <v>0.77487535930759</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>jgn awak mok mcm iii</t>
+          <t>最后的机会!只需存款RM50即可获得238次免费旋转。优惠今晚到期。立即在12huatmy{dot}com领取!</t>
         </is>
       </c>
       <c r="B234" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C234" t="n">
-        <v>0.7663739566150112</v>
+        <v>0.8959923551190524</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>END - 06/15 22:58 AC2:No connection</t>
+          <t>15/6 Talang - 250 Syukeri - 50 Rani - 50 Pait kangkong - 50 Saidon - 100 ( tng ) Abu shamah - 50 Fikri fatin - 100 Koyong - 50</t>
         </is>
       </c>
       <c r="B235" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C235" t="n">
-        <v>0.8918451313319606</v>
+        <v>0.7247746751416354</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>rm30 can?</t>
+          <t>Dok.Mana..Buat15</t>
         </is>
       </c>
       <c r="B236" t="n">
         <v>0</v>
       </c>
       <c r="C236" t="n">
-        <v>0.8095768447575169</v>
+        <v>0.7120455966103701</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>Bank loan (offer) - Rm10K - 400K / 5-10 yrs - Debt Consolidate - Hard to get Loan Approve? - Credit card limit burst? - CTOS/ Blacklist issue? No worried, WE CAN SETTLE YOUR PROBLEM REPLY YES for details</t>
+          <t>BX99: (ID: suhiom88) Congrats, you are one of todays lucky picks. Deposit RM50 to get 228 FREE Spins. Dont miss out! bx99my{dot}com</t>
         </is>
       </c>
       <c r="B237" t="n">
         <v>0</v>
       </c>
       <c r="C237" t="n">
-        <v>0.626309877222498</v>
+        <v>0.5082820520508914</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>112184102410 maybank</t>
+          <t>ACE66: We missed you! Here's RM50 free credit to kickstart your winning journey with us. Claim at ace66my{dot}com now!</t>
         </is>
       </c>
       <c r="B238" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C238" t="n">
-        <v>0.7690163497271938</v>
+        <v>0.7382592127431064</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>Name : Ajit Budget : as low as possible when move in : 1july How many ppl stay : 8 Nepal friend or family : workers Occupation : security Working company name/ school name : security company Local / Foreigner : Race : nepal Tenancy 1 or 2 years : 2</t>
+          <t>Assalamualaikum Aji apa khabar ini Ape.ini daripada no 0199682615.ini no baru sy</t>
         </is>
       </c>
       <c r="B239" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C239" t="n">
-        <v>0.5471590999904079</v>
+        <v>0.540124999057117</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>Satgi lepas tutup kedai abg P lewat skit,abg skit tumit jalan banyak 2/3hari ni</t>
+          <t>FPX RESOLVED P-250615: Failure rate increase on Database service EFPXPROD:Failure rate increase</t>
         </is>
       </c>
       <c r="B240" t="n">
         <v>0</v>
       </c>
       <c r="C240" t="n">
-        <v>0.8161616082844334</v>
+        <v>0.8401178882229953</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>Beli number baru,,, number Lama abaikan.. Whassup ko pun keli dah bolh Baca.. Pandai sgt</t>
+          <t>9----15-6 rm - 198 198 +90= - 288</t>
         </is>
       </c>
       <c r="B241" t="n">
         <v>0</v>
       </c>
       <c r="C241" t="n">
-        <v>0.8663669731077748</v>
+        <v>0.5424901113618045</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>Company Kami sedia Free Angpao dan Bonus Special. Sila Claim dekat WS amoi sekarang : 01 13762 3807!</t>
+          <t>#vivo#simc##862241033847002#1#89601624050700854110#</t>
         </is>
       </c>
       <c r="B242" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C242" t="n">
-        <v>0.6387143190559941</v>
+        <v>0.5939794316183896</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>IMEI : 862004070888606 Location is http://www.google.com/maps/place/2.9094171,101.5637074 Your Location is : Latitude is 2.9094171, Longitude is 101.5637074 Location time : 2025-06-16 12:06:50 AM</t>
+          <t>FPX RESOLVED P-250615: Failure rate increase on Database service EFPXPROD:Failure rate increase</t>
         </is>
       </c>
       <c r="B243" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C243" t="n">
-        <v>0.5726050381007595</v>
+        <v>0.8401178882229953</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>Ayo chat di WhatsApp, aplikasi yang cepat, sederhana, dan aman untuk berkirim pesan dan menelepon secara gratis. Dapatkan di https://whatsapp.com/dl/code=XGMOPQanYv?mode=c</t>
+          <t>196242 GnZwmVwXwj</t>
         </is>
       </c>
       <c r="B244" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C244" t="n">
-        <v>0.6905160601791935</v>
+        <v>0.6478694810759397</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>f6cbb53539260847dog_</t>
+          <t>https://images.app.goo.gl/sGYYfKrpJYe4wMc76</t>
         </is>
       </c>
       <c r="B245" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C245" t="n">
-        <v>0.577918136531393</v>
+        <v>0.5621905789483218</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>Bank loan (offer) - Rm10K - 400K / 5-10 yrs - Debt Consolidate - Hard to get Loan Approve? - Credit card limit burst? - CTOS/ Blacklist issue? No worried, WE CAN SETTLE YOUR PROBLEM REPLY YES for details</t>
+          <t>Company Kami sedia Free Angpao dan Bonus Special. Sila Claim dekat WS amoi sekarang : 01 13762 3807!</t>
         </is>
       </c>
       <c r="B246" t="n">
         <v>0</v>
       </c>
       <c r="C246" t="n">
-        <v>0.626309877222498</v>
+        <v>0.7623925075638919</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>https://images.app.goo.gl/QJQ6bqWbeMMFs9yh9</t>
+          <t>2957+126+174=3257</t>
         </is>
       </c>
       <c r="B247" t="n">
         <v>1</v>
       </c>
       <c r="C247" t="n">
-        <v>0.5051811580005092</v>
+        <v>0.5519635810744138</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>Tu ak ckp ak MMG dah tak blh nk belah la dgn prgai bbi sial pukimak KO ni....nk kurang AJK 24jam dgn ak lpas tu nk maki ak 24jam woiiii sial KO ingt ak ni tmpat maki KO ke pukimak anjing....ape KO ckp ko nk bawak Myvi KO kan ok cun...KO bawak ok...ak tak kan ambit punye pukimak babi....sbb KO tak ad hrmat ak cukup la ak tgk KO punye pergai MMG sampai ke mmpus tak kan berubah punye sial....so skrg ni keputusan ak muktamad ak tak kan dtg ambit ko nye sial....</t>
+          <t>Welcome to I BC22: Level up your gaming experience, win like a PRO! Discover exciting promotions and hottest games at ibc22mys{dot}com now!</t>
         </is>
       </c>
       <c r="B248" t="n">
         <v>0</v>
       </c>
       <c r="C248" t="n">
-        <v>0.5646182056126194</v>
+        <v>0.6077189908135562</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>(585200) AmowZBAEX</t>
+          <t>9----15-6 rm 420</t>
         </is>
       </c>
       <c r="B249" t="n">
         <v>0</v>
       </c>
       <c r="C249" t="n">
-        <v>0.5866782191743559</v>
+        <v>0.771307186852756</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>(T)=249.00 阿水 16/06/25</t>
+          <t>To join the meeting on Google Meet, click this link: https://meet.google.com/gow-xyon-gdu Or open Meet and enter this code: gow-xyon-gdu</t>
         </is>
       </c>
       <c r="B250" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C250" t="n">
-        <v>0.7353277679930025</v>
+        <v>0.7086298928368716</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>Mudah: I'm interested in your ad on Mudah 2007 Perodua MYVI 1.3 EZ (A), please share more details with me.</t>
+          <t>To join the meeting on Google Meet, click this link: https://meet.google.com/gow-xyon-gdu Or open Meet and enter this code: gow-xyon-gdu</t>
         </is>
       </c>
       <c r="B251" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C251" t="n">
-        <v>0.6768153783331209</v>
+        <v>0.7086298928368716</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>Tengok live mantap joran tiktok. Abg fon xd line</t>
+          <t>‎Let's chat on WhatsApp! It's a fast, simple, and secure app we can use to message and call each other for free. Get it at</t>
         </is>
       </c>
       <c r="B252" t="n">
         <v>1</v>
       </c>
       <c r="C252" t="n">
-        <v>0.8030220743665987</v>
+        <v>0.508270038593945</v>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>Balance:(-298), Bet:(-132), Total:(-430), Mau transfer lagi dah tauke,dah bnyk amount..tq</t>
+          <t>BX99: (ID: ra1244) Congrats, you are one of todays lucky picks. Deposit RM50 to get 228 FREE Spins. Dont miss out! bx99my{dot}com</t>
         </is>
       </c>
       <c r="B253" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C253" t="n">
-        <v>0.6220074418534941</v>
+        <v>0.5498523249518247</v>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>To join the meeting on Google Meet, click this link: https://meet.google.com/bxe-hyrj-oxe Or open Meet and enter this code: bxe-hyrj-oxe</t>
+          <t>5Why you blocked me? king I just need RM300 now and let me secure a place by paying a deposit tomorrow me!in and put it this into your calculation. I need to confirm and pay the deposit tomorrow morning</t>
         </is>
       </c>
       <c r="B254" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C254" t="n">
-        <v>0.6359874483595186</v>
+        <v>0.57319860316402</v>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>Mudah: I'm interested in your ad on Mudah Land in Beranang, Ulu Langat, Selangor, please share more details with me.</t>
+          <t>Company Kami sedia Free Angpao dan Bonus Special. Sila Claim dekat WS amoi sekarang : 01 13762 3807!</t>
         </is>
       </c>
       <c r="B255" t="n">
         <v>0</v>
       </c>
       <c r="C255" t="n">
-        <v>0.5436365130891508</v>
+        <v>0.7623925075638919</v>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>BX99:您被选了(chye666)!恭喜您获得228次免费旋转。存RM50就解锁!bx99my{dot}com</t>
+          <t>BX99:您被选了(nms413191)!恭喜您获得228次免费旋转。存RM50就解锁!bx99my{dot}com</t>
         </is>
       </c>
       <c r="B256" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C256" t="n">
-        <v>0.6059200886239714</v>
+        <v>0.5603886976134153</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>Rumah Pam Taman Cendana Suction Low Recovery</t>
+          <t>Leela pa and u add me in whatsapp 1st then i can send u what tje conversation actual was</t>
         </is>
       </c>
       <c r="B257" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C257" t="n">
-        <v>0.6065377470503145</v>
+        <v>0.880622612010303</v>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>BX99: (ID: yonglee04) Congrats, you are one of todays lucky picks. Deposit RM50 to get 228 FREE Spins. Dont miss out! bx99my{dot}com</t>
+          <t>*123*849934199814250#</t>
         </is>
       </c>
       <c r="B258" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C258" t="n">
-        <v>0.7526456591139131</v>
+        <v>0.7622396514523654</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>BX99:您被选了(hui173)!恭喜您获得228次免费旋转。存RM50就解锁!bx99my{dot}com</t>
+          <t>Nk ajak kwn baru dia tidak ada duit</t>
         </is>
       </c>
       <c r="B259" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C259" t="n">
-        <v>0.5264093753347688</v>
+        <v>0.8531402514088778</v>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>U388: 嘿! 您升级后的RM50免费积分感到孤独。赶快在它们离开前领取吧!u388my{dot}com</t>
+          <t>Selamat Hari Lahir. Selamat bertambah usia. Semoga apa yang kau semogakan, tersemoga. Semoga terus suksess dalam apa jua. Sihat, berbahagia &amp; kuat selalu. Thank you sudah jadi kawan yang baik utk beberapa hari. Selepas tu, dont know lah jadi apa suda. Its not the same Hafiz Ikhwan. Semoga perangai yang tak baik, cepat2 lah diubah. Semoga masih sempat utk insaf &amp; jadi manusia yang berguna. Oh yaa, aku ada text ibu kau. Tanya kau suka makan apa. Ibu cakqp, kau suka brownies. And i think i will cook brownies for you. Sudi tak terima? Saja tanya awal, kang tak terima. Aku tak buat lah. Memandangkan esok aku dah apply cuti, pastu ko teda pun d Tawau. So i'll celebrate n menikmati cuti itu. Nanti ko balik roger lah, i'll belanja u makan. Itupun kalau sudi lah. Kalau tak, its okey. Tak paksa. Hmm tu jaaa laa, selamat hari lahir beib. ly</t>
         </is>
       </c>
       <c r="B260" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C260" t="n">
-        <v>0.7078223701963716</v>
+        <v>0.6247035131562381</v>
       </c>
     </row>
     <row r="261">
@@ -3822,1476 +3822,813 @@
         <v>0</v>
       </c>
       <c r="C261" t="n">
-        <v>0.614550304745645</v>
+        <v>0.8054012522805362</v>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>明天4000我不太可能,我最快也要等到我新山的工完,我还可以安排3000给你,不过这个是月尾的事了 如果你是说2/300,明天星期一,还行,我明天要去收钱,可以2/300</t>
+          <t>Bik noh rah mulek bituh jagak noh</t>
         </is>
       </c>
       <c r="B262" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C262" t="n">
-        <v>0.61100496086976</v>
+        <v>0.5020636453520627</v>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>Bank loan (offer) - Rm10K - 400K / 5-10 yrs - Debt Consolidate - Hard to get Loan Approve? - Credit card limit burst? - CTOS/ Blacklist issue? No worried, WE CAN SETTLE YOUR PROBLEM REPLY YES for details</t>
+          <t>Amoi sini company goldenbet99,apa kabar sudah bossku,lama dah tak try spin mari.jackpot,free game,Bonusgame menanti anda. Web ; goldenbet99 .com</t>
         </is>
       </c>
       <c r="B263" t="n">
         <v>0</v>
       </c>
       <c r="C263" t="n">
-        <v>0.6906784001340575</v>
+        <v>0.6442074046242862</v>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>最后的机会!只需存款RM50即可获得238次免费旋转。优惠今晚到期。立即在12huatmy{dot}com领取!</t>
+          <t>&lt;0528752&gt; AC Power Failure</t>
         </is>
       </c>
       <c r="B264" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C264" t="n">
-        <v>0.860946846341104</v>
+        <v>0.7062027587782712</v>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>15/6 Talang - 250 Syukeri - 50 Rani - 50 Pait kangkong - 50 Saidon - 100 ( tng ) Abu shamah - 50 Fikri fatin - 100 Koyong - 50</t>
+          <t>TOWER SG SELANGOR, S.Mode=NORWL DANGER=219.84m, RF LIGHT=1.5mm, RFDaily= 0.0mm, RFCumm= 52.5mm, Batt Nor= 12.8Vdc, 000, 16062025,00:04</t>
         </is>
       </c>
       <c r="B265" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C265" t="n">
-        <v>0.5857158425798125</v>
+        <v>0.660466505516705</v>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>HARAP TAK SALAH LAGI</t>
+          <t>Company Kami sedia Free Angpao dan Bonus Special. Sila Claim dekat WS amoi sekarang : 01 13762 3807!</t>
         </is>
       </c>
       <c r="B266" t="n">
         <v>0</v>
       </c>
       <c r="C266" t="n">
-        <v>0.7292320552816099</v>
+        <v>0.7623926863778262</v>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>Dok.Mana..Buat15</t>
+          <t>Mudah: I'm interested in your ad on Mudah Anak Tupai, please share more details with me.</t>
         </is>
       </c>
       <c r="B267" t="n">
         <v>0</v>
       </c>
       <c r="C267" t="n">
-        <v>0.5348485830774016</v>
+        <v>0.7591400013077884</v>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>BX99: (ID: suhiom88) Congrats, you are one of todays lucky picks. Deposit RM50 to get 228 FREE Spins. Dont miss out! bx99my{dot}com</t>
+          <t>#vivo#simc##862241033847002#1#89601624050700854110#</t>
         </is>
       </c>
       <c r="B268" t="n">
         <v>1</v>
       </c>
       <c r="C268" t="n">
-        <v>0.58967201676467</v>
+        <v>0.5939794316183896</v>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>ACE66: We missed you! Here's RM50 free credit to kickstart your winning journey with us. Claim at ace66my{dot}com now!</t>
+          <t>&lt;0528752&gt; AC Power Restored</t>
         </is>
       </c>
       <c r="B269" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C269" t="n">
-        <v>0.7031427446355528</v>
+        <v>0.5447595848929258</v>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>Assalamualaikum Aji apa khabar ini Ape.ini daripada no 0199682615.ini no baru sy</t>
+          <t>https://images.app.goo.gl/sGYYfKrpJYe4wMc76</t>
         </is>
       </c>
       <c r="B270" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C270" t="n">
-        <v>0.6391259905348116</v>
+        <v>0.5621905789483218</v>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>FPX RESOLVED P-250615: Failure rate increase on Database service EFPXPROD:Failure rate increase</t>
+          <t>Company Kami sedia Free Angpao dan Bonus Special. Sila Claim dekat WS amoi sekarang : 01 13762 3807!</t>
         </is>
       </c>
       <c r="B271" t="n">
         <v>0</v>
       </c>
       <c r="C271" t="n">
-        <v>0.7151490572442717</v>
+        <v>0.7623926863778262</v>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>9----15-6 rm - 198 198 +90= - 288</t>
+          <t>http://maps.google.com/maps?f=q&amp;q=5.849513,118.039284</t>
         </is>
       </c>
       <c r="B272" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C272" t="n">
-        <v>0.6213074800024324</v>
+        <v>0.8330107197869449</v>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>Jgn tnye npe kte ttp PGL awak biey ye</t>
+          <t>http://maps.google.com/maps?f=q&amp;q=5.849513,118.039284</t>
         </is>
       </c>
       <c r="B273" t="n">
         <v>0</v>
       </c>
       <c r="C273" t="n">
-        <v>0.6958115521421141</v>
+        <v>0.8330106005776553</v>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>#vivo#simc##862241033847002#1#89601624050700854110#</t>
+          <t>F re3 Cr3dlt M€ g@/K1 §§/P u§§ y Was@p - 01_46139668 0ng m@li Jajwnsns</t>
         </is>
       </c>
       <c r="B274" t="n">
         <v>1</v>
       </c>
       <c r="C274" t="n">
-        <v>0.7418716427336031</v>
+        <v>0.5711763038527341</v>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>FPX RESOLVED P-250615: Failure rate increase on Database service EFPXPROD:Failure rate increase</t>
+          <t>To join the meeting on Google Meet, click this link: https://meet.google.com/gow-xyon-gdu Or open Meet and enter this code: gow-xyon-gdu</t>
         </is>
       </c>
       <c r="B275" t="n">
         <v>0</v>
       </c>
       <c r="C275" t="n">
-        <v>0.7151490572442717</v>
+        <v>0.7086298928368716</v>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>380</t>
+          <t>E T: Wlcm u, MAX-M u=123281882465 p=TTtt2773 on:16/06 00:09:51</t>
         </is>
       </c>
       <c r="B276" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C276" t="n">
-        <v>0.7789318684091276</v>
+        <v>0.6631398930441709</v>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>196242 GnZwmVwXwj</t>
+          <t>Let's chat on WhatsApp! It's a fast, simple, and secure app we can use to message and call each other for free. Get it at https://whatsapp.com/dl/</t>
         </is>
       </c>
       <c r="B277" t="n">
         <v>1</v>
       </c>
       <c r="C277" t="n">
-        <v>0.822940933371573</v>
+        <v>0.7418096198927732</v>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>https://images.app.goo.gl/sGYYfKrpJYe4wMc76</t>
+          <t>160166186588,Rohani binti Hassan @ serbane</t>
         </is>
       </c>
       <c r="B278" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C278" t="n">
-        <v>0.5885683771620088</v>
+        <v>0.6757947669137149</v>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>Company Kami sedia Free Angpao dan Bonus Special. Sila Claim dekat WS amoi sekarang : 01 13762 3807!</t>
+          <t>l ALWAYS LOVE U G009</t>
         </is>
       </c>
       <c r="B279" t="n">
         <v>0</v>
       </c>
       <c r="C279" t="n">
-        <v>0.6798649552812285</v>
+        <v>0.7786114678490786</v>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>2957+126+174=3257</t>
+          <t>Company Kami sedia Free Angpao dan Bonus Special. Sila Claim dekat WS amoi sekarang : 01 13762 3807!</t>
         </is>
       </c>
       <c r="B280" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C280" t="n">
-        <v>0.7114272591123872</v>
+        <v>0.7623926863778262</v>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>Welcome to I BC22: Level up your gaming experience, win like a PRO! Discover exciting promotions and hottest games at ibc22mys{dot}com now!</t>
+          <t>Ayo chat di WhatsApp, aplikasi yang cepat, sederhana, dan aman untuk berkirim pesan dan menelepon secara gratis. Dapatkan di https://whatsapp.com/dl/code=wPUUTXFumG?mode=c</t>
         </is>
       </c>
       <c r="B281" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C281" t="n">
-        <v>0.5180269357214266</v>
+        <v>0.7536352143395572</v>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>9----15-6 rm 420</t>
+          <t>16号了咯,你到底要进钱给我吗</t>
         </is>
       </c>
       <c r="B282" t="n">
         <v>0</v>
       </c>
       <c r="C282" t="n">
-        <v>0.6315223697175688</v>
+        <v>0.8709143564808993</v>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>To join the meeting on Google Meet, click this link: https://meet.google.com/gow-xyon-gdu Or open Meet and enter this code: gow-xyon-gdu</t>
+          <t>595291+5 407412+7</t>
         </is>
       </c>
       <c r="B283" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C283" t="n">
-        <v>0.5848308924188322</v>
+        <v>0.63017715357655</v>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>To join the meeting on Google Meet, click this link: https://meet.google.com/gow-xyon-gdu Or open Meet and enter this code: gow-xyon-gdu</t>
+          <t>#vivo#simc##862241033847002#1#89601624050700854110#</t>
         </is>
       </c>
       <c r="B284" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C284" t="n">
-        <v>0.5848308924188322</v>
+        <v>0.5939794316183896</v>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>‎Let's chat on WhatsApp! It's a fast, simple, and secure app we can use to message and call each other for free. Get it at</t>
+          <t>1 ,L2 FMC 19 R1 TMP 02 (CIMB-SVR1),IN CRITICAL MODE, Monday, June 16, 2025 12:11:13 AM.</t>
         </is>
       </c>
       <c r="B285" t="n">
         <v>1</v>
       </c>
       <c r="C285" t="n">
-        <v>0.5677910856456662</v>
+        <v>0.5861851706396909</v>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>BX99: (ID: ra1244) Congrats, you are one of todays lucky picks. Deposit RM50 to get 228 FREE Spins. Dont miss out! bx99my{dot}com</t>
+          <t>Call From HQ Jessy Congratulations For You FRxx P01N TRY Gam3 Whatsap : 6 0 1 3 4 4 4 4 1 8 8</t>
         </is>
       </c>
       <c r="B286" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C286" t="n">
-        <v>0.6608713082523251</v>
+        <v>0.5216650829423098</v>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>5Why you blocked me? king I just need RM300 now and let me secure a place by paying a deposit tomorrow me!in and put it this into your calculation. I need to confirm and pay the deposit tomorrow morning</t>
+          <t>BX99:您被选了(bonnieliew)!恭喜您获得228次免费旋转。存RM50就解锁!bx99my{dot}com</t>
         </is>
       </c>
       <c r="B287" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C287" t="n">
-        <v>0.5556946210117245</v>
+        <v>0.6492538914788394</v>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>Company Kami sedia Free Angpao dan Bonus Special. Sila Claim dekat WS amoi sekarang : 01 13762 3807!</t>
+          <t>https://images.app.goo.gl/3fsFEcNTAXyoPA4Z8</t>
         </is>
       </c>
       <c r="B288" t="n">
         <v>0</v>
       </c>
       <c r="C288" t="n">
-        <v>0.6754754968433475</v>
+        <v>0.6632926926720767</v>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>BX99:您被选了(nms413191)!恭喜您获得228次免费旋转。存RM50就解锁!bx99my{dot}com</t>
+          <t>Amoi sini company goldenbet99,apa kabar sudah bossku,lama dah tak try spin mari.jackpot,free game,Bonusgame menanti anda. Web ; goldenbet99 .com</t>
         </is>
       </c>
       <c r="B289" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C289" t="n">
-        <v>0.6643276623935604</v>
+        <v>0.6442074046242862</v>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>Leela pa and u add me in whatsapp 1st then i can send u what tje conversation actual was</t>
+          <t>Company Kami sedia Free Angpao dan Bonus Special. Sila Claim dekat WS amoi sekarang : 01 13762 3807!</t>
         </is>
       </c>
       <c r="B290" t="n">
         <v>0</v>
       </c>
       <c r="C290" t="n">
-        <v>0.796002287462244</v>
+        <v>0.7623926863778262</v>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>*123*849934199814250#</t>
+          <t>1 ,L2 FMC 19 R1 TMP 02 (CIMB-SVR1),IN CRITICAL MODE, Monday, June 16, 2025 12:11:13 AM.</t>
         </is>
       </c>
       <c r="B291" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C291" t="n">
-        <v>0.6676377542762851</v>
+        <v>0.5861851706396909</v>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>Nk ajak kwn baru dia tidak ada duit</t>
+          <t>HIJACK.HIJACK.HIJACK. KeyOff 24.9V 0km/h N5.09748,E100.44873 http://map.dftracker.com/?loc=3923365642E484</t>
         </is>
       </c>
       <c r="B292" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C292" t="n">
-        <v>0.7004537769107914</v>
+        <v>0.727303995121655</v>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>Selamat Hari Lahir. Selamat bertambah usia. Semoga apa yang kau semogakan, tersemoga. Semoga terus suksess dalam apa jua. Sihat, berbahagia &amp; kuat selalu. Thank you sudah jadi kawan yang baik utk beberapa hari. Selepas tu, dont know lah jadi apa suda. Its not the same Hafiz Ikhwan. Semoga perangai yang tak baik, cepat2 lah diubah. Semoga masih sempat utk insaf &amp; jadi manusia yang berguna. Oh yaa, aku ada text ibu kau. Tanya kau suka makan apa. Ibu cakqp, kau suka brownies. And i think i will cook brownies for you. Sudi tak terima? Saja tanya awal, kang tak terima. Aku tak buat lah. Memandangkan esok aku dah apply cuti, pastu ko teda pun d Tawau. So i'll celebrate n menikmati cuti itu. Nanti ko balik roger lah, i'll belanja u makan. Itupun kalau sudi lah. Kalau tak, its okey. Tak paksa. Hmm tu jaaa laa, selamat hari lahir beib. ly</t>
+          <t>Rm374</t>
         </is>
       </c>
       <c r="B293" t="n">
         <v>1</v>
       </c>
       <c r="C293" t="n">
-        <v>0.5286313704700375</v>
+        <v>0.7029068603407712</v>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>Ari 2023 sampai 2025 agi mh enda nmu puas bula..sampai mati.mh d nya bula</t>
+          <t>RM0 ZUS Coffee: Welcome to ZUS Coffee! Your 4 digits verification code is 4089. Enjoy!</t>
         </is>
       </c>
       <c r="B294" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C294" t="n">
-        <v>0.6270473190097904</v>
+        <v>0.7461503877531858</v>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>Bik noh rah mulek bituh jagak noh</t>
+          <t>Company Kami sedia Free Angpao dan Bonus Special. Sila Claim dekat WS amoi sekarang : 01 13762 3807!</t>
         </is>
       </c>
       <c r="B295" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C295" t="n">
-        <v>0.7248385361881161</v>
+        <v>0.7623925075638919</v>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>Amoi sini company goldenbet99,apa kabar sudah bossku,lama dah tak try spin mari.jackpot,free game,Bonusgame menanti anda. Web ; goldenbet99 .com</t>
+          <t>https://play.google.com/store/apps/details?id=castle.heroes.tower.defense.kingdom.magic.battle.archer</t>
         </is>
       </c>
       <c r="B296" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C296" t="n">
-        <v>0.5087528042049313</v>
+        <v>0.6171393857110171</v>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>&lt;0528752&gt; AC Power Failure</t>
+          <t>https://play.google.com/store/apps/details?id=castle.heroes.tower.defense.kingdom.magic.battle.archer</t>
         </is>
       </c>
       <c r="B297" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C297" t="n">
-        <v>0.8598671964855099</v>
+        <v>0.6171393857110171</v>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>TOWER SG SELANGOR, S.Mode=NORWL DANGER=219.84m, RF LIGHT=1.5mm, RFDaily= 0.0mm, RFCumm= 52.5mm, Batt Nor= 12.8Vdc, 000, 16062025,00:04</t>
+          <t>Wlkmslm ct blm gaji lagi atta kurang duit bulan ini</t>
         </is>
       </c>
       <c r="B298" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C298" t="n">
-        <v>0.7977310828418637</v>
+        <v>0.8749843106377749</v>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>Company Kami sedia Free Angpao dan Bonus Special. Sila Claim dekat WS amoi sekarang : 01 13762 3807!</t>
+          <t>Arming with keyswitch #1 Your Alarm Site SST PERIMETER 16 Jun 0h13</t>
         </is>
       </c>
       <c r="B299" t="n">
         <v>0</v>
       </c>
       <c r="C299" t="n">
-        <v>0.6754754968433475</v>
+        <v>0.8523178563225894</v>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>Mudah: I'm interested in your ad on Mudah Anak Tupai, please share more details with me.</t>
+          <t>Line bb habis, nnti bb chat blik nehh</t>
         </is>
       </c>
       <c r="B300" t="n">
         <v>0</v>
       </c>
       <c r="C300" t="n">
-        <v>0.6327979155330753</v>
+        <v>0.8885400757897525</v>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>#vivo#simc##862241033847002#1#89601624050700854110#</t>
+          <t>To join the meeting on Google Meet, click this link: https://meet.google.com/gow-xyon-gdu Or open Meet and enter this code: gow-xyon-gdu</t>
         </is>
       </c>
       <c r="B301" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C301" t="n">
-        <v>0.7289137057514096</v>
+        <v>0.7086298928368716</v>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>&lt;0528752&gt; AC Power Restored</t>
+          <t>To join the meeting on Google Meet, click this link: https://meet.google.com/gow-xyon-gdu Or open Meet and enter this code: gow-xyon-gdu</t>
         </is>
       </c>
       <c r="B302" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C302" t="n">
-        <v>0.6852596215457821</v>
+        <v>0.7086298928368716</v>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>https://images.app.goo.gl/sGYYfKrpJYe4wMc76</t>
+          <t>Nagios:eth9 Bandwidth - Outbound Host: exadomdbracp5 IP: 10.188.201.123 CRITICAL: Bytes_sent was 1206.05 MB/s 16/06/2025 00:10:38</t>
         </is>
       </c>
       <c r="B303" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C303" t="n">
-        <v>0.573215823575964</v>
+        <v>0.79802228666431</v>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>Ma da nyaa kjn adp MU tuui²...ma da nyaa tiwas de adp MU...bukan nyaa doi byr..</t>
+          <t>Call From HQ Jessy Congratulations For You FRxx P01N TRY Gam3 Whatsap : 6 0 1 3 4 4 4 4 1 8 8</t>
         </is>
       </c>
       <c r="B304" t="n">
         <v>0</v>
       </c>
       <c r="C304" t="n">
-        <v>0.7342231460361576</v>
+        <v>0.5216650829423098</v>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>Ngan number blkg tu skali</t>
+          <t>&lt;0528752&gt; AC Power Failure</t>
         </is>
       </c>
       <c r="B305" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C305" t="n">
-        <v>0.8715505190639591</v>
+        <v>0.7062027587782712</v>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>Company Kami sedia Free Angpao dan Bonus Special. Sila Claim dekat WS amoi sekarang : 01 13762 3807!</t>
+          <t>Nagios:eth9 Bandwidth - Outbound Host: exadomdbracp5 IP: 10.188.201.123 CRITICAL: Bytes_sent was 1206.05 MB/s 16/06/2025 00:10:38</t>
         </is>
       </c>
       <c r="B306" t="n">
         <v>0</v>
       </c>
       <c r="C306" t="n">
-        <v>0.6754754372387027</v>
+        <v>0.79802228666431</v>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>http://maps.google.com/maps?f=q&amp;q=5.849513,118.039284</t>
+          <t>Nagios:eth9 Bandwidth - Outbound Host: exadomdbracp5 IP: 10.188.201.123 CRITICAL: Bytes_sent was 1206.05 MB/s 16/06/2025 00:10:38</t>
         </is>
       </c>
       <c r="B307" t="n">
         <v>0</v>
       </c>
       <c r="C307" t="n">
-        <v>0.7352361865787601</v>
+        <v>0.79802228666431</v>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>http://maps.google.com/maps?f=q&amp;q=5.849513,118.039284</t>
+          <t>#vivo#simc##862241033847002#1#89601624050700854110#</t>
         </is>
       </c>
       <c r="B308" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C308" t="n">
-        <v>0.7352361865787601</v>
+        <v>0.5939794316183896</v>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>F re3 Cr3dlt M€ g@/K1 §§/P u§§ y Was@p - 01_46139668 0ng m@li Jajwnsns</t>
+          <t>&lt;0528752&gt; AC Power Restored</t>
         </is>
       </c>
       <c r="B309" t="n">
         <v>1</v>
       </c>
       <c r="C309" t="n">
-        <v>0.7344719580860043</v>
+        <v>0.5447595848929258</v>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>To join the meeting on Google Meet, click this link: https://meet.google.com/gow-xyon-gdu Or open Meet and enter this code: gow-xyon-gdu</t>
+          <t>Call From HQ Jessy Congratulations For You FRxx P01N TRY Gam3 Whatsap : 6 0 1 3 4 4 4 4 1 8 8</t>
         </is>
       </c>
       <c r="B310" t="n">
         <v>0</v>
       </c>
       <c r="C310" t="n">
-        <v>0.592966992452631</v>
+        <v>0.5216650829423098</v>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>E T: Wlcm u, MAX-M u=123281882465 p=TTtt2773 on:16/06 00:09:51</t>
+          <t>https://images.app.goo.gl/3fsFEcNTAXyoPA4Z8</t>
         </is>
       </c>
       <c r="B311" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C311" t="n">
-        <v>0.8118397406787777</v>
+        <v>0.6632926926720767</v>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>Let's chat on WhatsApp! It's a fast, simple, and secure app we can use to message and call each other for free. Get it at https://whatsapp.com/dl/</t>
+          <t>明早出门是吗?注意安全</t>
         </is>
       </c>
       <c r="B312" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C312" t="n">
-        <v>0.8777228595604866</v>
+        <v>0.786669211160007</v>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>160166186588,Rohani binti Hassan @ serbane</t>
+          <t>‎Mari bersembang di WhatsApp! Ia cepat, mudah dan selamat untuk membuat panggilan dan menghantar mesej secara percuma. Dapatkannya di</t>
         </is>
       </c>
       <c r="B313" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C313" t="n">
-        <v>0.5244084594855339</v>
+        <v>0.6464315786253781</v>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>l ALWAYS LOVE U G009</t>
+          <t>U388: 嘿! 您升级后的RM50免费积分感到孤独。赶快在它们离开前领取吧!u388my{dot}com</t>
         </is>
       </c>
       <c r="B314" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C314" t="n">
-        <v>0.6268931625494988</v>
+        <v>0.6092501416098447</v>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>义烧30 花生9 豆沙3 加央3</t>
+          <t>&lt;0528752&gt; AC Power Failure</t>
         </is>
       </c>
       <c r="B315" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C315" t="n">
-        <v>0.8605949280867607</v>
+        <v>0.7062027587782712</v>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>Ku bruk abis mkn tek alu mndik. bak mndik bruk nyaman sa nyawa tok. Mkn lh mun dh lmk x mkn hahahaha aok eh mun dh minat x kesah nk oh p mok jaga juak lh tkt ajak mun dh xda org minat gk nk cehhh bebual hahaha</t>
+          <t>&lt;0528752&gt; AC Power Restored</t>
         </is>
       </c>
       <c r="B316" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C316" t="n">
-        <v>0.8888407794842751</v>
+        <v>0.5447595848929258</v>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>Company Kami sedia Free Angpao dan Bonus Special. Sila Claim dekat WS amoi sekarang : 01 13762 3807!</t>
+          <t>UOB-RSA Token User: Your QR Code import/ZIP File Password is !Numb456</t>
         </is>
       </c>
       <c r="B317" t="n">
         <v>0</v>
       </c>
       <c r="C317" t="n">
-        <v>0.6327659485945732</v>
+        <v>0.5934844479668765</v>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>Ayo chat di WhatsApp, aplikasi yang cepat, sederhana, dan aman untuk berkirim pesan dan menelepon secara gratis. Dapatkan di https://whatsapp.com/dl/code=wPUUTXFumG?mode=c</t>
+          <t>*V 2.1.0* Stn Name:BANTING 16/06/2025 00:12:02 Status:RF START Int=9.0mm/60min Daily=7.0mm Monthly=102.0mm Yearly=998.0mm Bat:13.2V</t>
         </is>
       </c>
       <c r="B318" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C318" t="n">
-        <v>0.6500362156043084</v>
+        <v>0.7774117126356931</v>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>16号了咯,你到底要进钱给我吗</t>
+          <t>https://play.google.com/store/apps/details?id=castle.heroes.tower.defense.kingdom.magic.battle.archer</t>
         </is>
       </c>
       <c r="B319" t="n">
         <v>0</v>
       </c>
       <c r="C319" t="n">
-        <v>0.7321086822161705</v>
+        <v>0.6171393857110171</v>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>595291+5 407412+7</t>
+          <t>xblock laa aku deactive semua social media aku...ws no se lg ade je qil 4413 tu..</t>
         </is>
       </c>
       <c r="B320" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C320" t="n">
-        <v>0.7751322986474006</v>
+        <v>0.7635991737950473</v>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>Nk tido la ni ats katil ni hah</t>
+          <t>‎Mari bersembang di WhatsApp! Ia cepat, mudah dan selamat untuk membuat panggilan dan menghantar mesej secara percuma. Dapatkannya di</t>
         </is>
       </c>
       <c r="B321" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C321" t="n">
-        <v>0.733792871058944</v>
+        <v>0.6464315786253781</v>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>Slmt mlm sygg.jg diri.ore mtk mg slh slp ore nga sygg</t>
+          <t>OPEN P-2506236: Process unavailable on Process WebLogic CAMSdomain ReflexManagedServer1:Process unavailable</t>
         </is>
       </c>
       <c r="B322" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C322" t="n">
-        <v>0.8590444622645409</v>
+        <v>0.7161218657385678</v>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>#vivo#simc##862241033847002#1#89601624050700854110#</t>
+          <t>‎Let's chat on WhatsApp! It's a fast, simple, and secure app we can use to message and call each other for free. Get it at</t>
         </is>
       </c>
       <c r="B323" t="n">
         <v>1</v>
       </c>
       <c r="C323" t="n">
-        <v>0.7438079120507209</v>
-      </c>
-    </row>
-    <row r="324">
-      <c r="A324" t="inlineStr">
-        <is>
-          <t>1 ,L2 FMC 19 R1 TMP 02 (CIMB-SVR1),IN CRITICAL MODE, Monday, June 16, 2025 12:11:13 AM.</t>
-        </is>
-      </c>
-      <c r="B324" t="n">
-        <v>1</v>
-      </c>
-      <c r="C324" t="n">
-        <v>0.728294074713227</v>
-      </c>
-    </row>
-    <row r="325">
-      <c r="A325" t="inlineStr">
-        <is>
-          <t>Call From HQ Jessy Congratulations For You FRxx P01N TRY Gam3 Whatsap : 6 0 1 3 4 4 4 4 1 8 8</t>
-        </is>
-      </c>
-      <c r="B325" t="n">
-        <v>1</v>
-      </c>
-      <c r="C325" t="n">
-        <v>0.6195907594552009</v>
-      </c>
-    </row>
-    <row r="326">
-      <c r="A326" t="inlineStr">
-        <is>
-          <t>BX99:您被选了(bonnieliew)!恭喜您获得228次免费旋转。存RM50就解锁!bx99my{dot}com</t>
-        </is>
-      </c>
-      <c r="B326" t="n">
-        <v>0</v>
-      </c>
-      <c r="C326" t="n">
-        <v>0.5227786896834404</v>
-      </c>
-    </row>
-    <row r="327">
-      <c r="A327" t="inlineStr">
-        <is>
-          <t>https://images.app.goo.gl/3fsFEcNTAXyoPA4Z8</t>
-        </is>
-      </c>
-      <c r="B327" t="n">
-        <v>0</v>
-      </c>
-      <c r="C327" t="n">
-        <v>0.526801824391845</v>
-      </c>
-    </row>
-    <row r="328">
-      <c r="A328" t="inlineStr">
-        <is>
-          <t>Amoi sini company goldenbet99,apa kabar sudah bossku,lama dah tak try spin mari.jackpot,free game,Bonusgame menanti anda. Web ; goldenbet99 .com</t>
-        </is>
-      </c>
-      <c r="B328" t="n">
-        <v>1</v>
-      </c>
-      <c r="C328" t="n">
-        <v>0.5072237851014106</v>
-      </c>
-    </row>
-    <row r="329">
-      <c r="A329" t="inlineStr">
-        <is>
-          <t>Company Kami sedia Free Angpao dan Bonus Special. Sila Claim dekat WS amoi sekarang : 01 13762 3807!</t>
-        </is>
-      </c>
-      <c r="B329" t="n">
-        <v>0</v>
-      </c>
-      <c r="C329" t="n">
-        <v>0.6327659485945732</v>
-      </c>
-    </row>
-    <row r="330">
-      <c r="A330" t="inlineStr">
-        <is>
-          <t>1 ,L2 FMC 19 R1 TMP 02 (CIMB-SVR1),IN CRITICAL MODE, Monday, June 16, 2025 12:11:13 AM.</t>
-        </is>
-      </c>
-      <c r="B330" t="n">
-        <v>1</v>
-      </c>
-      <c r="C330" t="n">
-        <v>0.728294074713227</v>
-      </c>
-    </row>
-    <row r="331">
-      <c r="A331" t="inlineStr">
-        <is>
-          <t>HIJACK.HIJACK.HIJACK. KeyOff 24.9V 0km/h N5.09748,E100.44873 http://map.dftracker.com/?loc=3923365642E484</t>
-        </is>
-      </c>
-      <c r="B331" t="n">
-        <v>1</v>
-      </c>
-      <c r="C331" t="n">
-        <v>0.8781408073296516</v>
-      </c>
-    </row>
-    <row r="332">
-      <c r="A332" t="inlineStr">
-        <is>
-          <t>Rm374</t>
-        </is>
-      </c>
-      <c r="B332" t="n">
-        <v>1</v>
-      </c>
-      <c r="C332" t="n">
-        <v>0.8473207952370613</v>
-      </c>
-    </row>
-    <row r="333">
-      <c r="A333" t="inlineStr">
-        <is>
-          <t>RM0 ZUS Coffee: Welcome to ZUS Coffee! Your 4 digits verification code is 4089. Enjoy!</t>
-        </is>
-      </c>
-      <c r="B333" t="n">
-        <v>1</v>
-      </c>
-      <c r="C333" t="n">
-        <v>0.8877298833718269</v>
-      </c>
-    </row>
-    <row r="334">
-      <c r="A334" t="inlineStr">
-        <is>
-          <t>Bereh2 . Lps ni ak bg blke brg mu. ckup ah snpai sni je. halal kan blke smua hk mu pnh v ke ak slme nie</t>
-        </is>
-      </c>
-      <c r="B334" t="n">
-        <v>0</v>
-      </c>
-      <c r="C334" t="n">
-        <v>0.8516078887591393</v>
-      </c>
-    </row>
-    <row r="335">
-      <c r="A335" t="inlineStr">
-        <is>
-          <t>Can't locate you on WhatsApp</t>
-        </is>
-      </c>
-      <c r="B335" t="n">
-        <v>0</v>
-      </c>
-      <c r="C335" t="n">
-        <v>0.8859366921792061</v>
-      </c>
-    </row>
-    <row r="336">
-      <c r="A336" t="inlineStr">
-        <is>
-          <t>Company Kami sedia Free Angpao dan Bonus Special. Sila Claim dekat WS amoi sekarang : 01 13762 3807!</t>
-        </is>
-      </c>
-      <c r="B336" t="n">
-        <v>0</v>
-      </c>
-      <c r="C336" t="n">
-        <v>0.6327659485945732</v>
-      </c>
-    </row>
-    <row r="337">
-      <c r="A337" t="inlineStr">
-        <is>
-          <t>SLMT HARI BAPA SYGG+LOVE U MORE</t>
-        </is>
-      </c>
-      <c r="B337" t="n">
-        <v>0</v>
-      </c>
-      <c r="C337" t="n">
-        <v>0.8984616099009545</v>
-      </c>
-    </row>
-    <row r="338">
-      <c r="A338" t="inlineStr">
-        <is>
-          <t>https://play.google.com/store/apps/details?id=castle.heroes.tower.defense.kingdom.magic.battle.archer</t>
-        </is>
-      </c>
-      <c r="B338" t="n">
-        <v>1</v>
-      </c>
-      <c r="C338" t="n">
-        <v>0.5048782827248542</v>
-      </c>
-    </row>
-    <row r="339">
-      <c r="A339" t="inlineStr">
-        <is>
-          <t>https://play.google.com/store/apps/details?id=castle.heroes.tower.defense.kingdom.magic.battle.archer</t>
-        </is>
-      </c>
-      <c r="B339" t="n">
-        <v>1</v>
-      </c>
-      <c r="C339" t="n">
-        <v>0.5048782827248542</v>
-      </c>
-    </row>
-    <row r="340">
-      <c r="A340" t="inlineStr">
-        <is>
-          <t>Wlkmslm ct blm gaji lagi atta kurang duit bulan ini</t>
-        </is>
-      </c>
-      <c r="B340" t="n">
-        <v>0</v>
-      </c>
-      <c r="C340" t="n">
-        <v>0.7088066337714226</v>
-      </c>
-    </row>
-    <row r="341">
-      <c r="A341" t="inlineStr">
-        <is>
-          <t>Arming with keyswitch #1 Your Alarm Site SST PERIMETER 16 Jun 0h13</t>
-        </is>
-      </c>
-      <c r="B341" t="n">
-        <v>0</v>
-      </c>
-      <c r="C341" t="n">
-        <v>0.7304432092318566</v>
-      </c>
-    </row>
-    <row r="342">
-      <c r="A342" t="inlineStr">
-        <is>
-          <t>Line bb habis, nnti bb chat blik nehh</t>
-        </is>
-      </c>
-      <c r="B342" t="n">
-        <v>0</v>
-      </c>
-      <c r="C342" t="n">
-        <v>0.7271357176909478</v>
-      </c>
-    </row>
-    <row r="343">
-      <c r="A343" t="inlineStr">
-        <is>
-          <t>To join the meeting on Google Meet, click this link: https://meet.google.com/gow-xyon-gdu Or open Meet and enter this code: gow-xyon-gdu</t>
-        </is>
-      </c>
-      <c r="B343" t="n">
-        <v>0</v>
-      </c>
-      <c r="C343" t="n">
-        <v>0.6445202340746863</v>
-      </c>
-    </row>
-    <row r="344">
-      <c r="A344" t="inlineStr">
-        <is>
-          <t>To join the meeting on Google Meet, click this link: https://meet.google.com/gow-xyon-gdu Or open Meet and enter this code: gow-xyon-gdu</t>
-        </is>
-      </c>
-      <c r="B344" t="n">
-        <v>0</v>
-      </c>
-      <c r="C344" t="n">
-        <v>0.6445202340746863</v>
-      </c>
-    </row>
-    <row r="345">
-      <c r="A345" t="inlineStr">
-        <is>
-          <t>Nagios:eth9 Bandwidth - Outbound Host: exadomdbracp5 IP: 10.188.201.123 CRITICAL: Bytes_sent was 1206.05 MB/s 16/06/2025 00:10:38</t>
-        </is>
-      </c>
-      <c r="B345" t="n">
-        <v>0</v>
-      </c>
-      <c r="C345" t="n">
-        <v>0.736812364068125</v>
-      </c>
-    </row>
-    <row r="346">
-      <c r="A346" t="inlineStr">
-        <is>
-          <t>betoi x d nafikan….imam nawawi ada riwayatkn dlm kita ibnu sunni kitab amal seharian….dari Anas…rasulullah saw setiap kali slesai solat selalu ngusap dahi dngn tngn kanan smbil mngucap.....tapi hadis ni daif bang....dan bukan daif biasa....daif jiddan....klau daif biasa abg nk amal ikut aa xdak msalah....sanad hadis ni terrrrlalu lemah....klu x silap sbbnya dua prawi hadis ni zaidul ammi dngn salam al tawil bmsalah kdua prawi ni....dan nasib baik time imam nawawi riwayat hadis ni dia letak skali nama2 prawi hadis supya bole semak status hadis yg ada.....klu hadis ni skdar daif biasa ja sya pn nk bramal abg oii...untuk fadail amal....tpi ni bukan daif biasa....ikot aa sya dh bgi pnerangan atas abg aa nk ikot atau x....wallahualam</t>
-        </is>
-      </c>
-      <c r="B346" t="n">
-        <v>0</v>
-      </c>
-      <c r="C346" t="n">
-        <v>0.8865351786280615</v>
-      </c>
-    </row>
-    <row r="347">
-      <c r="A347" t="inlineStr">
-        <is>
-          <t>Call From HQ Jessy Congratulations For You FRxx P01N TRY Gam3 Whatsap : 6 0 1 3 4 4 4 4 1 8 8</t>
-        </is>
-      </c>
-      <c r="B347" t="n">
-        <v>1</v>
-      </c>
-      <c r="C347" t="n">
-        <v>0.5459061155652063</v>
-      </c>
-    </row>
-    <row r="348">
-      <c r="A348" t="inlineStr">
-        <is>
-          <t>ওয়ালাইকুমুস সালাম আসসালামু আলাইকুম কে আপনি? এবং কাকে চাই?</t>
-        </is>
-      </c>
-      <c r="B348" t="n">
-        <v>0</v>
-      </c>
-      <c r="C348" t="n">
-        <v>0.8728025962973578</v>
-      </c>
-    </row>
-    <row r="349">
-      <c r="A349" t="inlineStr">
-        <is>
-          <t>&lt;0528752&gt; AC Power Failure</t>
-        </is>
-      </c>
-      <c r="B349" t="n">
-        <v>1</v>
-      </c>
-      <c r="C349" t="n">
-        <v>0.7814093122815149</v>
-      </c>
-    </row>
-    <row r="350">
-      <c r="A350" t="inlineStr">
-        <is>
-          <t>Nagios:eth9 Bandwidth - Outbound Host: exadomdbracp5 IP: 10.188.201.123 CRITICAL: Bytes_sent was 1206.05 MB/s 16/06/2025 00:10:38</t>
-        </is>
-      </c>
-      <c r="B350" t="n">
-        <v>0</v>
-      </c>
-      <c r="C350" t="n">
-        <v>0.736812364068125</v>
-      </c>
-    </row>
-    <row r="351">
-      <c r="A351" t="inlineStr">
-        <is>
-          <t>Nagios:eth9 Bandwidth - Outbound Host: exadomdbracp5 IP: 10.188.201.123 CRITICAL: Bytes_sent was 1206.05 MB/s 16/06/2025 00:10:38</t>
-        </is>
-      </c>
-      <c r="B351" t="n">
-        <v>0</v>
-      </c>
-      <c r="C351" t="n">
-        <v>0.736812364068125</v>
-      </c>
-    </row>
-    <row r="352">
-      <c r="A352" t="inlineStr">
-        <is>
-          <t>#vivo#simc##862241033847002#1#89601624050700854110#</t>
-        </is>
-      </c>
-      <c r="B352" t="n">
-        <v>1</v>
-      </c>
-      <c r="C352" t="n">
-        <v>0.6699446330403345</v>
-      </c>
-    </row>
-    <row r="353">
-      <c r="A353" t="inlineStr">
-        <is>
-          <t>&lt;0528752&gt; AC Power Restored</t>
-        </is>
-      </c>
-      <c r="B353" t="n">
-        <v>1</v>
-      </c>
-      <c r="C353" t="n">
-        <v>0.6193467269276636</v>
-      </c>
-    </row>
-    <row r="354">
-      <c r="A354" t="inlineStr">
-        <is>
-          <t>Call From HQ Jessy Congratulations For You FRxx P01N TRY Gam3 Whatsap : 6 0 1 3 4 4 4 4 1 8 8</t>
-        </is>
-      </c>
-      <c r="B354" t="n">
-        <v>1</v>
-      </c>
-      <c r="C354" t="n">
-        <v>0.5459061155652063</v>
-      </c>
-    </row>
-    <row r="355">
-      <c r="A355" t="inlineStr">
-        <is>
-          <t>https://images.app.goo.gl/3fsFEcNTAXyoPA4Z8</t>
-        </is>
-      </c>
-      <c r="B355" t="n">
-        <v>0</v>
-      </c>
-      <c r="C355" t="n">
-        <v>0.5966895332003577</v>
-      </c>
-    </row>
-    <row r="356">
-      <c r="A356" t="inlineStr">
-        <is>
-          <t>Lulisan hg jd mcm mn</t>
-        </is>
-      </c>
-      <c r="B356" t="n">
-        <v>0</v>
-      </c>
-      <c r="C356" t="n">
-        <v>0.8792976548338873</v>
-      </c>
-    </row>
-    <row r="357">
-      <c r="A357" t="inlineStr">
-        <is>
-          <t>明早出门是吗?注意安全</t>
-        </is>
-      </c>
-      <c r="B357" t="n">
-        <v>0</v>
-      </c>
-      <c r="C357" t="n">
-        <v>0.7028707375193579</v>
-      </c>
-    </row>
-    <row r="358">
-      <c r="A358" t="inlineStr">
-        <is>
-          <t>‎Mari bersembang di WhatsApp! Ia cepat, mudah dan selamat untuk membuat panggilan dan menghantar mesej secara percuma. Dapatkannya di</t>
-        </is>
-      </c>
-      <c r="B358" t="n">
-        <v>1</v>
-      </c>
-      <c r="C358" t="n">
-        <v>0.7218469868039148</v>
-      </c>
-    </row>
-    <row r="359">
-      <c r="A359" t="inlineStr">
-        <is>
-          <t>U388: 嘿! 您升级后的RM50免费积分感到孤独。赶快在它们离开前领取吧!u388my{dot}com</t>
-        </is>
-      </c>
-      <c r="B359" t="n">
-        <v>1</v>
-      </c>
-      <c r="C359" t="n">
-        <v>0.6729929337834375</v>
-      </c>
-    </row>
-    <row r="360">
-      <c r="A360" t="inlineStr">
-        <is>
-          <t>&lt;0528752&gt; AC Power Failure</t>
-        </is>
-      </c>
-      <c r="B360" t="n">
-        <v>1</v>
-      </c>
-      <c r="C360" t="n">
-        <v>0.7814093122815149</v>
-      </c>
-    </row>
-    <row r="361">
-      <c r="A361" t="inlineStr">
-        <is>
-          <t>Tak pun kau duduk je dalam bilik kau tu diam2 , dia panggil ke buat bodh je kau diam jee .. mak tak bagi aku kawan dan jumpa dia dah .</t>
-        </is>
-      </c>
-      <c r="B361" t="n">
-        <v>0</v>
-      </c>
-      <c r="C361" t="n">
-        <v>0.8219634701872809</v>
-      </c>
-    </row>
-    <row r="362">
-      <c r="A362" t="inlineStr">
-        <is>
-          <t>&lt;0528752&gt; AC Power Restored</t>
-        </is>
-      </c>
-      <c r="B362" t="n">
-        <v>1</v>
-      </c>
-      <c r="C362" t="n">
-        <v>0.619346071276571</v>
-      </c>
-    </row>
-    <row r="363">
-      <c r="A363" t="inlineStr">
-        <is>
-          <t>UOB-RSA Token User: Your QR Code import/ZIP File Password is !Numb456</t>
-        </is>
-      </c>
-      <c r="B363" t="n">
-        <v>0</v>
-      </c>
-      <c r="C363" t="n">
-        <v>0.5319907178545935</v>
-      </c>
-    </row>
-    <row r="364">
-      <c r="A364" t="inlineStr">
-        <is>
-          <t>*V 2.1.0* Stn Name:BANTING 16/06/2025 00:12:02 Status:RF START Int=9.0mm/60min Daily=7.0mm Monthly=102.0mm Yearly=998.0mm Bat:13.2V</t>
-        </is>
-      </c>
-      <c r="B364" t="n">
-        <v>1</v>
-      </c>
-      <c r="C364" t="n">
-        <v>0.8490828762387292</v>
-      </c>
-    </row>
-    <row r="365">
-      <c r="A365" t="inlineStr">
-        <is>
-          <t>https://play.google.com/store/apps/details?id=castle.heroes.tower.defense.kingdom.magic.battle.archer</t>
-        </is>
-      </c>
-      <c r="B365" t="n">
-        <v>0</v>
-      </c>
-      <c r="C365" t="n">
-        <v>0.5624122132922156</v>
-      </c>
-    </row>
-    <row r="366">
-      <c r="A366" t="inlineStr">
-        <is>
-          <t>xblock laa aku deactive semua social media aku...ws no se lg ade je qil 4413 tu..</t>
-        </is>
-      </c>
-      <c r="B366" t="n">
-        <v>0</v>
-      </c>
-      <c r="C366" t="n">
-        <v>0.6755233516360266</v>
-      </c>
-    </row>
-    <row r="367">
-      <c r="A367" t="inlineStr">
-        <is>
-          <t>‎Mari bersembang di WhatsApp! Ia cepat, mudah dan selamat untuk membuat panggilan dan menghantar mesej secara percuma. Dapatkannya di</t>
-        </is>
-      </c>
-      <c r="B367" t="n">
-        <v>1</v>
-      </c>
-      <c r="C367" t="n">
-        <v>0.7218469868039148</v>
-      </c>
-    </row>
-    <row r="368">
-      <c r="A368" t="inlineStr">
-        <is>
-          <t>OPEN P-2506236: Process unavailable on Process WebLogic CAMSdomain ReflexManagedServer1:Process unavailable</t>
-        </is>
-      </c>
-      <c r="B368" t="n">
-        <v>1</v>
-      </c>
-      <c r="C368" t="n">
-        <v>0.7746053228711145</v>
-      </c>
-    </row>
-    <row r="369">
-      <c r="A369" t="inlineStr">
-        <is>
-          <t>https://share.icloud.com/photos/001PVwZTx7M8sCAAum-c7_2rA</t>
-        </is>
-      </c>
-      <c r="B369" t="n">
-        <v>0</v>
-      </c>
-      <c r="C369" t="n">
-        <v>0.8615509678984625</v>
-      </c>
-    </row>
-    <row r="370">
-      <c r="A370" t="inlineStr">
-        <is>
-          <t>https://share.icloud.com/photos/001PVwZTx7M8sCAAum-c7_2rA</t>
-        </is>
-      </c>
-      <c r="B370" t="n">
-        <v>0</v>
-      </c>
-      <c r="C370" t="n">
-        <v>0.8615509678984625</v>
-      </c>
-    </row>
-    <row r="371">
-      <c r="A371" t="inlineStr">
-        <is>
-          <t>https://share.icloud.com/photos/001PVwZTx7M8sCAAum-c7_2rA</t>
-        </is>
-      </c>
-      <c r="B371" t="n">
-        <v>0</v>
-      </c>
-      <c r="C371" t="n">
-        <v>0.8615509678984625</v>
-      </c>
-    </row>
-    <row r="372">
-      <c r="A372" t="inlineStr">
-        <is>
-          <t>Selamat Malam, assalamualaikum</t>
-        </is>
-      </c>
-      <c r="B372" t="n">
-        <v>0</v>
-      </c>
-      <c r="C372" t="n">
-        <v>0.8471347798968298</v>
-      </c>
-    </row>
-    <row r="373">
-      <c r="A373" t="inlineStr">
-        <is>
-          <t>https://share.icloud.com/photos/001PVwZTx7M8sCAAum-c7_2rA</t>
-        </is>
-      </c>
-      <c r="B373" t="n">
-        <v>0</v>
-      </c>
-      <c r="C373" t="n">
-        <v>0.8615509678984625</v>
-      </c>
-    </row>
-    <row r="374">
-      <c r="A374" t="inlineStr">
-        <is>
-          <t>‎Let's chat on WhatsApp! It's a fast, simple, and secure app we can use to message and call each other for free. Get it at</t>
-        </is>
-      </c>
-      <c r="B374" t="n">
-        <v>1</v>
-      </c>
-      <c r="C374" t="n">
-        <v>0.5626952538823145</v>
+        <v>0.508270038593945</v>
       </c>
     </row>
   </sheetData>
